--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D564E189-092B-4C37-9070-0A77AD270B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D5F592-804F-4BA4-878A-9FC11BE65B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4235,9 +4235,6 @@
       <c r="S6" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T6" s="3">
-        <v>1</v>
-      </c>
       <c r="U6" s="1">
         <v>10</v>
       </c>
@@ -4384,9 +4381,6 @@
       <c r="S9" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="T9" s="3">
-        <v>2</v>
-      </c>
       <c r="U9" s="1">
         <v>95</v>
       </c>
@@ -4437,9 +4431,6 @@
       <c r="S10" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="T10" s="3">
-        <v>3</v>
-      </c>
       <c r="U10" s="1">
         <v>133</v>
       </c>
@@ -4490,9 +4481,6 @@
       <c r="S11" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="T11" s="3">
-        <v>3</v>
-      </c>
       <c r="U11" s="1">
         <v>162</v>
       </c>
@@ -4543,9 +4531,6 @@
       <c r="S12" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="T12" s="3">
-        <v>3</v>
-      </c>
       <c r="U12" s="1">
         <v>191</v>
       </c>
@@ -4592,9 +4577,6 @@
       </c>
       <c r="S13" s="3" t="s">
         <v>421</v>
-      </c>
-      <c r="T13" s="3">
-        <v>1</v>
       </c>
       <c r="U13" s="1">
         <v>15</v>
@@ -4692,9 +4674,6 @@
       <c r="S15" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T15" s="3">
-        <v>1</v>
-      </c>
       <c r="U15" s="1">
         <v>37</v>
       </c>
@@ -4788,9 +4767,6 @@
       <c r="S17" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T17" s="3">
-        <v>1</v>
-      </c>
       <c r="U17" s="1">
         <v>13</v>
       </c>
@@ -4835,9 +4811,6 @@
       <c r="S18" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T18" s="3">
-        <v>2</v>
-      </c>
       <c r="U18" s="1">
         <v>60</v>
       </c>
@@ -4885,9 +4858,6 @@
       <c r="S19" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T19" s="3">
-        <v>3</v>
-      </c>
       <c r="U19" s="1">
         <v>102</v>
       </c>
@@ -4935,9 +4905,6 @@
       <c r="S20" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T20" s="3">
-        <v>3</v>
-      </c>
       <c r="U20" s="1">
         <v>136</v>
       </c>
@@ -4985,9 +4952,6 @@
       <c r="S21" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T21" s="3">
-        <v>3</v>
-      </c>
       <c r="U21" s="1">
         <v>165</v>
       </c>
@@ -5037,9 +5001,6 @@
       </c>
       <c r="S22" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="T22" s="3">
-        <v>3</v>
       </c>
       <c r="U22" s="1">
         <v>194</v>
@@ -5136,9 +5097,6 @@
       <c r="S24" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T24" s="3">
-        <v>1</v>
-      </c>
       <c r="U24" s="1">
         <v>5</v>
       </c>
@@ -5186,9 +5144,6 @@
       <c r="S25" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T25" s="3">
-        <v>2</v>
-      </c>
       <c r="U25" s="1">
         <v>71</v>
       </c>
@@ -5239,9 +5194,6 @@
       <c r="S26" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T26" s="3">
-        <v>3</v>
-      </c>
       <c r="U26" s="1">
         <v>127</v>
       </c>
@@ -5292,9 +5244,6 @@
       <c r="S27" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T27" s="3">
-        <v>3</v>
-      </c>
       <c r="U27" s="1">
         <v>157</v>
       </c>
@@ -5342,9 +5291,6 @@
       <c r="S28" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T28" s="3">
-        <v>3</v>
-      </c>
       <c r="U28" s="1">
         <v>186</v>
       </c>
@@ -5395,9 +5341,6 @@
       <c r="S29" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T29" s="3">
-        <v>1</v>
-      </c>
       <c r="U29" s="1">
         <v>27</v>
       </c>
@@ -5448,9 +5391,6 @@
       <c r="S30" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T30" s="3">
-        <v>3</v>
-      </c>
       <c r="U30" s="1">
         <v>116</v>
       </c>
@@ -5501,9 +5441,6 @@
       <c r="S31" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T31" s="3">
-        <v>3</v>
-      </c>
       <c r="U31" s="1">
         <v>147</v>
       </c>
@@ -5554,9 +5491,6 @@
       <c r="S32" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T32" s="3">
-        <v>3</v>
-      </c>
       <c r="U32" s="1">
         <v>176</v>
       </c>
@@ -5606,9 +5540,6 @@
       </c>
       <c r="S33" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="T33" s="3">
-        <v>3</v>
       </c>
       <c r="U33" s="1">
         <v>205</v>
@@ -5706,9 +5637,6 @@
       <c r="S35" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T35" s="3">
-        <v>1</v>
-      </c>
       <c r="U35" s="1">
         <v>35</v>
       </c>
@@ -5855,9 +5783,6 @@
       <c r="S38" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T38" s="3">
-        <v>2</v>
-      </c>
       <c r="U38" s="1">
         <v>82</v>
       </c>
@@ -6294,9 +6219,6 @@
       <c r="S46" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T46" s="3">
-        <v>3</v>
-      </c>
       <c r="U46" s="1">
         <v>159</v>
       </c>
@@ -6347,9 +6269,6 @@
       <c r="S47" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T47" s="3">
-        <v>3</v>
-      </c>
       <c r="U47" s="1">
         <v>160</v>
       </c>
@@ -6400,9 +6319,6 @@
       <c r="S48" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T48" s="3">
-        <v>3</v>
-      </c>
       <c r="U48" s="1">
         <v>188</v>
       </c>
@@ -6452,9 +6368,6 @@
       </c>
       <c r="S49" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="T49" s="3">
-        <v>3</v>
       </c>
       <c r="U49" s="1">
         <v>189</v>
@@ -6692,9 +6605,6 @@
       <c r="S54" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T54" s="3">
-        <v>2</v>
-      </c>
       <c r="U54" s="1">
         <v>81</v>
       </c>
@@ -6745,9 +6655,6 @@
       <c r="S55" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T55" s="3">
-        <v>3</v>
-      </c>
       <c r="U55" s="1">
         <v>120</v>
       </c>
@@ -6798,9 +6705,6 @@
       <c r="S56" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T56" s="3">
-        <v>3</v>
-      </c>
       <c r="U56" s="1">
         <v>151</v>
       </c>
@@ -6850,9 +6754,6 @@
       </c>
       <c r="S57" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="T57" s="3">
-        <v>3</v>
       </c>
       <c r="U57" s="1">
         <v>180</v>
@@ -6953,9 +6854,6 @@
       </c>
       <c r="S59" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="T59" s="3">
-        <v>1</v>
       </c>
       <c r="U59" s="1">
         <v>49</v>
@@ -7053,9 +6951,6 @@
       <c r="S61" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T61" s="3">
-        <v>1</v>
-      </c>
       <c r="U61" s="1">
         <v>9</v>
       </c>
@@ -7102,9 +6997,6 @@
       </c>
       <c r="S62" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="T62" s="3">
-        <v>2</v>
       </c>
       <c r="U62" s="1">
         <v>97</v>
@@ -7248,9 +7140,6 @@
       <c r="S65" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T65" s="3">
-        <v>1</v>
-      </c>
       <c r="U65" s="1">
         <v>29</v>
       </c>
@@ -7297,9 +7186,6 @@
       </c>
       <c r="S66" s="3" t="s">
         <v>421</v>
-      </c>
-      <c r="T66" s="3">
-        <v>2</v>
       </c>
       <c r="U66" s="1">
         <v>94</v>
@@ -7399,9 +7285,6 @@
       <c r="S68" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T68" s="3">
-        <v>1</v>
-      </c>
       <c r="U68" s="1">
         <v>28</v>
       </c>
@@ -7452,9 +7335,6 @@
       <c r="S69" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T69" s="3">
-        <v>3</v>
-      </c>
       <c r="U69" s="1">
         <v>117</v>
       </c>
@@ -7505,9 +7385,6 @@
       <c r="S70" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T70" s="3">
-        <v>3</v>
-      </c>
       <c r="U70" s="1">
         <v>148</v>
       </c>
@@ -7558,9 +7435,6 @@
       <c r="S71" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T71" s="3">
-        <v>3</v>
-      </c>
       <c r="U71" s="1">
         <v>177</v>
       </c>
@@ -7611,9 +7485,6 @@
       <c r="S72" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T72" s="3">
-        <v>3</v>
-      </c>
       <c r="U72" s="1">
         <v>206</v>
       </c>
@@ -7664,9 +7535,6 @@
       <c r="S73" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="T73" s="3">
-        <v>1</v>
-      </c>
       <c r="U73" s="1">
         <v>43</v>
       </c>
@@ -7714,9 +7582,6 @@
       <c r="S74" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T74" s="3">
-        <v>2</v>
-      </c>
       <c r="U74" s="1">
         <v>86</v>
       </c>
@@ -7764,9 +7629,6 @@
       <c r="S75" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T75" s="3">
-        <v>2</v>
-      </c>
       <c r="U75" s="1">
         <v>87</v>
       </c>
@@ -7814,9 +7676,6 @@
       <c r="S76" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T76" s="3">
-        <v>3</v>
-      </c>
       <c r="U76" s="1">
         <v>122</v>
       </c>
@@ -7864,9 +7723,6 @@
       <c r="S77" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T77" s="3">
-        <v>3</v>
-      </c>
       <c r="U77" s="1">
         <v>123</v>
       </c>
@@ -7917,9 +7773,6 @@
       <c r="S78" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T78" s="3">
-        <v>3</v>
-      </c>
       <c r="U78" s="1">
         <v>153</v>
       </c>
@@ -7969,9 +7822,6 @@
       </c>
       <c r="S79" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="T79" s="3">
-        <v>3</v>
       </c>
       <c r="U79" s="1">
         <v>182</v>
@@ -8069,9 +7919,6 @@
       <c r="S81" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T81" s="3">
-        <v>1</v>
-      </c>
       <c r="U81" s="1">
         <v>18</v>
       </c>
@@ -8121,9 +7968,6 @@
       </c>
       <c r="S82" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="T82" s="3">
-        <v>1</v>
       </c>
       <c r="U82" s="1">
         <v>34</v>
@@ -8267,9 +8111,6 @@
       <c r="S85" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T85" s="3">
-        <v>1</v>
-      </c>
       <c r="U85" s="1">
         <v>4</v>
       </c>
@@ -8317,9 +8158,6 @@
       <c r="S86" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T86" s="3">
-        <v>2</v>
-      </c>
       <c r="U86" s="1">
         <v>69</v>
       </c>
@@ -8367,9 +8205,6 @@
       <c r="S87" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T87" s="3">
-        <v>2</v>
-      </c>
       <c r="U87" s="1">
         <v>70</v>
       </c>
@@ -8420,9 +8255,6 @@
       <c r="S88" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T88" s="3">
-        <v>3</v>
-      </c>
       <c r="U88" s="1">
         <v>126</v>
       </c>
@@ -8473,9 +8305,6 @@
       <c r="S89" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T89" s="3">
-        <v>3</v>
-      </c>
       <c r="U89" s="1">
         <v>156</v>
       </c>
@@ -8522,9 +8351,6 @@
       </c>
       <c r="S90" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="T90" s="3">
-        <v>3</v>
       </c>
       <c r="U90" s="1">
         <v>185</v>
@@ -8678,9 +8504,6 @@
       <c r="S93" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="T93" s="3">
-        <v>1</v>
-      </c>
       <c r="U93" s="1">
         <v>16</v>
       </c>
@@ -8731,9 +8554,6 @@
       <c r="S94" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="T94" s="3">
-        <v>1</v>
-      </c>
       <c r="U94" s="1">
         <v>57</v>
       </c>
@@ -8784,9 +8604,6 @@
       <c r="S95" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="T95" s="3">
-        <v>3</v>
-      </c>
       <c r="U95" s="1">
         <v>132</v>
       </c>
@@ -8834,9 +8651,6 @@
       <c r="S96" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="T96" s="3">
-        <v>3</v>
-      </c>
       <c r="U96" s="1">
         <v>161</v>
       </c>
@@ -8887,9 +8701,6 @@
       <c r="S97" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="T97" s="3">
-        <v>3</v>
-      </c>
       <c r="U97" s="1">
         <v>190</v>
       </c>
@@ -8939,9 +8750,6 @@
       </c>
       <c r="S98" s="3" t="s">
         <v>632</v>
-      </c>
-      <c r="T98" s="3">
-        <v>2</v>
       </c>
       <c r="U98" s="1">
         <v>64</v>
@@ -9038,9 +8846,6 @@
       <c r="S100" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T100" s="3">
-        <v>1</v>
-      </c>
       <c r="U100" s="1">
         <v>36</v>
       </c>
@@ -9091,9 +8896,6 @@
       <c r="S101" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T101" s="3">
-        <v>1</v>
-      </c>
       <c r="U101" s="1">
         <v>39</v>
       </c>
@@ -9150,9 +8952,6 @@
       <c r="R102" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T102" s="3">
-        <v>2</v>
-      </c>
       <c r="U102" s="1">
         <v>67</v>
       </c>
@@ -9203,9 +9002,6 @@
       <c r="S103" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="T103" s="3">
-        <v>1</v>
-      </c>
       <c r="U103" s="1">
         <v>48</v>
       </c>
@@ -9256,9 +9052,6 @@
       <c r="S104" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T104" s="3">
-        <v>2</v>
-      </c>
       <c r="U104" s="1">
         <v>80</v>
       </c>
@@ -9309,9 +9102,6 @@
       <c r="S105" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T105" s="3">
-        <v>1</v>
-      </c>
       <c r="U105" s="1">
         <v>32</v>
       </c>
@@ -9361,9 +9151,6 @@
       </c>
       <c r="S106" s="3" t="s">
         <v>549</v>
-      </c>
-      <c r="T106" s="3">
-        <v>1</v>
       </c>
       <c r="U106" s="1">
         <v>41</v>
@@ -9461,9 +9248,6 @@
       <c r="S108" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="T108" s="3">
-        <v>1</v>
-      </c>
       <c r="U108" s="1">
         <v>21</v>
       </c>
@@ -9570,9 +9354,6 @@
       <c r="S110" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="T110" s="3">
-        <v>3</v>
-      </c>
       <c r="U110" s="1">
         <v>143</v>
       </c>
@@ -9623,9 +9404,6 @@
       <c r="S111" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="T111" s="3">
-        <v>3</v>
-      </c>
       <c r="U111" s="1">
         <v>172</v>
       </c>
@@ -9676,9 +9454,6 @@
       <c r="S112" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="T112" s="3">
-        <v>3</v>
-      </c>
       <c r="U112" s="1">
         <v>201</v>
       </c>
@@ -9729,9 +9504,6 @@
       <c r="S113" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T113" s="3">
-        <v>3</v>
-      </c>
       <c r="U113" s="1">
         <v>106</v>
       </c>
@@ -9782,9 +9554,6 @@
       <c r="S114" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T114" s="3">
-        <v>3</v>
-      </c>
       <c r="U114" s="1">
         <v>141</v>
       </c>
@@ -9835,9 +9604,6 @@
       <c r="S115" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T115" s="3">
-        <v>3</v>
-      </c>
       <c r="U115" s="1">
         <v>170</v>
       </c>
@@ -9888,9 +9654,6 @@
       <c r="S116" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T116" s="3">
-        <v>3</v>
-      </c>
       <c r="U116" s="1">
         <v>199</v>
       </c>
@@ -9997,9 +9760,6 @@
       <c r="S118" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T118" s="3">
-        <v>2</v>
-      </c>
       <c r="U118" s="1">
         <v>51</v>
       </c>
@@ -10047,9 +9807,6 @@
       <c r="S119" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T119" s="3">
-        <v>2</v>
-      </c>
       <c r="U119" s="1">
         <v>52</v>
       </c>
@@ -10100,9 +9857,6 @@
       <c r="S120" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T120" s="3">
-        <v>2</v>
-      </c>
       <c r="U120" s="1">
         <v>53</v>
       </c>
@@ -10150,9 +9904,6 @@
       <c r="S121" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T121" s="3">
-        <v>2</v>
-      </c>
       <c r="U121" s="1">
         <v>54</v>
       </c>
@@ -10200,9 +9951,6 @@
       <c r="S122" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T122" s="3">
-        <v>2</v>
-      </c>
       <c r="U122" s="1">
         <v>88</v>
       </c>
@@ -10250,9 +9998,6 @@
       <c r="S123" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T123" s="3">
-        <v>2</v>
-      </c>
       <c r="U123" s="1">
         <v>89</v>
       </c>
@@ -10300,9 +10045,6 @@
       <c r="S124" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T124" s="3">
-        <v>2</v>
-      </c>
       <c r="U124" s="1">
         <v>90</v>
       </c>
@@ -10350,9 +10092,6 @@
       <c r="S125" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T125" s="3">
-        <v>3</v>
-      </c>
       <c r="U125" s="1">
         <v>124</v>
       </c>
@@ -10400,9 +10139,6 @@
       <c r="S126" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T126" s="3">
-        <v>3</v>
-      </c>
       <c r="U126" s="1">
         <v>125</v>
       </c>
@@ -10453,9 +10189,6 @@
       <c r="S127" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T127" s="3">
-        <v>3</v>
-      </c>
       <c r="U127" s="1">
         <v>154</v>
       </c>
@@ -10503,9 +10236,6 @@
       <c r="S128" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T128" s="3">
-        <v>3</v>
-      </c>
       <c r="U128" s="1">
         <v>155</v>
       </c>
@@ -10556,9 +10286,6 @@
       <c r="S129" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T129" s="3">
-        <v>3</v>
-      </c>
       <c r="U129" s="1">
         <v>183</v>
       </c>
@@ -10606,9 +10333,6 @@
       <c r="S130" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T130" s="3">
-        <v>3</v>
-      </c>
       <c r="U130" s="1">
         <v>184</v>
       </c>
@@ -10656,9 +10380,6 @@
       <c r="S131" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T131" s="3">
-        <v>1</v>
-      </c>
       <c r="U131" s="1">
         <v>14</v>
       </c>
@@ -10762,9 +10483,6 @@
       <c r="S133" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T133" s="3">
-        <v>3</v>
-      </c>
       <c r="U133" s="1">
         <v>101</v>
       </c>
@@ -10812,9 +10530,6 @@
       <c r="S134" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T134" s="3">
-        <v>3</v>
-      </c>
       <c r="U134" s="1">
         <v>135</v>
       </c>
@@ -10862,9 +10577,6 @@
       <c r="S135" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T135" s="3">
-        <v>3</v>
-      </c>
       <c r="U135" s="1">
         <v>164</v>
       </c>
@@ -10912,9 +10624,6 @@
       <c r="S136" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T136" s="3">
-        <v>3</v>
-      </c>
       <c r="U136" s="1">
         <v>193</v>
       </c>
@@ -10965,9 +10674,6 @@
       <c r="S137" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T137" s="3">
-        <v>1</v>
-      </c>
       <c r="U137" s="1">
         <v>25</v>
       </c>
@@ -11070,9 +10776,6 @@
       </c>
       <c r="S139" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="T139" s="3">
-        <v>3</v>
       </c>
       <c r="U139" s="1">
         <v>100</v>
@@ -11167,9 +10870,6 @@
       <c r="S141" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T141" s="3">
-        <v>1</v>
-      </c>
       <c r="U141" s="1">
         <v>40</v>
       </c>
@@ -11219,9 +10919,6 @@
       </c>
       <c r="S142" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="T142" s="3">
-        <v>1</v>
       </c>
       <c r="U142" s="1">
         <v>38</v>
@@ -11316,9 +11013,6 @@
       <c r="S144" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T144" s="3">
-        <v>1</v>
-      </c>
       <c r="U144" s="1">
         <v>11</v>
       </c>
@@ -11417,9 +11111,6 @@
       <c r="S146" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T146" s="3">
-        <v>2</v>
-      </c>
       <c r="U146" s="1">
         <v>77</v>
       </c>
@@ -11470,9 +11161,6 @@
       <c r="S147" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T147" s="3">
-        <v>3</v>
-      </c>
       <c r="U147" s="1">
         <v>119</v>
       </c>
@@ -11523,9 +11211,6 @@
       <c r="S148" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T148" s="3">
-        <v>3</v>
-      </c>
       <c r="U148" s="1">
         <v>150</v>
       </c>
@@ -11576,9 +11261,6 @@
       <c r="S149" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T149" s="3">
-        <v>3</v>
-      </c>
       <c r="U149" s="1">
         <v>179</v>
       </c>
@@ -11628,9 +11310,6 @@
       </c>
       <c r="S150" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="T150" s="3">
-        <v>3</v>
       </c>
       <c r="U150" s="1">
         <v>208</v>
@@ -11733,9 +11412,6 @@
       <c r="S152" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T152" s="3">
-        <v>1</v>
-      </c>
       <c r="U152" s="1">
         <v>6</v>
       </c>
@@ -11787,9 +11463,6 @@
       <c r="S153" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T153" s="3">
-        <v>2</v>
-      </c>
       <c r="U153" s="1">
         <v>61</v>
       </c>
@@ -11841,9 +11514,6 @@
       <c r="S154" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T154" s="3">
-        <v>2</v>
-      </c>
       <c r="U154" s="1">
         <v>62</v>
       </c>
@@ -11895,9 +11565,6 @@
       <c r="S155" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T155" s="3">
-        <v>2</v>
-      </c>
       <c r="U155" s="1">
         <v>63</v>
       </c>
@@ -11949,9 +11616,6 @@
       <c r="S156" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T156" s="3">
-        <v>3</v>
-      </c>
       <c r="U156" s="1">
         <v>104</v>
       </c>
@@ -12003,9 +11667,6 @@
       <c r="S157" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T157" s="3">
-        <v>3</v>
-      </c>
       <c r="U157" s="1">
         <v>105</v>
       </c>
@@ -12057,9 +11718,6 @@
       <c r="S158" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T158" s="3">
-        <v>3</v>
-      </c>
       <c r="U158" s="1">
         <v>139</v>
       </c>
@@ -12111,9 +11769,6 @@
       <c r="S159" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T159" s="3">
-        <v>3</v>
-      </c>
       <c r="U159" s="1">
         <v>140</v>
       </c>
@@ -12165,9 +11820,6 @@
       <c r="S160" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T160" s="3">
-        <v>3</v>
-      </c>
       <c r="U160" s="1">
         <v>168</v>
       </c>
@@ -12219,9 +11871,6 @@
       <c r="S161" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T161" s="3">
-        <v>3</v>
-      </c>
       <c r="U161" s="1">
         <v>169</v>
       </c>
@@ -12273,9 +11922,6 @@
       <c r="S162" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T162" s="3">
-        <v>3</v>
-      </c>
       <c r="U162" s="1">
         <v>197</v>
       </c>
@@ -12327,9 +11973,6 @@
       <c r="S163" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T163" s="3">
-        <v>3</v>
-      </c>
       <c r="U163" s="1">
         <v>198</v>
       </c>
@@ -12428,9 +12071,6 @@
       </c>
       <c r="S165" s="3" t="s">
         <v>421</v>
-      </c>
-      <c r="T165" s="3">
-        <v>2</v>
       </c>
       <c r="U165" s="1">
         <v>96</v>
@@ -12525,9 +12165,6 @@
       <c r="S167" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T167" s="3">
-        <v>1</v>
-      </c>
       <c r="U167" s="1">
         <v>19</v>
       </c>
@@ -12575,9 +12212,6 @@
       <c r="S168" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T168" s="3">
-        <v>2</v>
-      </c>
       <c r="U168" s="1">
         <v>83</v>
       </c>
@@ -12627,9 +12261,6 @@
       </c>
       <c r="S169" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="T169" s="3">
-        <v>2</v>
       </c>
       <c r="U169" s="1">
         <v>84</v>
@@ -12727,9 +12358,6 @@
       <c r="S171" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T171" s="3">
-        <v>2</v>
-      </c>
       <c r="U171" s="1">
         <v>79</v>
       </c>
@@ -12778,9 +12406,6 @@
       <c r="S172" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T172" s="3">
-        <v>3</v>
-      </c>
       <c r="U172" s="1">
         <v>118</v>
       </c>
@@ -12829,9 +12454,6 @@
       <c r="S173" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T173" s="3">
-        <v>3</v>
-      </c>
       <c r="U173" s="1">
         <v>149</v>
       </c>
@@ -12880,9 +12502,6 @@
       <c r="S174" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T174" s="3">
-        <v>3</v>
-      </c>
       <c r="U174" s="1">
         <v>178</v>
       </c>
@@ -12930,9 +12549,6 @@
       </c>
       <c r="S175" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="T175" s="3">
-        <v>3</v>
       </c>
       <c r="U175" s="1">
         <v>207</v>
@@ -13127,9 +12743,6 @@
       <c r="S179" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T179" s="3">
-        <v>1</v>
-      </c>
       <c r="U179" s="1">
         <v>12</v>
       </c>
@@ -13230,9 +12843,6 @@
       <c r="S181" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T181" s="3">
-        <v>2</v>
-      </c>
       <c r="U181" s="1">
         <v>98</v>
       </c>
@@ -13333,9 +12943,6 @@
       <c r="S183" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T183" s="3">
-        <v>3</v>
-      </c>
       <c r="U183" s="1">
         <v>134</v>
       </c>
@@ -13435,9 +13042,6 @@
       </c>
       <c r="S185" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="T185" s="3">
-        <v>3</v>
       </c>
       <c r="U185" s="1">
         <v>192</v>
@@ -13487,9 +13091,6 @@
       <c r="S186" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="T186" s="3">
-        <v>1</v>
-      </c>
       <c r="U186" s="1">
         <v>23</v>
       </c>
@@ -13586,9 +13187,6 @@
       <c r="S188" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="T188" s="3">
-        <v>1</v>
-      </c>
       <c r="U188" s="1">
         <v>42</v>
       </c>
@@ -13849,9 +13447,6 @@
       <c r="S193" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T193" s="3">
-        <v>3</v>
-      </c>
       <c r="U193" s="1">
         <v>128</v>
       </c>
@@ -13900,9 +13495,6 @@
       <c r="S194" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T194" s="3">
-        <v>3</v>
-      </c>
       <c r="U194" s="1">
         <v>129</v>
       </c>
@@ -14004,9 +13596,6 @@
       <c r="S196" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T196" s="3">
-        <v>3</v>
-      </c>
       <c r="U196" s="1">
         <v>187</v>
       </c>
@@ -14055,9 +13644,6 @@
       <c r="S197" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="T197" s="3">
-        <v>1</v>
-      </c>
       <c r="U197" s="1">
         <v>44</v>
       </c>
@@ -14159,9 +13745,6 @@
       <c r="S199" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T199" s="3">
-        <v>2</v>
-      </c>
       <c r="U199" s="1">
         <v>85</v>
       </c>
@@ -14209,9 +13792,6 @@
       <c r="S200" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="T200" s="3">
-        <v>1</v>
-      </c>
       <c r="U200" s="1">
         <v>46</v>
       </c>
@@ -14259,9 +13839,6 @@
       <c r="S201" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T201" s="3">
-        <v>3</v>
-      </c>
       <c r="U201" s="1">
         <v>138</v>
       </c>
@@ -14309,9 +13886,6 @@
       <c r="S202" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T202" s="3">
-        <v>3</v>
-      </c>
       <c r="U202" s="1">
         <v>167</v>
       </c>
@@ -14358,9 +13932,6 @@
       </c>
       <c r="S203" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="T203" s="3">
-        <v>3</v>
       </c>
       <c r="U203" s="1">
         <v>196</v>
@@ -14513,9 +14084,6 @@
       <c r="S206" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T206" s="3">
-        <v>1</v>
-      </c>
       <c r="U206" s="1">
         <v>26</v>
       </c>
@@ -14566,9 +14134,6 @@
       <c r="S207" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T207" s="3">
-        <v>3</v>
-      </c>
       <c r="U207" s="1">
         <v>121</v>
       </c>
@@ -14619,9 +14184,6 @@
       <c r="S208" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T208" s="3">
-        <v>3</v>
-      </c>
       <c r="U208" s="1">
         <v>152</v>
       </c>
@@ -14671,9 +14233,6 @@
       </c>
       <c r="S209" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="T209" s="3">
-        <v>3</v>
       </c>
       <c r="U209" s="1">
         <v>181</v>
@@ -15215,9 +14774,6 @@
       <c r="S220" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="T220" s="3">
-        <v>1</v>
-      </c>
       <c r="U220" s="1">
         <v>20</v>
       </c>
@@ -15265,9 +14821,6 @@
       <c r="S221" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="T221" s="3">
-        <v>2</v>
-      </c>
       <c r="U221" s="1">
         <v>65</v>
       </c>
@@ -15315,9 +14868,6 @@
       <c r="S222" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="T222" s="3">
-        <v>2</v>
-      </c>
       <c r="U222" s="1">
         <v>66</v>
       </c>
@@ -15365,9 +14915,6 @@
       <c r="S223" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T223" s="3">
-        <v>1</v>
-      </c>
       <c r="U223" s="1">
         <v>24</v>
       </c>
@@ -15415,9 +14962,6 @@
       <c r="S224" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T224" s="3">
-        <v>3</v>
-      </c>
       <c r="U224" s="1">
         <v>114</v>
       </c>
@@ -15465,9 +15009,6 @@
       <c r="S225" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T225" s="3">
-        <v>3</v>
-      </c>
       <c r="U225" s="1">
         <v>145</v>
       </c>
@@ -15515,9 +15056,6 @@
       <c r="S226" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T226" s="3">
-        <v>3</v>
-      </c>
       <c r="U226" s="1">
         <v>174</v>
       </c>
@@ -15565,9 +15103,6 @@
       <c r="S227" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T227" s="3">
-        <v>3</v>
-      </c>
       <c r="U227" s="1">
         <v>203</v>
       </c>
@@ -15618,9 +15153,6 @@
       <c r="R228" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T228" s="3">
-        <v>2</v>
-      </c>
       <c r="U228" s="1">
         <v>78</v>
       </c>
@@ -15724,9 +15256,6 @@
       <c r="S230" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T230" s="3">
-        <v>1</v>
-      </c>
       <c r="U230" s="1">
         <v>33</v>
       </c>
@@ -15774,9 +15303,6 @@
       <c r="S231" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T231" s="3">
-        <v>2</v>
-      </c>
       <c r="U231" s="1">
         <v>76</v>
       </c>
@@ -15824,9 +15350,6 @@
       <c r="S232" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T232" s="3">
-        <v>3</v>
-      </c>
       <c r="U232" s="1">
         <v>107</v>
       </c>
@@ -15874,9 +15397,6 @@
       <c r="S233" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T233" s="3">
-        <v>3</v>
-      </c>
       <c r="U233" s="1">
         <v>142</v>
       </c>
@@ -15924,9 +15444,6 @@
       <c r="S234" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="T234" s="3">
-        <v>3</v>
-      </c>
       <c r="U234" s="1">
         <v>171</v>
       </c>
@@ -15973,9 +15490,6 @@
       </c>
       <c r="S235" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="T235" s="3">
-        <v>3</v>
       </c>
       <c r="U235" s="1">
         <v>200</v>
@@ -16070,9 +15584,6 @@
       <c r="S237" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T237" s="3">
-        <v>3</v>
-      </c>
       <c r="U237" s="1">
         <v>103</v>
       </c>
@@ -16120,9 +15631,6 @@
       <c r="S238" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T238" s="3">
-        <v>3</v>
-      </c>
       <c r="U238" s="1">
         <v>137</v>
       </c>
@@ -16170,9 +15678,6 @@
       <c r="S239" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="T239" s="3">
-        <v>3</v>
-      </c>
       <c r="U239" s="1">
         <v>166</v>
       </c>
@@ -16219,9 +15724,6 @@
       </c>
       <c r="S240" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="T240" s="3">
-        <v>3</v>
       </c>
       <c r="U240" s="1">
         <v>195</v>
@@ -16314,9 +15816,6 @@
       <c r="S242" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="T242" s="3">
-        <v>1</v>
-      </c>
       <c r="U242" s="1">
         <v>22</v>
       </c>
@@ -16364,9 +15863,6 @@
       <c r="S243" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="T243" s="3">
-        <v>3</v>
-      </c>
       <c r="U243" s="1">
         <v>110</v>
       </c>
@@ -16414,9 +15910,6 @@
       <c r="S244" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="T244" s="3">
-        <v>3</v>
-      </c>
       <c r="U244" s="1">
         <v>144</v>
       </c>
@@ -16464,9 +15957,6 @@
       <c r="S245" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="T245" s="3">
-        <v>3</v>
-      </c>
       <c r="U245" s="1">
         <v>173</v>
       </c>
@@ -16514,9 +16004,6 @@
       <c r="S246" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="T246" s="3">
-        <v>3</v>
-      </c>
       <c r="U246" s="1">
         <v>202</v>
       </c>
@@ -16564,9 +16051,6 @@
       <c r="S247" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="T247" s="3">
-        <v>2</v>
-      </c>
       <c r="U247" s="1">
         <v>75</v>
       </c>
@@ -16613,9 +16097,6 @@
       </c>
       <c r="S248" s="3" t="s">
         <v>569</v>
-      </c>
-      <c r="T248" s="3">
-        <v>1</v>
       </c>
       <c r="U248" s="1">
         <v>45</v>
@@ -16756,9 +16237,6 @@
       <c r="S251" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="T251" s="3">
-        <v>1</v>
-      </c>
       <c r="U251" s="1">
         <v>47</v>
       </c>
@@ -16806,9 +16284,6 @@
       <c r="S252" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="T252" s="3">
-        <v>3</v>
-      </c>
       <c r="U252" s="1">
         <v>113</v>
       </c>
@@ -16856,9 +16331,6 @@
       <c r="S253" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="T253" s="3">
-        <v>3</v>
-      </c>
       <c r="U253" s="1">
         <v>108</v>
       </c>
@@ -16905,9 +16377,6 @@
       </c>
       <c r="S254" s="3" t="s">
         <v>652</v>
-      </c>
-      <c r="T254" s="3">
-        <v>2</v>
       </c>
       <c r="U254" s="1">
         <v>68</v>

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04D3F37-EE28-4455-A146-C639E414BC9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06FFBDC-DF63-4A6B-A1C5-A1535145DDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="599">
   <si>
     <t>Image</t>
   </si>
@@ -646,24 +646,15 @@
     <t>Ca' Rezzonico</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/76/Marly_horse_Louvre_MR1802.jpg/1280px-Marly_horse_Louvre_MR1802.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Guillaume</t>
   </si>
   <si>
     <t>COUSTOU L'ANCIEN</t>
   </si>
   <si>
-    <t>1677</t>
-  </si>
-  <si>
     <t>1746</t>
   </si>
   <si>
-    <t>1739-1745</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/53/Vulcan_Coustou_Louvre_MR1814.jpg/960px-Vulcan_Coustou_Louvre_MR1814.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -1012,9 +1003,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/d/d0/Rome_basilica_st_peter_015.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=fr</t>
   </si>
   <si>
-    <t>Michel-Ange</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/8/83/La_Seine_et_la_Marne_MR1801.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
@@ -1123,9 +1111,6 @@
     <t>Sanmartino</t>
   </si>
   <si>
-    <t>Nef</t>
-  </si>
-  <si>
     <t>Le Christ voilé</t>
   </si>
   <si>
@@ -1135,9 +1120,6 @@
     <t>L'Amour se faisant un arc de la massue d'Hercule</t>
   </si>
   <si>
-    <t>Galerie</t>
-  </si>
-  <si>
     <t>Pigalle</t>
   </si>
   <si>
@@ -1162,18 +1144,6 @@
     <t>Britannique</t>
   </si>
   <si>
-    <t>Nollekens</t>
-  </si>
-  <si>
-    <t>Buste de Laurence Sterne</t>
-  </si>
-  <si>
-    <t>Bust of Laurence Sterne</t>
-  </si>
-  <si>
-    <t>Musée</t>
-  </si>
-  <si>
     <t>Allemande</t>
   </si>
   <si>
@@ -1186,9 +1156,6 @@
     <t>Bois peint et doré</t>
   </si>
   <si>
-    <t>Niche centrale</t>
-  </si>
-  <si>
     <t>Slodtz</t>
   </si>
   <si>
@@ -1270,9 +1237,6 @@
     <t>L'Enfant à la cage</t>
   </si>
   <si>
-    <t>San Pietro</t>
-  </si>
-  <si>
     <t>1795-1805</t>
   </si>
   <si>
@@ -1303,9 +1267,6 @@
     <t>Musées du Vatican</t>
   </si>
   <si>
-    <t>Musée Chiaramonti</t>
-  </si>
-  <si>
     <t>Persée tenant la tête de Méduse</t>
   </si>
   <si>
@@ -1363,21 +1324,12 @@
     <t>Schutzengelgruppe</t>
   </si>
   <si>
-    <t>Église des Girolamini</t>
-  </si>
-  <si>
-    <t>Statue de Saint Pierre</t>
-  </si>
-  <si>
     <t>Parme</t>
   </si>
   <si>
     <t>Galleria Nazionale di Parma</t>
   </si>
   <si>
-    <t>Salle principale</t>
-  </si>
-  <si>
     <t>Marie-Louise d'Autriche en Concorde</t>
   </si>
   <si>
@@ -1390,9 +1342,6 @@
     <t>Musée archéologique national</t>
   </si>
   <si>
-    <t>Galerie des sculptures</t>
-  </si>
-  <si>
     <t>Ferdinand IV en Minerve</t>
   </si>
   <si>
@@ -1420,21 +1369,6 @@
     <t>Blaise Pascal</t>
   </si>
   <si>
-    <t>Statue de Saint Bruno</t>
-  </si>
-  <si>
-    <t>Barletta</t>
-  </si>
-  <si>
-    <t>Église du Saint-Sépulcre</t>
-  </si>
-  <si>
-    <t>Le Christ mort</t>
-  </si>
-  <si>
-    <t>Cristo morto</t>
-  </si>
-  <si>
     <t>Classement Gemini /200</t>
   </si>
   <si>
@@ -1513,9 +1447,6 @@
     <t>La Seine et la Marne</t>
   </si>
   <si>
-    <t>Cheval retenu par un palefrenier (Chevaux de Marly)</t>
-  </si>
-  <si>
     <t>Vulcain</t>
   </si>
   <si>
@@ -1549,9 +1480,6 @@
     <t>Satyre et Bacchante</t>
   </si>
   <si>
-    <t>Jean-Jacques Rousseau, drapé à l’antique, livre, enfant, nu.</t>
-  </si>
-  <si>
     <t>Sainte Barbe</t>
   </si>
   <si>
@@ -1646,13 +1574,256 @@
   </si>
   <si>
     <t>Michel</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Louvre_biscuit.jpg/960px-Louvre_biscuit.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Boizot</t>
+  </si>
+  <si>
+    <t>La Beauté couronnée par les Grâces</t>
+  </si>
+  <si>
+    <t>La Beauté couronnée</t>
+  </si>
+  <si>
+    <t>Biscuit de porcelaine</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b6/Buste_de_Louis_XVI_-_Le_Petit_Trianon.jpg/960px-Buste_de_Louis_XVI_-_Le_Petit_Trianon.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Château de Fontainebleau</t>
+  </si>
+  <si>
+    <t>Petit Trianon</t>
+  </si>
+  <si>
+    <t>Buste de Louis XVI</t>
+  </si>
+  <si>
+    <t>Louis XVI</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c6/Marly_horse_Louvre_MR1803.jpg/960px-Marly_horse_Louvre_MR1803.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1743-1745</t>
+  </si>
+  <si>
+    <t>Cour Marly</t>
+  </si>
+  <si>
+    <t>Les Chevaux de Marly</t>
+  </si>
+  <si>
+    <t>Chevaux de Marly</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2a/Versalles_Fuente_de_Neptuno_01.JPG/1280px-Versalles_Fuente_de_Neptuno_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bassin de Neptune</t>
+  </si>
+  <si>
+    <t>René-Michel</t>
+  </si>
+  <si>
+    <t>dit Michel-Ange Slodtz</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/40/Virginia_State_Capitol_complex_-_Houdon%27s_Washington%2C_seen_from_the_front.jpg/960px-Virginia_State_Capitol_complex_-_Houdon%27s_Washington%2C_seen_from_the_front.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Richmond</t>
+  </si>
+  <si>
+    <t>Capitole de l'État de Virginie</t>
+  </si>
+  <si>
+    <t>Statue de George Washington</t>
+  </si>
+  <si>
+    <t>George Washington</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a9/Benjamin_Franklin_by_Jean-Antoine_Houdon_Louvre_RF349_%28001%29.jpg/960px-Benjamin_Franklin_by_Jean-Antoine_Houdon_Louvre_RF349_%28001%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Buste de Benjamin Franklin</t>
+  </si>
+  <si>
+    <t>Benjamin Franklin</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Jean_Jacques_Rousseau_-_Jean-Antoine_Houdon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_1729_-_photo_2.jpg/960px-Jean_Jacques_Rousseau_-_Jean-Antoine_Houdon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_1729_-_photo_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Buste de Jean-Jacques Rousseau</t>
+  </si>
+  <si>
+    <t>Jean-Jacques Rousseau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bronze </t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>Neptune et Amphitrite</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Bordeaux_-_Grand_Theatre_de_Bordeaux.jpg/1280px-Bordeaux_-_Grand_Theatre_de_Bordeaux.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Berruer</t>
+  </si>
+  <si>
+    <t>Bordeaux</t>
+  </si>
+  <si>
+    <t>Grand Théâtre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Façade </t>
+  </si>
+  <si>
+    <t>Les Neuf Muses et Trois Déesses</t>
+  </si>
+  <si>
+    <t>Les Muses</t>
+  </si>
+  <si>
+    <t>Pierre calcaire</t>
+  </si>
+  <si>
+    <t>ttps://thumb.wikimedia.org/wikipedia/commons/thumb/2/20/Thetis_and_Achilles%2C_V%26A_London_02.jpg/1280px-Thetis_and_Achilles%2C_V%26A_London_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>Thetis plongeant Achille dans le Styx</t>
+  </si>
+  <si>
+    <t>Thetis Dipping Achilles in the River Styx</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/80/Somerset_House-Strand-Statue_Of_George_III_%26_Neptune.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Bacon</t>
+  </si>
+  <si>
+    <t>Somerset House</t>
+  </si>
+  <si>
+    <t>Cour d'honneur</t>
+  </si>
+  <si>
+    <t>George III et l'allégorie de la Tamise</t>
+  </si>
+  <si>
+    <t>George III and the River Thames</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/24/Monument_to_William_Pitt%2C_Earl_of_Chatham%2C_Westminster_Abbey_02.jpg/1280px-Monument_to_William_Pitt%2C_Earl_of_Chatham%2C_Westminster_Abbey_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Tombeau de William Pitt, comte de Chatham</t>
+  </si>
+  <si>
+    <t>Monument to William Pitt</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Samuel_Johnson_statue%2C_St_Paul%27s_Cathedral.jpg/960px-Samuel_Johnson_statue%2C_St_Paul%27s_Cathedral.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Cathédrale Saint-Paul</t>
+  </si>
+  <si>
+    <t>Monument à Samuel Johnson</t>
+  </si>
+  <si>
+    <t>Monument to Samuel Johnson</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/81/Berlin_%285595857760%29.jpg/960px-Berlin_%285595857760%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Andreas</t>
+  </si>
+  <si>
+    <t>Schlüter</t>
+  </si>
+  <si>
+    <t>Château de Charlottenburg</t>
+  </si>
+  <si>
+    <t>Statue équestre du Grand Électeur</t>
+  </si>
+  <si>
+    <t>Reiterstandbild des Großen Kurfürsten</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Allegoria_San_Lorenzo_%28Agrigento%29_20_02_2016_04.jpg/960px-Allegoria_San_Lorenzo_%28Agrigento%29_20_02_2016_04.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Giacomo</t>
+  </si>
+  <si>
+    <t>Serpotta</t>
+  </si>
+  <si>
+    <t>Palerme</t>
+  </si>
+  <si>
+    <t>Oratoire de San Domenico</t>
+  </si>
+  <si>
+    <t>L'Allégorie de la Simplicité</t>
+  </si>
+  <si>
+    <t>La Prudenza</t>
+  </si>
+  <si>
+    <t>Stuc</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/c/ce/OSL_%28Palermo%29_16_07_2019_13.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>1710-1717</t>
+  </si>
+  <si>
+    <t>Oratoire de San Lorenzo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les Vertus </t>
+  </si>
+  <si>
+    <t>Le Virtù</t>
+  </si>
+  <si>
+    <t>Stuc (Gesso)</t>
+  </si>
+  <si>
+    <t>Grès</t>
+  </si>
+  <si>
+    <t>Jean-Jacques Rousseau observant les premiers pas de l'enfance, ou l'éducation d'Emile</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1701,8 +1872,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF202122"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1730,6 +1907,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1762,7 +1945,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1795,6 +1978,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2098,14 +2302,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U79"/>
+  <dimension ref="A1:W88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" style="9" customWidth="1"/>
     <col min="3" max="3" width="18" style="9" customWidth="1"/>
-    <col min="4" max="4" width="6" style="9" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" style="3" customWidth="1"/>
+    <col min="4" max="5" width="6" style="9" customWidth="1"/>
     <col min="6" max="6" width="9.85546875" style="3" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="3" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" style="3" customWidth="1"/>
@@ -2121,6 +2324,7 @@
     <col min="19" max="19" width="12.7109375" style="3" customWidth="1"/>
     <col min="20" max="20" width="6.85546875" style="3" customWidth="1"/>
     <col min="21" max="21" width="14.42578125" style="3" customWidth="1"/>
+    <col min="23" max="23" width="9.140625" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2185,19 +2389,19 @@
         <v>19</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>471</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="9" t="s">
-        <v>540</v>
+        <v>516</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>541</v>
+        <v>517</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="F2" s="3">
         <v>1738</v>
@@ -2215,10 +2419,10 @@
         <v>35</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>90</v>
@@ -2233,7 +2437,7 @@
         <v>22</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="T2" s="3">
         <v>1</v>
@@ -2269,7 +2473,7 @@
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="8" t="s">
-        <v>524</v>
+        <v>500</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
@@ -2288,10 +2492,10 @@
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>160</v>
@@ -2299,13 +2503,13 @@
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>34</v>
@@ -2315,7 +2519,7 @@
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="8" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
@@ -2333,73 +2537,75 @@
       </c>
     </row>
     <row r="5" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="8" t="s">
-        <v>486</v>
-      </c>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T5" s="5">
+      <c r="A5" s="14" t="s">
+        <v>533</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1759</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1740</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>550</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="P5" s="3">
+        <v>320</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>540</v>
+      </c>
+      <c r="R5" s="3">
+        <v>280</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="T5" s="3">
         <v>1</v>
+      </c>
+      <c r="U5" s="1">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>74</v>
+        <v>332</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>75</v>
+        <v>333</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>34</v>
@@ -2409,7 +2615,7 @@
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="8" t="s">
-        <v>532</v>
+        <v>464</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
@@ -2417,7 +2623,7 @@
         <v>28</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>80</v>
+        <v>279</v>
       </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
@@ -2430,325 +2636,344 @@
     </row>
     <row r="7" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>103</v>
+        <v>34</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>386</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="K7" s="5"/>
       <c r="L7" s="8" t="s">
-        <v>396</v>
+        <v>508</v>
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="P7" s="5"/>
+        <v>28</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="T7" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>346</v>
+      <c r="A8" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>347</v>
+        <v>99</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>348</v>
+        <v>100</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5" t="s">
-        <v>334</v>
+        <v>101</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>349</v>
+        <v>61</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>287</v>
+        <v>102</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="5"/>
+        <v>104</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>376</v>
+      </c>
       <c r="L8" s="8" t="s">
-        <v>487</v>
+        <v>385</v>
       </c>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
       <c r="O8" s="5" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="T8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>564</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3">
+        <v>1740</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1799</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1786</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>568</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="P9" s="3">
+        <v>280</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>350</v>
+      </c>
+      <c r="R9" s="3">
+        <v>210</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="T9" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="5" t="s">
+      <c r="U9" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3">
+        <v>1740</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1799</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1795</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="O10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T9" s="5">
+      <c r="P10" s="3">
+        <v>210</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>95</v>
+      </c>
+      <c r="R10" s="3">
+        <v>85</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="T10" s="3">
+        <v>3</v>
+      </c>
+      <c r="U10" s="1">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>570</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3">
+        <v>1740</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1799</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1784</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="3">
+        <v>750</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>420</v>
+      </c>
+      <c r="R11" s="3">
+        <v>280</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="T11" s="3">
+        <v>3</v>
+      </c>
+      <c r="U11" s="1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>559</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1735</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1805</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1790</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>562</v>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="T12" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" s="5"/>
-      <c r="L10" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T10" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="T11" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="K12" s="5"/>
-      <c r="L12" s="8" t="s">
-        <v>490</v>
-      </c>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="T12" s="5">
-        <v>2</v>
-      </c>
+      <c r="U12" s="20"/>
     </row>
     <row r="13" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>244</v>
+      <c r="A13" s="10" t="s">
+        <v>342</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>245</v>
+        <v>343</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>246</v>
+        <v>344</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5" t="s">
-        <v>25</v>
+        <v>330</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>247</v>
+        <v>345</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>249</v>
+        <v>34</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>250</v>
+        <v>35</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="8" t="s">
-        <v>491</v>
+        <v>465</v>
       </c>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="P13" s="5" t="s">
-        <v>251</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
       <c r="S13" s="5" t="s">
@@ -2759,434 +2984,395 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>30</v>
+      <c r="A14" s="14" t="s">
+        <v>551</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>31</v>
+        <v>343</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>357</v>
+        <v>552</v>
       </c>
       <c r="F14" s="3">
-        <v>1757</v>
+        <v>1733</v>
       </c>
       <c r="G14" s="3">
-        <v>1822</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>33</v>
+        <v>1807</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1773</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>34</v>
+        <v>553</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>35</v>
+        <v>554</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>555</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>358</v>
+        <v>556</v>
       </c>
       <c r="N14" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>28</v>
+        <v>557</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>558</v>
       </c>
       <c r="P14" s="3">
-        <v>155</v>
+        <v>230</v>
       </c>
       <c r="Q14" s="3">
-        <v>168</v>
+        <v>85</v>
       </c>
       <c r="R14" s="3">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="T14" s="3">
         <v>1</v>
       </c>
       <c r="U14" s="1">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1757</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1822</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>402</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="O15" s="3" t="s">
+      <c r="A15" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="5"/>
+      <c r="L15" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P15" s="3">
-        <v>540</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>480</v>
-      </c>
-      <c r="R15" s="3">
-        <v>290</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="T15" s="5">
         <v>2</v>
       </c>
-      <c r="U15" s="1">
-        <v>56</v>
-      </c>
     </row>
     <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>473</v>
+      <c r="A16" s="14" t="s">
+        <v>518</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>31</v>
+        <v>307</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>357</v>
+        <v>519</v>
       </c>
       <c r="F16" s="3">
-        <v>1757</v>
+        <v>1743</v>
       </c>
       <c r="G16" s="3">
-        <v>1822</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>186</v>
+        <v>1809</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1773</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>419</v>
+        <v>35</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>420</v>
+        <v>520</v>
       </c>
       <c r="N16" s="9" t="s">
-        <v>421</v>
+        <v>521</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>28</v>
+        <v>522</v>
       </c>
       <c r="P16" s="3">
-        <v>345</v>
+        <v>48</v>
       </c>
       <c r="Q16" s="3">
-        <v>150</v>
+        <v>32</v>
       </c>
       <c r="R16" s="3">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="T16" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U16" s="1">
-        <v>91</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>474</v>
+      <c r="A17" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>31</v>
+        <v>307</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>357</v>
+        <v>519</v>
       </c>
       <c r="F17" s="3">
-        <v>1757</v>
+        <v>1743</v>
       </c>
       <c r="G17" s="3">
-        <v>1822</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>53</v>
+        <v>1809</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1777</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>423</v>
+        <v>524</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>367</v>
+        <v>525</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>424</v>
+        <v>526</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>425</v>
+        <v>527</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>28</v>
       </c>
       <c r="P17" s="3">
-        <v>590</v>
+        <v>82</v>
       </c>
       <c r="Q17" s="3">
-        <v>450</v>
+        <v>65</v>
       </c>
       <c r="R17" s="3">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="T17" s="3">
         <v>3</v>
       </c>
       <c r="U17" s="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>475</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1757</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1822</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1790</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J18" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="L18" s="11" t="s">
-        <v>428</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="O18" s="3" t="s">
+      <c r="B18" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" s="5"/>
+      <c r="L18" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P18" s="3">
-        <v>220</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>110</v>
-      </c>
-      <c r="R18" s="3">
-        <v>95</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="T18" s="3">
-        <v>3</v>
-      </c>
-      <c r="U18" s="1">
-        <v>93</v>
+      <c r="P18" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="T18" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="F19" s="3">
-        <v>1757</v>
-      </c>
-      <c r="G19" s="3">
-        <v>1822</v>
-      </c>
-      <c r="H19" s="3">
-        <v>1796</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="L19" s="11" t="s">
-        <v>452</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>453</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P19" s="3">
-        <v>135</v>
-      </c>
-      <c r="Q19" s="3">
-        <v>110</v>
-      </c>
-      <c r="R19" s="3">
-        <v>95</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="T19" s="3">
-        <v>3</v>
-      </c>
-      <c r="U19" s="1">
-        <v>130</v>
+      <c r="A19" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="K19" s="5"/>
+      <c r="L19" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="T19" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>477</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1757</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1822</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>455</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="L20" s="11" t="s">
-        <v>457</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>458</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P20" s="3">
-        <v>290</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>140</v>
-      </c>
-      <c r="R20" s="3">
-        <v>125</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="T20" s="3">
-        <v>3</v>
-      </c>
-      <c r="U20" s="1">
-        <v>131</v>
+      <c r="A20" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="K20" s="5"/>
+      <c r="L20" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="P20" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="T20" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>312</v>
+        <v>241</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>313</v>
+        <v>242</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>314</v>
+        <v>243</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>79</v>
+        <v>244</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>192</v>
+        <v>245</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>315</v>
+        <v>246</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>316</v>
+        <v>247</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="8" t="s">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
       <c r="O21" s="5" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>317</v>
+        <v>248</v>
       </c>
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
       <c r="S21" s="5" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="T21" s="5">
         <v>2</v>
@@ -3194,419 +3380,467 @@
     </row>
     <row r="22" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="H22" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1757</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1822</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P22" s="3">
+        <v>155</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>168</v>
+      </c>
+      <c r="R22" s="3">
+        <v>101</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="T22" s="3">
+        <v>1</v>
+      </c>
+      <c r="U22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1757</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1822</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P23" s="3">
+        <v>540</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>480</v>
+      </c>
+      <c r="R23" s="3">
+        <v>290</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="T23" s="3">
+        <v>2</v>
+      </c>
+      <c r="U23" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="F24" s="3">
+        <v>1757</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1822</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P24" s="3">
+        <v>345</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>150</v>
+      </c>
+      <c r="R24" s="3">
         <v>110</v>
       </c>
-      <c r="I22" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="K22" s="5"/>
-      <c r="L22" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T22" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="S24" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="T24" s="3">
+        <v>3</v>
+      </c>
+      <c r="U24" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1757</v>
+      </c>
+      <c r="G25" s="3">
+        <v>1822</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P25" s="3">
+        <v>590</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>450</v>
+      </c>
+      <c r="R25" s="3">
+        <v>210</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="T25" s="3">
+        <v>3</v>
+      </c>
+      <c r="U25" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1757</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1822</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1790</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P26" s="3">
+        <v>220</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>110</v>
+      </c>
+      <c r="R26" s="3">
+        <v>95</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="T26" s="3">
+        <v>3</v>
+      </c>
+      <c r="U26" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1757</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1822</v>
+      </c>
+      <c r="H27" s="3">
+        <v>1796</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P27" s="3">
+        <v>135</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>110</v>
+      </c>
+      <c r="R27" s="3">
+        <v>95</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="T27" s="3">
+        <v>3</v>
+      </c>
+      <c r="U27" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1757</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1822</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P28" s="3">
+        <v>290</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>140</v>
+      </c>
+      <c r="R28" s="3">
         <v>125</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="K23" s="5"/>
-      <c r="L23" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T23" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K24" s="5"/>
-      <c r="L24" s="8" t="s">
-        <v>495</v>
-      </c>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T24" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K25" s="5"/>
-      <c r="L25" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="O25" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P25" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T25" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K26" s="5"/>
-      <c r="L26" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T26" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K27" s="5"/>
-      <c r="L27" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T27" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K28" s="5"/>
-      <c r="L28" s="8" t="s">
-        <v>498</v>
-      </c>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T28" s="5">
-        <v>2</v>
+      <c r="S28" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="T28" s="3">
+        <v>3</v>
+      </c>
+      <c r="U28" s="1">
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>122</v>
+        <v>309</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>123</v>
+        <v>310</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>124</v>
+        <v>311</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>127</v>
+        <v>312</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>128</v>
+        <v>313</v>
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="8" t="s">
-        <v>499</v>
+        <v>470</v>
       </c>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
       <c r="O29" s="5" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="P29" s="5" t="s">
-        <v>55</v>
+        <v>314</v>
       </c>
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
       <c r="S29" s="5" t="s">
-        <v>29</v>
+        <v>147</v>
       </c>
       <c r="T29" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>174</v>
+        <v>290</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>175</v>
+        <v>291</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>176</v>
+        <v>292</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>178</v>
+        <v>293</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>179</v>
+        <v>110</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K30" s="5"/>
       <c r="L30" s="8" t="s">
-        <v>500</v>
+        <v>471</v>
       </c>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
       <c r="O30" s="5" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
       <c r="S30" s="5" t="s">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="T30" s="5">
         <v>2</v>
@@ -3614,281 +3848,283 @@
     </row>
     <row r="31" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5" t="s">
-        <v>341</v>
+        <v>162</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>39</v>
+        <v>318</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>342</v>
+        <v>125</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>343</v>
+        <v>62</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>344</v>
+        <v>247</v>
       </c>
       <c r="K31" s="5"/>
       <c r="L31" s="8" t="s">
-        <v>529</v>
+        <v>472</v>
       </c>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
       <c r="O31" s="5" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="P31" s="5"/>
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
       <c r="S31" s="5" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="T31" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>71</v>
+        <v>25</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="K32" s="5"/>
       <c r="L32" s="8" t="s">
-        <v>501</v>
+        <v>473</v>
       </c>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
       <c r="O32" s="5" t="s">
-        <v>113</v>
+        <v>28</v>
       </c>
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
       <c r="S32" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="T32" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1696</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1770</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="L33" s="11" t="s">
-        <v>528</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="P33" s="3">
-        <v>85</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>45</v>
-      </c>
-      <c r="R33" s="3">
-        <v>35</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="T33" s="3">
-        <v>3</v>
-      </c>
-      <c r="U33" s="1">
-        <v>111</v>
+        <v>36</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="K33" s="5"/>
+      <c r="L33" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="T33" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>266</v>
+        <v>327</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>267</v>
+        <v>328</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>268</v>
+        <v>329</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5" t="s">
-        <v>269</v>
+        <v>68</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>237</v>
+        <v>330</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>234</v>
+        <v>331</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>270</v>
+        <v>34</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>271</v>
+        <v>35</v>
       </c>
       <c r="K34" s="5"/>
       <c r="L34" s="8" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
       <c r="O34" s="5" t="s">
-        <v>272</v>
+        <v>28</v>
       </c>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
       <c r="R34" s="5"/>
       <c r="S34" s="5" t="s">
-        <v>273</v>
+        <v>46</v>
       </c>
       <c r="T34" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>182</v>
+      <c r="A35" s="14" t="s">
+        <v>528</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>208</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="K35" s="5"/>
-      <c r="L35" s="8" t="s">
-        <v>503</v>
-      </c>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="P35" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q35" s="5"/>
-      <c r="R35" s="5"/>
-      <c r="S35" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T35" s="5">
-        <v>2</v>
+        <v>209</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1677</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1746</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>531</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P35" s="3">
+        <v>340</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>284</v>
+      </c>
+      <c r="R35" s="3">
+        <v>127</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="T35" s="3">
+        <v>1</v>
+      </c>
+      <c r="U35" s="1">
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>57</v>
+      <c r="A36" s="14" t="s">
+        <v>211</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>58</v>
+        <v>208</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="8" t="s">
-        <v>504</v>
+        <v>475</v>
       </c>
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
       <c r="O36" s="5" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
@@ -3902,358 +4138,330 @@
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="F37" s="3">
-        <v>1725</v>
-      </c>
-      <c r="G37" s="3">
-        <v>1775</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="L37" s="11" t="s">
-        <v>445</v>
-      </c>
-      <c r="N37" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="P37" s="3">
-        <v>182</v>
-      </c>
-      <c r="Q37" s="3">
+        <v>122</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="R37" s="3">
-        <v>75</v>
-      </c>
-      <c r="S37" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="T37" s="3">
-        <v>3</v>
-      </c>
-      <c r="U37" s="1">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G37" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="K37" s="5"/>
+      <c r="L37" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P37" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="T37" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="F38" s="3">
-        <v>1741</v>
-      </c>
-      <c r="G38" s="3">
-        <v>1828</v>
-      </c>
-      <c r="H38" s="3">
-        <v>1778</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="L38" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="N38" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P38" s="3">
-        <v>138</v>
-      </c>
-      <c r="Q38" s="3">
-        <v>90</v>
-      </c>
-      <c r="R38" s="3">
-        <v>100</v>
-      </c>
-      <c r="S38" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="T38" s="3">
-        <v>1</v>
-      </c>
-      <c r="U38" s="1">
+        <v>174</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="K38" s="5"/>
+      <c r="L38" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="T38" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="F39" s="3">
-        <v>1731</v>
-      </c>
-      <c r="G39" s="3">
-        <v>1804</v>
-      </c>
-      <c r="H39" s="3">
-        <v>1787</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="L39" s="11" t="s">
-        <v>408</v>
-      </c>
-      <c r="N39" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P39" s="3">
-        <v>145</v>
-      </c>
-      <c r="Q39" s="3">
-        <v>115</v>
-      </c>
-      <c r="R39" s="3">
-        <v>80</v>
-      </c>
-      <c r="S39" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="T39" s="3">
-        <v>1</v>
-      </c>
-      <c r="U39" s="1">
-        <v>59</v>
+      <c r="A39" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="K39" s="5"/>
+      <c r="L39" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="M39" s="8"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="T39" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="F40" s="3">
-        <v>1706</v>
-      </c>
-      <c r="G40" s="3">
-        <v>1775</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="L40" s="11" t="s">
-        <v>525</v>
-      </c>
-      <c r="N40" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="P40" s="3">
-        <v>45</v>
-      </c>
-      <c r="Q40" s="3">
-        <v>38</v>
-      </c>
-      <c r="R40" s="3">
-        <v>38</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="T40" s="3">
-        <v>3</v>
-      </c>
-      <c r="U40" s="1">
+        <v>106</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5" t="s">
         <v>109</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="K40" s="5"/>
+      <c r="L40" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="T40" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="K41" s="5"/>
-      <c r="L41" s="8" t="s">
-        <v>505</v>
-      </c>
-      <c r="M41" s="6"/>
-      <c r="N41" s="6"/>
-      <c r="O41" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="5"/>
-      <c r="S41" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T41" s="5">
-        <v>1</v>
+        <v>288</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1696</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1770</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="N41" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="P41" s="3">
+        <v>85</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>45</v>
+      </c>
+      <c r="R41" s="3">
+        <v>35</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="T41" s="3">
+        <v>3</v>
+      </c>
+      <c r="U41" s="1">
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>227</v>
+        <v>264</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>138</v>
+        <v>266</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="I42" s="5"/>
+        <v>231</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>267</v>
+      </c>
       <c r="J42" s="5" t="s">
-        <v>231</v>
+        <v>268</v>
       </c>
       <c r="K42" s="5"/>
       <c r="L42" s="8" t="s">
-        <v>506</v>
+        <v>479</v>
       </c>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
       <c r="O42" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P42" s="5" t="s">
-        <v>232</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="P42" s="5"/>
       <c r="Q42" s="5"/>
       <c r="R42" s="5"/>
       <c r="S42" s="5" t="s">
-        <v>46</v>
+        <v>270</v>
       </c>
       <c r="T42" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>182</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>27</v>
+        <v>187</v>
       </c>
       <c r="K43" s="5"/>
       <c r="L43" s="8" t="s">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
       <c r="O43" s="5" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="P43" s="5" t="s">
-        <v>55</v>
+        <v>188</v>
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="5"/>
@@ -4266,945 +4474,927 @@
     </row>
     <row r="44" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>164</v>
+        <v>57</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>166</v>
+        <v>59</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>167</v>
+        <v>60</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>143</v>
+        <v>32</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>168</v>
+        <v>61</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>170</v>
+        <v>63</v>
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="M44" s="8" t="s">
-        <v>527</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="P44" s="5" t="s">
-        <v>172</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="P44" s="5"/>
       <c r="Q44" s="5"/>
       <c r="R44" s="5"/>
       <c r="S44" s="5" t="s">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="T44" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K45" s="5"/>
-      <c r="L45" s="8" t="s">
-        <v>508</v>
-      </c>
-      <c r="M45" s="6"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="P45" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q45" s="5"/>
-      <c r="R45" s="5"/>
-      <c r="S45" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T45" s="5">
-        <v>1</v>
+      <c r="A45" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1725</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1775</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="N45" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="P45" s="3">
+        <v>182</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>95</v>
+      </c>
+      <c r="R45" s="3">
+        <v>75</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="T45" s="3">
+        <v>3</v>
+      </c>
+      <c r="U45" s="1">
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="I46" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="F46" s="3">
+        <v>1741</v>
+      </c>
+      <c r="G46" s="3">
+        <v>1828</v>
+      </c>
+      <c r="H46" s="3">
+        <v>1778</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J46" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="K46" s="5"/>
-      <c r="L46" s="8" t="s">
-        <v>509</v>
-      </c>
-      <c r="M46" s="6"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="5" t="s">
+      <c r="J46" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="N46" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="O46" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="5"/>
-      <c r="R46" s="5"/>
-      <c r="S46" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T46" s="5">
+      <c r="P46" s="3">
+        <v>138</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>90</v>
+      </c>
+      <c r="R46" s="3">
+        <v>100</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="T46" s="3">
+        <v>1</v>
+      </c>
+      <c r="U46" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="I47" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="J47" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="K47" s="5"/>
-      <c r="L47" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
-      <c r="O47" s="5" t="s">
+      <c r="A47" s="14" t="s">
+        <v>537</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1741</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1828</v>
+      </c>
+      <c r="H47" s="3">
+        <v>1788</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="N47" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="O47" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="P47" s="5" t="s">
+      <c r="P47" s="3">
+        <v>203</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>105</v>
+      </c>
+      <c r="R47" s="3">
+        <v>90</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="T47" s="3">
+        <v>2</v>
+      </c>
+      <c r="U47" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1741</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1828</v>
+      </c>
+      <c r="H48" s="3">
+        <v>1778</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>543</v>
+      </c>
+      <c r="N48" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P48" s="3">
+        <v>53</v>
+      </c>
+      <c r="Q48" s="3">
         <v>42</v>
       </c>
-      <c r="Q47" s="5"/>
-      <c r="R47" s="5"/>
-      <c r="S47" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T47" s="5">
+      <c r="R48" s="3">
+        <v>28</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="T48" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="48" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="K48" s="5"/>
-      <c r="L48" s="8" t="s">
-        <v>511</v>
-      </c>
-      <c r="M48" s="6"/>
-      <c r="N48" s="6"/>
-      <c r="O48" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P48" s="5"/>
-      <c r="Q48" s="5"/>
-      <c r="R48" s="5"/>
-      <c r="S48" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="T48" s="5">
+      <c r="U48" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
+        <v>545</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1741</v>
+      </c>
+      <c r="G49" s="3">
+        <v>1828</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1781</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="N49" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="P49" s="3">
+        <v>51</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>30</v>
+      </c>
+      <c r="R49" s="3">
+        <v>25</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="T49" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="49" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="J49" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="K49" s="5"/>
-      <c r="L49" s="8" t="s">
-        <v>512</v>
-      </c>
-      <c r="M49" s="6"/>
-      <c r="N49" s="6"/>
-      <c r="O49" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P49" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="Q49" s="5"/>
-      <c r="R49" s="5"/>
-      <c r="S49" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="T49" s="5">
-        <v>1</v>
+      <c r="U49" s="1">
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="12"/>
+      <c r="A50" s="2" t="s">
+        <v>341</v>
+      </c>
       <c r="B50" s="9" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F50" s="3">
-        <v>1737</v>
+        <v>1731</v>
       </c>
       <c r="G50" s="3">
-        <v>1823</v>
+        <v>1804</v>
       </c>
       <c r="H50" s="3">
-        <v>1773</v>
+        <v>1787</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>186</v>
+        <v>395</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>187</v>
+        <v>396</v>
       </c>
       <c r="L50" s="11" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="N50" s="9" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="O50" s="3" t="s">
         <v>28</v>
       </c>
       <c r="P50" s="3">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="Q50" s="3">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="R50" s="3">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="T50" s="3">
         <v>1</v>
       </c>
       <c r="U50" s="1">
-        <v>17</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="10" t="s">
-        <v>43</v>
+      <c r="A51" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>44</v>
+        <v>262</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>376</v>
+        <v>419</v>
       </c>
       <c r="F51" s="3">
-        <v>1730</v>
+        <v>1706</v>
       </c>
       <c r="G51" s="3">
-        <v>1809</v>
-      </c>
-      <c r="H51" s="3">
-        <v>1783</v>
+        <v>1775</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>420</v>
       </c>
       <c r="I51" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="N51" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="P51" s="3">
+        <v>45</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>38</v>
+      </c>
+      <c r="R51" s="3">
+        <v>38</v>
+      </c>
+      <c r="S51" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="T51" s="3">
+        <v>3</v>
+      </c>
+      <c r="U51" s="1">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="I52" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J51" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L51" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="N51" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="O51" s="3" t="s">
+      <c r="J52" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="K52" s="5"/>
+      <c r="L52" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="M52" s="6"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="5"/>
+      <c r="R52" s="5"/>
+      <c r="S52" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="T52" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="K53" s="5"/>
+      <c r="L53" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+      <c r="O53" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P51" s="3">
-        <v>178</v>
-      </c>
-      <c r="Q51" s="3">
-        <v>86</v>
-      </c>
-      <c r="R51" s="3">
-        <v>82</v>
-      </c>
-      <c r="S51" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="T51" s="3">
+      <c r="P53" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q53" s="5"/>
+      <c r="R53" s="5"/>
+      <c r="S53" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="T53" s="5">
         <v>1</v>
       </c>
-      <c r="U51" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="10" t="s">
-        <v>478</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1730</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1809</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1773</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="J52" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="L52" s="11" t="s">
-        <v>404</v>
-      </c>
-      <c r="N52" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="O52" s="3" t="s">
+    </row>
+    <row r="54" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K54" s="5"/>
+      <c r="L54" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="M54" s="6"/>
+      <c r="N54" s="6"/>
+      <c r="O54" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P52" s="3">
-        <v>60</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>45</v>
-      </c>
-      <c r="R52" s="3">
-        <v>32</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="T52" s="3">
+      <c r="P54" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q54" s="5"/>
+      <c r="R54" s="5"/>
+      <c r="S54" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="T54" s="5">
         <v>2</v>
-      </c>
-      <c r="U52" s="1">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="F53" s="3">
-        <v>1730</v>
-      </c>
-      <c r="G53" s="3">
-        <v>1809</v>
-      </c>
-      <c r="H53" s="3">
-        <v>1775</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J53" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L53" s="11" t="s">
-        <v>430</v>
-      </c>
-      <c r="N53" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="O53" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P53" s="3">
-        <v>75</v>
-      </c>
-      <c r="Q53" s="3">
-        <v>50</v>
-      </c>
-      <c r="R53" s="3">
-        <v>45</v>
-      </c>
-      <c r="S53" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="T53" s="3">
-        <v>2</v>
-      </c>
-      <c r="U53" s="1">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
-        <v>482</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="F54" s="3">
-        <v>1730</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1809</v>
-      </c>
-      <c r="H54" s="3">
-        <v>1769</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J54" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L54" s="11" t="s">
-        <v>464</v>
-      </c>
-      <c r="N54" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P54" s="3">
-        <v>76</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>54</v>
-      </c>
-      <c r="R54" s="3">
-        <v>45</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="T54" s="3">
-        <v>3</v>
-      </c>
-      <c r="U54" s="1">
-        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>47</v>
+        <v>164</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>49</v>
+        <v>166</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5" t="s">
-        <v>50</v>
+        <v>167</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>52</v>
+        <v>168</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>53</v>
+        <v>169</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="K55" s="5"/>
       <c r="L55" s="8" t="s">
-        <v>513</v>
-      </c>
-      <c r="M55" s="6"/>
+        <v>502</v>
+      </c>
+      <c r="M55" s="8" t="s">
+        <v>503</v>
+      </c>
       <c r="N55" s="6"/>
       <c r="O55" s="5" t="s">
-        <v>28</v>
+        <v>171</v>
       </c>
       <c r="P55" s="5" t="s">
-        <v>55</v>
+        <v>172</v>
       </c>
       <c r="Q55" s="5"/>
       <c r="R55" s="5"/>
       <c r="S55" s="5" t="s">
-        <v>56</v>
+        <v>173</v>
       </c>
       <c r="T55" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="F56" s="3">
-        <v>1714</v>
-      </c>
-      <c r="G56" s="3">
-        <v>1785</v>
-      </c>
-      <c r="H56" s="3">
-        <v>1744</v>
-      </c>
-      <c r="I56" s="3" t="s">
+      <c r="A56" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K56" s="5"/>
+      <c r="L56" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="M56" s="6"/>
+      <c r="N56" s="6"/>
+      <c r="O56" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="P56" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q56" s="5"/>
+      <c r="R56" s="5"/>
+      <c r="S56" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="T56" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="I57" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J56" s="9" t="s">
+      <c r="J57" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="K57" s="5"/>
+      <c r="L57" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="M57" s="8"/>
+      <c r="N57" s="8"/>
+      <c r="O57" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="P57" s="5"/>
+      <c r="Q57" s="5"/>
+      <c r="R57" s="5"/>
+      <c r="S57" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="T57" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="K58" s="5"/>
+      <c r="L58" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="M58" s="6"/>
+      <c r="N58" s="6"/>
+      <c r="O58" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q58" s="5"/>
+      <c r="R58" s="5"/>
+      <c r="S58" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="T58" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="K59" s="5"/>
+      <c r="L59" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="M59" s="6"/>
+      <c r="N59" s="6"/>
+      <c r="O59" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="5"/>
+      <c r="R59" s="5"/>
+      <c r="S59" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="T59" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="K60" s="5"/>
+      <c r="L60" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+      <c r="O60" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P60" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q60" s="5"/>
+      <c r="R60" s="5"/>
+      <c r="S60" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="T60" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="F61" s="3">
+        <v>1730</v>
+      </c>
+      <c r="G61" s="3">
+        <v>1809</v>
+      </c>
+      <c r="H61" s="3">
+        <v>1783</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J61" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="L56" s="11" t="s">
-        <v>373</v>
-      </c>
-      <c r="N56" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="O56" s="3" t="s">
+      <c r="L61" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="N61" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="O61" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="P56" s="3">
-        <v>58</v>
-      </c>
-      <c r="Q56" s="3">
-        <v>35</v>
-      </c>
-      <c r="R56" s="3">
-        <v>38</v>
-      </c>
-      <c r="S56" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="T56" s="3">
-        <v>1</v>
-      </c>
-      <c r="U56" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="10" t="s">
-        <v>539</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1714</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1785</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="J57" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="L57" s="11" t="s">
-        <v>413</v>
-      </c>
-      <c r="N57" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="P57" s="3">
-        <v>610</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>480</v>
-      </c>
-      <c r="R57" s="3">
-        <v>280</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="T57" s="3">
-        <v>2</v>
-      </c>
-      <c r="U57" s="1">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="13" t="s">
-        <v>535</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1714</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1785</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1776</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J58" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L58" s="11" t="s">
-        <v>414</v>
-      </c>
-      <c r="N58" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P58" s="3">
-        <v>150</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>85</v>
-      </c>
-      <c r="R58" s="3">
-        <v>80</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="T58" s="3">
-        <v>2</v>
-      </c>
-      <c r="U58" s="1">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="59" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="10" t="s">
-        <v>534</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1714</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1785</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1759</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J59" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L59" s="11" t="s">
-        <v>415</v>
-      </c>
-      <c r="N59" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P59" s="3">
-        <v>48</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>32</v>
-      </c>
-      <c r="R59" s="3">
-        <v>30</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="T59" s="3">
-        <v>2</v>
-      </c>
-      <c r="U59" s="1">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="13" t="s">
-        <v>537</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="F60" s="3">
-        <v>1714</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1785</v>
-      </c>
-      <c r="H60" s="3">
-        <v>1770</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="J60" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="L60" s="11" t="s">
-        <v>538</v>
-      </c>
-      <c r="N60" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="P60" s="3">
-        <v>380</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>250</v>
-      </c>
-      <c r="R60" s="3">
-        <v>240</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="T60" s="3">
-        <v>3</v>
-      </c>
-      <c r="U60" s="1">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="61" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="F61" s="3">
-        <v>1704</v>
-      </c>
-      <c r="G61" s="3">
-        <v>1762</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J61" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L61" s="11" t="s">
-        <v>483</v>
-      </c>
-      <c r="N61" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="O61" s="3" t="s">
-        <v>400</v>
-      </c>
       <c r="P61" s="3">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="Q61" s="3">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="R61" s="3">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="T61" s="3">
         <v>1</v>
       </c>
       <c r="U61" s="1">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>307</v>
+      <c r="A62" s="10" t="s">
+        <v>456</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>308</v>
+        <v>44</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>392</v>
+        <v>370</v>
       </c>
       <c r="F62" s="3">
-        <v>1702</v>
+        <v>1730</v>
       </c>
       <c r="G62" s="3">
-        <v>1762</v>
+        <v>1809</v>
       </c>
       <c r="H62" s="3">
-        <v>1761</v>
+        <v>1773</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>186</v>
+        <v>457</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>289</v>
+        <v>458</v>
       </c>
       <c r="L62" s="11" t="s">
         <v>393</v>
@@ -5216,148 +5406,160 @@
         <v>28</v>
       </c>
       <c r="P62" s="3">
-        <v>245</v>
+        <v>60</v>
       </c>
       <c r="Q62" s="3">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="R62" s="3">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="T62" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U62" s="1">
-        <v>31</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="J63" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="K63" s="5"/>
-      <c r="L63" s="8" t="s">
-        <v>514</v>
-      </c>
-      <c r="M63" s="6"/>
-      <c r="N63" s="6"/>
-      <c r="O63" s="5" t="s">
+      <c r="A63" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="F63" s="3">
+        <v>1730</v>
+      </c>
+      <c r="G63" s="3">
+        <v>1809</v>
+      </c>
+      <c r="H63" s="3">
+        <v>1775</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L63" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="N63" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="O63" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="P63" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q63" s="5"/>
-      <c r="R63" s="5"/>
-      <c r="S63" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T63" s="5">
+      <c r="P63" s="3">
+        <v>75</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>50</v>
+      </c>
+      <c r="R63" s="3">
+        <v>45</v>
+      </c>
+      <c r="S63" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="T63" s="3">
         <v>2</v>
       </c>
+      <c r="U63" s="1">
+        <v>99</v>
+      </c>
     </row>
     <row r="64" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="H64" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="I64" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="J64" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="K64" s="5"/>
-      <c r="L64" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="M64" s="6"/>
-      <c r="N64" s="6"/>
-      <c r="O64" s="5" t="s">
+      <c r="A64" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="F64" s="3">
+        <v>1730</v>
+      </c>
+      <c r="G64" s="3">
+        <v>1809</v>
+      </c>
+      <c r="H64" s="3">
+        <v>1769</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J64" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="N64" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="O64" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="P64" s="5"/>
-      <c r="Q64" s="5"/>
-      <c r="R64" s="5"/>
-      <c r="S64" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="T64" s="5">
-        <v>1</v>
+      <c r="P64" s="3">
+        <v>76</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>54</v>
+      </c>
+      <c r="R64" s="3">
+        <v>45</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="T64" s="3">
+        <v>3</v>
+      </c>
+      <c r="U64" s="1">
+        <v>163</v>
       </c>
     </row>
     <row r="65" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>218</v>
+      <c r="A65" s="16" t="s">
+        <v>47</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>219</v>
+        <v>48</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>220</v>
+        <v>49</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5" t="s">
-        <v>221</v>
+        <v>50</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>222</v>
+        <v>51</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>201</v>
+        <v>52</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="K65" s="5"/>
       <c r="L65" s="8" t="s">
-        <v>516</v>
+        <v>489</v>
       </c>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
@@ -5365,407 +5567,427 @@
         <v>28</v>
       </c>
       <c r="P65" s="5" t="s">
-        <v>223</v>
+        <v>55</v>
       </c>
       <c r="Q65" s="5"/>
       <c r="R65" s="5"/>
       <c r="S65" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="T65" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="I66" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K66" s="5"/>
-      <c r="L66" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="M66" s="6"/>
-      <c r="N66" s="6"/>
-      <c r="O66" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="P66" s="5"/>
-      <c r="Q66" s="5"/>
-      <c r="R66" s="5"/>
-      <c r="S66" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="T66" s="5">
-        <v>2</v>
+        <v>230</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="F66" s="3">
+        <v>1714</v>
+      </c>
+      <c r="G66" s="3">
+        <v>1785</v>
+      </c>
+      <c r="H66" s="3">
+        <v>1744</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J66" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="N66" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P66" s="3">
+        <v>58</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>35</v>
+      </c>
+      <c r="R66" s="3">
+        <v>38</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="T66" s="3">
+        <v>1</v>
+      </c>
+      <c r="U66" s="1">
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>199</v>
+      <c r="A67" s="10" t="s">
+        <v>515</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="C67" s="9" t="s">
         <v>366</v>
       </c>
       <c r="F67" s="3">
-        <v>1720</v>
+        <v>1714</v>
       </c>
       <c r="G67" s="3">
-        <v>1793</v>
-      </c>
-      <c r="H67" s="3">
-        <v>1753</v>
+        <v>1785</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>399</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>41</v>
+        <v>401</v>
       </c>
       <c r="L67" s="11" t="s">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>369</v>
+        <v>402</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>28</v>
+        <v>384</v>
       </c>
       <c r="P67" s="3">
-        <v>50</v>
+        <v>610</v>
       </c>
       <c r="Q67" s="3">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="R67" s="3">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="T67" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U67" s="1">
-        <v>3</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="12"/>
+      <c r="A68" s="13" t="s">
+        <v>511</v>
+      </c>
       <c r="B68" s="9" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>366</v>
       </c>
       <c r="F68" s="3">
-        <v>1720</v>
+        <v>1714</v>
       </c>
       <c r="G68" s="3">
-        <v>1793</v>
+        <v>1785</v>
       </c>
       <c r="H68" s="3">
-        <v>1757</v>
+        <v>1776</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>447</v>
+        <v>35</v>
       </c>
       <c r="L68" s="11" t="s">
-        <v>448</v>
+        <v>403</v>
       </c>
       <c r="N68" s="9" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="O68" s="3" t="s">
         <v>28</v>
       </c>
       <c r="P68" s="3">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="Q68" s="3">
+        <v>85</v>
+      </c>
+      <c r="R68" s="3">
         <v>80</v>
       </c>
-      <c r="R68" s="3">
-        <v>75</v>
-      </c>
       <c r="S68" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="T68" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U68" s="1">
-        <v>115</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>484</v>
+        <v>510</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="C69" s="9" t="s">
         <v>366</v>
       </c>
       <c r="F69" s="3">
-        <v>1720</v>
+        <v>1714</v>
       </c>
       <c r="G69" s="3">
-        <v>1793</v>
+        <v>1785</v>
       </c>
       <c r="H69" s="3">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>459</v>
+        <v>35</v>
       </c>
       <c r="L69" s="11" t="s">
-        <v>460</v>
+        <v>404</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>461</v>
+        <v>404</v>
       </c>
       <c r="O69" s="3" t="s">
         <v>28</v>
       </c>
       <c r="P69" s="3">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="Q69" s="3">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="R69" s="3">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="S69" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="T69" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U69" s="1">
-        <v>146</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="12"/>
+      <c r="A70" s="13" t="s">
+        <v>513</v>
+      </c>
       <c r="B70" s="9" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="C70" s="9" t="s">
         <v>366</v>
       </c>
       <c r="F70" s="3">
-        <v>1720</v>
+        <v>1714</v>
       </c>
       <c r="G70" s="3">
-        <v>1793</v>
+        <v>1785</v>
       </c>
       <c r="H70" s="3">
-        <v>1765</v>
+        <v>1770</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>40</v>
+        <v>512</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="L70" s="11" t="s">
-        <v>466</v>
+        <v>514</v>
       </c>
       <c r="N70" s="9" t="s">
-        <v>391</v>
+        <v>446</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="P70" s="3">
-        <v>215</v>
+        <v>380</v>
       </c>
       <c r="Q70" s="3">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="R70" s="3">
-        <v>75</v>
+        <v>240</v>
       </c>
       <c r="S70" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="T70" s="3">
         <v>3</v>
       </c>
       <c r="U70" s="1">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="71" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="12"/>
+      <c r="A71" s="15" t="s">
+        <v>136</v>
+      </c>
       <c r="B71" s="9" t="s">
-        <v>200</v>
+        <v>137</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="F71" s="3">
-        <v>1720</v>
+        <v>1704</v>
       </c>
       <c r="G71" s="3">
-        <v>1793</v>
-      </c>
-      <c r="H71" s="3">
-        <v>1770</v>
+        <v>1762</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>387</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>467</v>
+        <v>40</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>468</v>
+        <v>41</v>
       </c>
       <c r="L71" s="11" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>470</v>
+        <v>388</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>121</v>
+        <v>389</v>
       </c>
       <c r="P71" s="3">
-        <v>45</v>
+        <v>195</v>
       </c>
       <c r="Q71" s="3">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="R71" s="3">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="S71" s="3" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="T71" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U71" s="1">
-        <v>204</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="G72" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="H72" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="I72" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="J72" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="K72" s="5"/>
-      <c r="L72" s="8" t="s">
-        <v>518</v>
-      </c>
-      <c r="M72" s="6"/>
-      <c r="N72" s="6"/>
-      <c r="O72" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="F72" s="3">
+        <v>1702</v>
+      </c>
+      <c r="G72" s="3">
+        <v>1762</v>
+      </c>
+      <c r="H72" s="3">
+        <v>1761</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="J72" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="N72" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="O72" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="P72" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q72" s="5"/>
-      <c r="R72" s="5"/>
-      <c r="S72" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="T72" s="5">
+      <c r="P72" s="3">
+        <v>245</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>150</v>
+      </c>
+      <c r="R72" s="3">
+        <v>95</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="T72" s="3">
         <v>1</v>
+      </c>
+      <c r="U72" s="1">
+        <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
       <c r="F73" s="5" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="K73" s="5"/>
       <c r="L73" s="8" t="s">
-        <v>519</v>
+        <v>490</v>
       </c>
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
       <c r="O73" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P73" s="5"/>
+      <c r="P73" s="5" t="s">
+        <v>73</v>
+      </c>
       <c r="Q73" s="5"/>
       <c r="R73" s="5"/>
       <c r="S73" s="5" t="s">
@@ -5777,77 +5999,70 @@
     </row>
     <row r="74" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="F74" s="3">
-        <v>1705</v>
-      </c>
-      <c r="G74" s="3">
-        <v>1764</v>
-      </c>
-      <c r="H74" s="3">
-        <v>1750</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J74" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L74" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="N74" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="O74" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="J74" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="K74" s="5"/>
+      <c r="L74" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P74" s="3">
-        <v>450</v>
-      </c>
-      <c r="Q74" s="3">
-        <v>190</v>
-      </c>
-      <c r="R74" s="3">
-        <v>170</v>
-      </c>
-      <c r="S74" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="T74" s="3">
+      <c r="P74" s="5"/>
+      <c r="Q74" s="5"/>
+      <c r="R74" s="5"/>
+      <c r="S74" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="T74" s="5">
         <v>1</v>
-      </c>
-      <c r="U74" s="1">
-        <v>30</v>
       </c>
     </row>
     <row r="75" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
       <c r="F75" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>234</v>
+        <v>201</v>
       </c>
       <c r="I75" s="5" t="s">
         <v>34</v>
@@ -5857,14 +6072,16 @@
       </c>
       <c r="K75" s="5"/>
       <c r="L75" s="8" t="s">
-        <v>520</v>
+        <v>492</v>
       </c>
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
       <c r="O75" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P75" s="5"/>
+      <c r="P75" s="5" t="s">
+        <v>220</v>
+      </c>
       <c r="Q75" s="5"/>
       <c r="R75" s="5"/>
       <c r="S75" s="5" t="s">
@@ -5876,43 +6093,45 @@
     </row>
     <row r="76" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>257</v>
+        <v>139</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>258</v>
+        <v>140</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>259</v>
+        <v>141</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
       <c r="F76" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>260</v>
+        <v>143</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="I76" s="5"/>
+        <v>144</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>145</v>
+      </c>
       <c r="J76" s="5" t="s">
-        <v>262</v>
+        <v>146</v>
       </c>
       <c r="K76" s="5"/>
       <c r="L76" s="8" t="s">
-        <v>521</v>
+        <v>493</v>
       </c>
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
       <c r="O76" s="5" t="s">
-        <v>263</v>
+        <v>121</v>
       </c>
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
       <c r="R76" s="5"/>
       <c r="S76" s="5" t="s">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="T76" s="5">
         <v>2</v>
@@ -5920,124 +6139,645 @@
     </row>
     <row r="77" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="F77" s="3">
+        <v>1720</v>
+      </c>
+      <c r="G77" s="3">
+        <v>1793</v>
+      </c>
+      <c r="H77" s="3">
+        <v>1753</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J77" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P77" s="3">
+        <v>50</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>180</v>
+      </c>
+      <c r="R77" s="3">
+        <v>80</v>
+      </c>
+      <c r="S77" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="T77" s="3">
+        <v>1</v>
+      </c>
+      <c r="U77" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="F78" s="3">
+        <v>1720</v>
+      </c>
+      <c r="G78" s="3">
+        <v>1793</v>
+      </c>
+      <c r="H78" s="3">
+        <v>1760</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J78" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="N78" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P78" s="3">
+        <v>150</v>
+      </c>
+      <c r="Q78" s="3">
+        <v>110</v>
+      </c>
+      <c r="R78" s="3">
+        <v>85</v>
+      </c>
+      <c r="S78" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="T78" s="3">
+        <v>3</v>
+      </c>
+      <c r="U78" s="1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="K79" s="5"/>
+      <c r="L79" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="M79" s="6"/>
+      <c r="N79" s="6"/>
+      <c r="O79" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P79" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q79" s="5"/>
+      <c r="R79" s="5"/>
+      <c r="S79" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="T79" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="K80" s="5"/>
+      <c r="L80" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="M80" s="6"/>
+      <c r="N80" s="6"/>
+      <c r="O80" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P80" s="5"/>
+      <c r="Q80" s="5"/>
+      <c r="R80" s="5"/>
+      <c r="S80" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="T80" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="17" t="s">
+        <v>577</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3">
+        <v>1664</v>
+      </c>
+      <c r="G81" s="3">
+        <v>1714</v>
+      </c>
+      <c r="H81" s="3">
+        <v>1703</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J81" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="L81" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="N81" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="O81" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="P81" s="3">
+        <v>290</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>260</v>
+      </c>
+      <c r="R81" s="3">
+        <v>140</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="T81" s="3">
+        <v>1</v>
+      </c>
+      <c r="U81" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="17" t="s">
+        <v>583</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3">
+        <v>1656</v>
+      </c>
+      <c r="G82" s="3">
+        <v>1732</v>
+      </c>
+      <c r="H82" s="3">
+        <v>1702</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="J82" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="L82" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="N82" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="O82" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="P82" s="3">
+        <v>185</v>
+      </c>
+      <c r="Q82" s="3">
+        <v>72</v>
+      </c>
+      <c r="R82" s="3">
+        <v>50</v>
+      </c>
+      <c r="S82" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="T82" s="3">
+        <v>3</v>
+      </c>
+      <c r="U82" s="1">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="17" t="s">
+        <v>591</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3">
+        <v>1656</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1732</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="J83" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="L83" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="N83" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="O83" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="P83" s="3">
+        <v>180</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>70</v>
+      </c>
+      <c r="R83" s="3">
+        <v>50</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="T83" s="3">
+        <v>1</v>
+      </c>
+      <c r="U83" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="F84" s="3">
+        <v>1705</v>
+      </c>
+      <c r="G84" s="3">
+        <v>1764</v>
+      </c>
+      <c r="H84" s="3">
+        <v>1750</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L84" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="N84" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P84" s="3">
+        <v>450</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>190</v>
+      </c>
+      <c r="R84" s="3">
+        <v>170</v>
+      </c>
+      <c r="S84" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="T84" s="3">
+        <v>1</v>
+      </c>
+      <c r="U84" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K85" s="5"/>
+      <c r="L85" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="M85" s="6"/>
+      <c r="N85" s="6"/>
+      <c r="O85" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P85" s="5"/>
+      <c r="Q85" s="5"/>
+      <c r="R85" s="5"/>
+      <c r="S85" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="T85" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="H86" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="I86" s="5"/>
+      <c r="J86" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="K86" s="5"/>
+      <c r="L86" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="M86" s="6"/>
+      <c r="N86" s="6"/>
+      <c r="O86" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="P86" s="5"/>
+      <c r="Q86" s="5"/>
+      <c r="R86" s="5"/>
+      <c r="S86" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="T86" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B87" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C87" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5" t="s">
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="G77" s="5" t="s">
+      <c r="G87" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="H77" s="5" t="s">
+      <c r="H87" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="I77" s="5"/>
-      <c r="J77" s="5" t="s">
+      <c r="I87" s="5"/>
+      <c r="J87" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="K77" s="5"/>
-      <c r="L77" s="8" t="s">
-        <v>522</v>
-      </c>
-      <c r="M77" s="6"/>
-      <c r="N77" s="6"/>
-      <c r="O77" s="5" t="s">
+      <c r="K87" s="5"/>
+      <c r="L87" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="M87" s="6"/>
+      <c r="N87" s="6"/>
+      <c r="O87" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="P77" s="5"/>
-      <c r="Q77" s="5"/>
-      <c r="R77" s="5"/>
-      <c r="S77" s="5" t="s">
+      <c r="P87" s="5"/>
+      <c r="Q87" s="5"/>
+      <c r="R87" s="5"/>
+      <c r="S87" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="T77" s="5">
+      <c r="T87" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
+    <row r="88" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B88" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="C88" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5" t="s">
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="G78" s="5" t="s">
+      <c r="G88" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="H78" s="5" t="s">
+      <c r="H88" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="I78" s="5" t="s">
+      <c r="I88" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="J78" s="5" t="s">
+      <c r="J88" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="K78" s="5"/>
-      <c r="L78" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="M78" s="6"/>
-      <c r="N78" s="6"/>
-      <c r="O78" s="5" t="s">
+      <c r="K88" s="5"/>
+      <c r="L88" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="M88" s="6"/>
+      <c r="N88" s="6"/>
+      <c r="O88" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P78" s="5" t="s">
+      <c r="P88" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="Q78" s="5"/>
-      <c r="R78" s="5"/>
-      <c r="S78" s="5" t="s">
+      <c r="Q88" s="5"/>
+      <c r="R88" s="5"/>
+      <c r="S88" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="T78" s="5">
+      <c r="T88" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="T79" s="3">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V82">
-    <sortCondition ref="C2:C82"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V92">
+    <sortCondition ref="C2:C92"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A15" r:id="rId1" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/61/St._Peter%27s_Basilica%2C_Monument_to_Pope_Clement_XIII%2C_by_Antonio_Canova%2C_1792_%2848466617492%29.jpg/960px-St._Peter%27s_Basilica%2C_Monument_to_Pope_Clement_XIII%2C_by_Antonio_Canova%2C_1792_%2848466617492%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{97D8A985-25A8-42F5-AB91-4D34B8D2CF33}"/>
-    <hyperlink ref="A16" r:id="rId2" xr:uid="{0085B750-7165-450F-88C7-C7D74EDB91D2}"/>
-    <hyperlink ref="A17" r:id="rId3" xr:uid="{33115DFF-D6FB-432C-AC20-F8188FC4E845}"/>
-    <hyperlink ref="A18" r:id="rId4" xr:uid="{564A8E9E-A430-4CBD-A867-E8D70CC037F1}"/>
-    <hyperlink ref="A19" r:id="rId5" xr:uid="{47B832C3-5F1F-4664-A39C-56986DEA70FD}"/>
-    <hyperlink ref="A20" r:id="rId6" xr:uid="{6FD1AA65-A962-43F5-9AF8-2782EDB38C99}"/>
-    <hyperlink ref="A8" r:id="rId7" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/ba/Berruer_-_Louis_XV_r%C3%A9compense_la_Peinture_et_la_Sculpture_02.jpg/960px-Berruer_-_Louis_XV_r%C3%A9compense_la_Peinture_et_la_Sculpture_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AC674F25-B516-4210-95DB-2B9BE4FA03D2}"/>
-    <hyperlink ref="A51" r:id="rId8" xr:uid="{07F915D4-1271-41D4-946B-F8A031FBE0FC}"/>
-    <hyperlink ref="A52" r:id="rId9" xr:uid="{6FBBC01C-B5AB-47B6-AFFB-C034C73ABAF2}"/>
-    <hyperlink ref="A53" r:id="rId10" xr:uid="{B8014724-DB41-4117-B03C-CBCF522A04E9}"/>
-    <hyperlink ref="A54" r:id="rId11" xr:uid="{687283BF-7CF3-4ECD-8A40-2FC25BA8E62F}"/>
-    <hyperlink ref="A47" r:id="rId12" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a2/Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg/960px-Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B882B89E-D692-4561-81F4-F9B10455D101}"/>
-    <hyperlink ref="A69" r:id="rId13" xr:uid="{87C77131-7AF2-443C-BE39-DA2381CEF0F2}"/>
-    <hyperlink ref="A59" r:id="rId14" xr:uid="{3981DDB0-AD13-4258-B3E4-558F12031D35}"/>
-    <hyperlink ref="A58" r:id="rId15" xr:uid="{9DF373F2-F34B-4B78-8BB5-19096B52117F}"/>
-    <hyperlink ref="A60" r:id="rId16" xr:uid="{2C298685-B822-4549-8B8B-1A988CC9C92E}"/>
-    <hyperlink ref="A57" r:id="rId17" xr:uid="{F0E9C6C5-DC60-4097-B4E8-6A9CB090D986}"/>
-    <hyperlink ref="A45" r:id="rId18" xr:uid="{3152661E-E9C2-4110-A6F4-B0000F786A7C}"/>
+    <hyperlink ref="A23" r:id="rId1" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/61/St._Peter%27s_Basilica%2C_Monument_to_Pope_Clement_XIII%2C_by_Antonio_Canova%2C_1792_%2848466617492%29.jpg/960px-St._Peter%27s_Basilica%2C_Monument_to_Pope_Clement_XIII%2C_by_Antonio_Canova%2C_1792_%2848466617492%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{97D8A985-25A8-42F5-AB91-4D34B8D2CF33}"/>
+    <hyperlink ref="A24" r:id="rId2" xr:uid="{0085B750-7165-450F-88C7-C7D74EDB91D2}"/>
+    <hyperlink ref="A25" r:id="rId3" xr:uid="{33115DFF-D6FB-432C-AC20-F8188FC4E845}"/>
+    <hyperlink ref="A26" r:id="rId4" xr:uid="{564A8E9E-A430-4CBD-A867-E8D70CC037F1}"/>
+    <hyperlink ref="A27" r:id="rId5" xr:uid="{47B832C3-5F1F-4664-A39C-56986DEA70FD}"/>
+    <hyperlink ref="A28" r:id="rId6" xr:uid="{6FD1AA65-A962-43F5-9AF8-2782EDB38C99}"/>
+    <hyperlink ref="A13" r:id="rId7" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/ba/Berruer_-_Louis_XV_r%C3%A9compense_la_Peinture_et_la_Sculpture_02.jpg/960px-Berruer_-_Louis_XV_r%C3%A9compense_la_Peinture_et_la_Sculpture_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AC674F25-B516-4210-95DB-2B9BE4FA03D2}"/>
+    <hyperlink ref="A61" r:id="rId8" xr:uid="{07F915D4-1271-41D4-946B-F8A031FBE0FC}"/>
+    <hyperlink ref="A62" r:id="rId9" xr:uid="{6FBBC01C-B5AB-47B6-AFFB-C034C73ABAF2}"/>
+    <hyperlink ref="A63" r:id="rId10" xr:uid="{B8014724-DB41-4117-B03C-CBCF522A04E9}"/>
+    <hyperlink ref="A64" r:id="rId11" xr:uid="{687283BF-7CF3-4ECD-8A40-2FC25BA8E62F}"/>
+    <hyperlink ref="A58" r:id="rId12" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a2/Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg/960px-Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B882B89E-D692-4561-81F4-F9B10455D101}"/>
+    <hyperlink ref="A78" r:id="rId13" xr:uid="{87C77131-7AF2-443C-BE39-DA2381CEF0F2}"/>
+    <hyperlink ref="A69" r:id="rId14" xr:uid="{3981DDB0-AD13-4258-B3E4-558F12031D35}"/>
+    <hyperlink ref="A68" r:id="rId15" xr:uid="{9DF373F2-F34B-4B78-8BB5-19096B52117F}"/>
+    <hyperlink ref="A70" r:id="rId16" xr:uid="{2C298685-B822-4549-8B8B-1A988CC9C92E}"/>
+    <hyperlink ref="A67" r:id="rId17" xr:uid="{F0E9C6C5-DC60-4097-B4E8-6A9CB090D986}"/>
+    <hyperlink ref="A56" r:id="rId18" xr:uid="{3152661E-E9C2-4110-A6F4-B0000F786A7C}"/>
+    <hyperlink ref="A16" r:id="rId19" xr:uid="{4B5C2BA1-F0E7-45E3-85F5-52FACA51AEEC}"/>
+    <hyperlink ref="A17" r:id="rId20" xr:uid="{E36BBF0A-FDD1-4E1F-B6AF-52B26008603D}"/>
+    <hyperlink ref="A35" r:id="rId21" xr:uid="{12BC5328-FD5C-46EE-BBFA-CC32724C1FF9}"/>
+    <hyperlink ref="A36" r:id="rId22" xr:uid="{59DAD066-FC37-40D1-AE3B-24B67C5BA5DB}"/>
+    <hyperlink ref="A71" r:id="rId23" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Francesco_Queirolo_-_Il_Disinganno_%281753-54%29_-_Detail.jpg/1280px-Francesco_Queirolo_-_Il_Disinganno_%281753-54%29_-_Detail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{E164A41D-A597-4071-A821-F2A3C24D3F2C}"/>
+    <hyperlink ref="A47" r:id="rId24" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/40/Virginia_State_Capitol_complex_-_Houdon%27s_Washington%2C_seen_from_the_front.jpg/960px-Virginia_State_Capitol_complex_-_Houdon%27s_Washington%2C_seen_from_the_front.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7D07FDBD-D83E-44FD-9843-724946F8CF2E}"/>
+    <hyperlink ref="A48" r:id="rId25" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a9/Benjamin_Franklin_by_Jean-Antoine_Houdon_Louvre_RF349_%28001%29.jpg/960px-Benjamin_Franklin_by_Jean-Antoine_Houdon_Louvre_RF349_%28001%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{02EF6FBA-1D59-44C1-81B9-9E02FBFCA15E}"/>
+    <hyperlink ref="A49" r:id="rId26" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Jean_Jacques_Rousseau_-_Jean-Antoine_Houdon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_1729_-_photo_2.jpg/960px-Jean_Jacques_Rousseau_-_Jean-Antoine_Houdon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_1729_-_photo_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{891A227E-7E17-4543-A86F-E151DEDE309A}"/>
+    <hyperlink ref="A65" r:id="rId27" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/WA1216_99_Lower_Belvedere_Apotheosis_of_Prince_Eugene_of_Savoy_3D.jpg/1280px-WA1216_99_Lower_Belvedere_Apotheosis_of_Prince_Eugene_of_Savoy_3D.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{64E12365-8F6F-4867-9D1F-F6D484E30252}"/>
+    <hyperlink ref="A5" r:id="rId28" xr:uid="{D7C82055-C52E-45AE-9DBA-19B870EA7238}"/>
+    <hyperlink ref="A14" r:id="rId29" xr:uid="{92F5F847-C929-46B0-B7D5-EABFBD5C1062}"/>
+    <hyperlink ref="A12" r:id="rId30" xr:uid="{B840ECC2-059E-4FB4-9C95-020AF3A34BFC}"/>
+    <hyperlink ref="A9" r:id="rId31" xr:uid="{BD82F391-08E2-4580-9316-5F6036E48C50}"/>
+    <hyperlink ref="A11" r:id="rId32" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/24/Monument_to_William_Pitt%2C_Earl_of_Chatham%2C_Westminster_Abbey_02.jpg/1280px-Monument_to_William_Pitt%2C_Earl_of_Chatham%2C_Westminster_Abbey_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{090DEA6E-279F-4E35-9453-E91299BE8DB1}"/>
+    <hyperlink ref="A10" r:id="rId33" xr:uid="{D556DA19-547A-422C-8D59-F79689BBC3AD}"/>
+    <hyperlink ref="A81" r:id="rId34" xr:uid="{DF772C01-846B-46CB-BBB5-54B3A39DFA21}"/>
+    <hyperlink ref="A82" r:id="rId35" xr:uid="{86F08EE4-9192-45E7-B96F-AA2CFF20DED3}"/>
+    <hyperlink ref="A83" r:id="rId36" xr:uid="{DF13CE7F-4EE7-4AC2-911A-28AC8D58DC65}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5382CA-FD74-4CA1-AA2C-67EDCDB269F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B293C7C5-5F0B-4DA1-9A10-A18DD10F4C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="684">
   <si>
     <t>Image</t>
   </si>
@@ -161,9 +161,6 @@
     <t>Chapelle Sansevero</t>
   </si>
   <si>
-    <t>c.180 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Psyche_Abandoned_LACMA_M.76.78.jpg/1280px-Psyche_Abandoned_LACMA_M.76.78.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -254,9 +251,6 @@
     <t>Musée de l'Ermitage</t>
   </si>
   <si>
-    <t>c.250 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Bather_Allegrain_Louvre_MR1747.jpg/1280px-Bather_Allegrain_Louvre_MR1747.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -302,15 +296,9 @@
     <t>New York</t>
   </si>
   <si>
-    <t>Collection privée / Metropolitan Museum of Art</t>
-  </si>
-  <si>
     <t>Terre cuite</t>
   </si>
   <si>
-    <t>c.34 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Louvre_amour_arc_mr1761.jpg/960px-Louvre_amour_arc_mr1761.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -488,9 +476,6 @@
     <t>Porcelaine</t>
   </si>
   <si>
-    <t>c.20 cm</t>
-  </si>
-  <si>
     <t>suisse</t>
   </si>
   <si>
@@ -533,12 +518,6 @@
     <t>Musée des Beaux Arts</t>
   </si>
   <si>
-    <t>Alliage plomb-étain</t>
-  </si>
-  <si>
-    <t>c.40 cm</t>
-  </si>
-  <si>
     <t>autrichienne</t>
   </si>
   <si>
@@ -575,9 +554,6 @@
     <t>Victoria and Albert Museum</t>
   </si>
   <si>
-    <t>c.60 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/da/2016_-_Statues_in_Saint_Peter%27s_Basilica_08.jpg/960px-2016_-_Statues_in_Saint_Peter%27s_Basilica_08.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -665,9 +641,6 @@
     <t>1776</t>
   </si>
   <si>
-    <t>c.100 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Jean-Antoine_Houdon%2C_voltaire%2C_1781.JPG/1280px-Jean-Antoine_Houdon%2C_voltaire%2C_1781.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -692,9 +665,6 @@
     <t>Château de Versailles</t>
   </si>
   <si>
-    <t>c.80 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/88/Mercury_Pigalle_Louvre_RF3023.jpg/960px-Mercury_Pigalle_Louvre_RF3023.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -749,9 +719,6 @@
     <t>Musée des Beaux-Arts</t>
   </si>
   <si>
-    <t>c.50 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7a/Grabmal_der_Liebe2.jpg/1280px-Grabmal_der_Liebe2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -845,9 +812,6 @@
     <t>172 cm</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8e/Detail_of_Newton_monument%2C_Westminster_Abbey.jpg/1280px-Detail_of_Newton_monument%2C_Westminster_Abbey.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>John Michael</t>
   </si>
   <si>
@@ -902,9 +866,6 @@
     <t>National Portrait Gallery</t>
   </si>
   <si>
-    <t>c.70 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/93/Adam_-_Neptune_calmant_les_flots_01.jpg/1280px-Adam_-_Neptune_calmant_les_flots_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -947,9 +908,6 @@
     <t>Museo Nacional de Escultura</t>
   </si>
   <si>
-    <t>c.170 cm</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Buste_d%27Etienne_Falconet_par_Marie-Anne_Collot.jpg/1280px-Buste_d%27Etienne_Falconet_par_Marie-Anne_Collot.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1580,9 +1538,6 @@
     <t>Pierre calcaire</t>
   </si>
   <si>
-    <t>ttps://thumb.wikimedia.org/wikipedia/commons/thumb/2/20/Thetis_and_Achilles%2C_V%26A_London_02.jpg/1280px-Thetis_and_Achilles%2C_V%26A_London_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
-  </si>
-  <si>
     <t>Thomas</t>
   </si>
   <si>
@@ -1944,6 +1899,192 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/%C3%89glise_Saint-Sulpice_de_Paris_Monument_Jean-Baptiste_Languet_de_Gergy.jpg/1280px-%C3%89glise_Saint-Sulpice_de_Paris_Monument_Jean-Baptiste_Languet_de_Gergy.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/21/Thetis_dipping_Achilles_into_the_River_Styx_%2849219058951%29.jpg/1280px-Thetis_dipping_Achilles_into_the_River_Styx_%2849219058951%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>c, 1200</t>
+  </si>
+  <si>
+    <t>Grès de Bohême</t>
+  </si>
+  <si>
+    <t>c,320 cm</t>
+  </si>
+  <si>
+    <t>Grès de Saxe</t>
+  </si>
+  <si>
+    <t>Etain</t>
+  </si>
+  <si>
+    <t>Metropolitan Museum of Art</t>
+  </si>
+  <si>
+    <t>Grès gris</t>
+  </si>
+  <si>
+    <t>c.400</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/12/Tumba_de_Isaac_Newton_-_panoramio_%28cropped%29.jpg/960px-Tumba_de_Isaac_Newton_-_panoramio_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Chartres_-_Cath%C3%A9drale_Notre-Dame_-_L%27Assomption_%28Charles-Antoine_Bridan%29.jpg/960px-Chartres_-_Cath%C3%A9drale_Notre-Dame_-_L%27Assomption_%28Charles-Antoine_Bridan%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Charles-Antoine</t>
+  </si>
+  <si>
+    <t>BRIDAN</t>
+  </si>
+  <si>
+    <t>Chartres</t>
+  </si>
+  <si>
+    <t>Cathédrale Notre-Dame</t>
+  </si>
+  <si>
+    <t>Un Fleuve</t>
+  </si>
+  <si>
+    <t>FOUCOU</t>
+  </si>
+  <si>
+    <t>Jean-Joseph</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Foucou_-_Un_fleuve_01.jpg/1280px-Foucou_-_Un_fleuve_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>L'Amour menaçant</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e8/L%27Amour_mena%C3%A7ant_%28Louvre%2C_RF_296%29.jpg/960px-L%27Amour_mena%C3%A7ant_%28Louvre%2C_RF_296%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>La Baigneuse</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_177.JPG/960px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_177.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Il giudizio di Paride</t>
+  </si>
+  <si>
+    <t>Le Jugement de Pâris</t>
+  </si>
+  <si>
+    <t>Musée de Capodimonte</t>
+  </si>
+  <si>
+    <t>TAGLIOLINI</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/e/ec/Julgamento-de-p%C3%A1ris.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4b/Bruxelles_Palais_de_la_Nation_01.jpg/1280px-Bruxelles_Palais_de_la_Nation_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Gilles-Lambert</t>
+  </si>
+  <si>
+    <t>GODECHARLE</t>
+  </si>
+  <si>
+    <t>Bruxelles</t>
+  </si>
+  <si>
+    <t>Palais de la Nation</t>
+  </si>
+  <si>
+    <t>Fronton</t>
+  </si>
+  <si>
+    <t>La Justice récompensant les Vertus</t>
+  </si>
+  <si>
+    <t>Belge</t>
+  </si>
+  <si>
+    <t>Hercule assis</t>
+  </si>
+  <si>
+    <t>Section 18e</t>
+  </si>
+  <si>
+    <t>Musées royaux des Beaux-Arts</t>
+  </si>
+  <si>
+    <t>DELVAUX</t>
+  </si>
+  <si>
+    <t>Laurent</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/Laurent_Delvaux%2C_Resting_Hercules_2.jpg/960px-Laurent_Delvaux%2C_Resting_Hercules_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Flamande</t>
+  </si>
+  <si>
+    <t>Büste von Moses Mendelssohn</t>
+  </si>
+  <si>
+    <t>Buste de Moïse Mendelssohn</t>
+  </si>
+  <si>
+    <t>Bodemuzeum</t>
+  </si>
+  <si>
+    <t>TASSAERT</t>
+  </si>
+  <si>
+    <t>Jean-Pierre-Antoine</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Bust_of_Moses_Mendelssohn_by_Jean-Pierre-Antoine_Tassaert.jpg/500px-Bust_of_Moses_Mendelssohn_by_Jean-Pierre-Antoine_Tassaert.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Statue of Edward VI</t>
+  </si>
+  <si>
+    <t>Statue d'Edward VI</t>
+  </si>
+  <si>
+    <t>Thomas's Hospital</t>
+  </si>
+  <si>
+    <t>QUELLINUS III</t>
+  </si>
+  <si>
+    <t>Artus</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/87/Edward_VI_statue.JPG/960px-Edward_VI_statue.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/65/Antwerp%2C_Cath%C3%A9drale_Notre-Dame_20.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Michiel</t>
+  </si>
+  <si>
+    <t>VAN DER VOORT LE VIEUX</t>
+  </si>
+  <si>
+    <t>Anvers</t>
+  </si>
+  <si>
+    <t>Chaire de vérité</t>
+  </si>
+  <si>
+    <t>Preekstoel</t>
+  </si>
+  <si>
+    <t>Bois de chêne</t>
   </si>
 </sst>
 </file>
@@ -2443,7 +2584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W100"/>
+  <dimension ref="A1:W110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="2" customWidth="1"/>
@@ -2531,48 +2672,54 @@
         <v>19</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="8" t="s">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
       <c r="O2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
+      <c r="P2" s="5">
+        <v>187</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>82</v>
+      </c>
+      <c r="R2" s="5">
+        <v>53</v>
+      </c>
       <c r="S2" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T2" s="5">
         <v>2</v>
@@ -2580,24 +2727,24 @@
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>34</v>
@@ -2607,18 +2754,24 @@
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="8" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
+      <c r="P3" s="5">
+        <v>85</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>59</v>
+      </c>
+      <c r="R3" s="5">
+        <v>48</v>
+      </c>
       <c r="S3" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T3" s="5">
         <v>1</v>
@@ -2626,13 +2779,13 @@
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F4" s="3">
         <v>1700</v>
@@ -2644,16 +2797,16 @@
         <v>1740</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="P4" s="3">
         <v>320</v>
@@ -2665,7 +2818,7 @@
         <v>280</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="T4" s="3">
         <v>1</v>
@@ -2675,25 +2828,25 @@
       </c>
     </row>
     <row r="5" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>322</v>
+      <c r="A5" s="14" t="s">
+        <v>308</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>34</v>
@@ -2703,20 +2856,24 @@
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="8" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P5" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
+      <c r="P5" s="5">
+        <v>114</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>82.5</v>
+      </c>
+      <c r="R5" s="5">
+        <v>48</v>
+      </c>
       <c r="S5" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T5" s="5">
         <v>1</v>
@@ -2724,24 +2881,24 @@
     </row>
     <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>76</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>79</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>34</v>
@@ -2751,7 +2908,7 @@
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="8" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
@@ -2759,12 +2916,16 @@
         <v>28</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
+        <v>78</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>62</v>
+      </c>
+      <c r="R6" s="5">
+        <v>67.5</v>
+      </c>
       <c r="S6" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T6" s="5">
         <v>1</v>
@@ -2772,47 +2933,49 @@
     </row>
     <row r="7" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="P7" s="5"/>
+        <v>99</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>623</v>
+      </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T7" s="5">
         <v>1</v>
@@ -2820,13 +2983,13 @@
     </row>
     <row r="8" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3">
@@ -2839,22 +3002,22 @@
         <v>1786</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="P8" s="3">
         <v>280</v>
@@ -2866,7 +3029,7 @@
         <v>210</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="T8" s="3">
         <v>2</v>
@@ -2877,13 +3040,13 @@
     </row>
     <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3">
@@ -2896,16 +3059,16 @@
         <v>1795</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="N9" s="9" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>28</v>
@@ -2920,7 +3083,7 @@
         <v>85</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="T9" s="3">
         <v>3</v>
@@ -2931,13 +3094,13 @@
     </row>
     <row r="10" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3">
@@ -2950,16 +3113,16 @@
         <v>1784</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="O10" s="9" t="s">
         <v>28</v>
@@ -2974,7 +3137,7 @@
         <v>280</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="T10" s="3">
         <v>3</v>
@@ -2985,13 +3148,13 @@
     </row>
     <row r="11" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>515</v>
+        <v>622</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>569</v>
+        <v>554</v>
       </c>
       <c r="F11" s="3">
         <v>1735</v>
@@ -3003,22 +3166,31 @@
         <v>1790</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="N11" s="25" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>28</v>
       </c>
+      <c r="P11" s="3">
+        <v>84</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>100</v>
+      </c>
+      <c r="R11" s="3">
+        <v>56</v>
+      </c>
       <c r="S11" s="3" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="T11" s="3">
         <v>2</v>
@@ -3027,24 +3199,24 @@
     </row>
     <row r="12" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>34</v>
@@ -3054,7 +3226,7 @@
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="8" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="M12" s="6"/>
       <c r="N12" s="26"/>
@@ -3071,7 +3243,7 @@
         <v>9</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T12" s="5">
         <v>2</v>
@@ -3079,13 +3251,13 @@
     </row>
     <row r="13" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="F13" s="3">
         <v>1733</v>
@@ -3097,19 +3269,19 @@
         <v>1773</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="P13" s="3">
         <v>230</v>
@@ -3121,7 +3293,7 @@
         <v>80</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="T13" s="3">
         <v>1</v>
@@ -3131,25 +3303,25 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>296</v>
+      <c r="A14" s="14" t="s">
+        <v>283</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>34</v>
@@ -3159,18 +3331,24 @@
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="8" t="s">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
+      <c r="P14" s="5">
+        <v>79</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>50</v>
+      </c>
+      <c r="R14" s="5">
+        <v>27</v>
+      </c>
       <c r="S14" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T14" s="5">
         <v>2</v>
@@ -3178,13 +3356,13 @@
     </row>
     <row r="15" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="F15" s="3">
         <v>1743</v>
@@ -3202,10 +3380,10 @@
         <v>35</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="P15" s="3">
         <v>48</v>
@@ -3217,7 +3395,7 @@
         <v>25</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="T15" s="3">
         <v>2</v>
@@ -3228,13 +3406,13 @@
     </row>
     <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="F16" s="3">
         <v>1743</v>
@@ -3246,13 +3424,13 @@
         <v>1777</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="O16" s="9" t="s">
         <v>28</v>
@@ -3267,7 +3445,7 @@
         <v>45</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="T16" s="3">
         <v>3</v>
@@ -3278,13 +3456,13 @@
     </row>
     <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>557</v>
+        <v>542</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3">
@@ -3303,10 +3481,10 @@
         <v>35</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>558</v>
+        <v>543</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>28</v>
@@ -3321,7 +3499,7 @@
         <v>75</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="T17" s="3">
         <v>1</v>
@@ -3332,13 +3510,13 @@
     </row>
     <row r="18" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>557</v>
+        <v>542</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3">
@@ -3357,10 +3535,10 @@
         <v>35</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="O18" s="9" t="s">
         <v>28</v>
@@ -3375,7 +3553,7 @@
         <v>119</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="T18" s="3">
         <v>3</v>
@@ -3386,13 +3564,13 @@
     </row>
     <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>557</v>
+        <v>542</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3">
@@ -3402,22 +3580,22 @@
         <v>1762</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>563</v>
+        <v>548</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>34</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>565</v>
+        <v>550</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>566</v>
+        <v>551</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="P19" s="3">
         <v>1200</v>
@@ -3429,7 +3607,7 @@
         <v>400</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="T19" s="3">
         <v>2</v>
@@ -3440,13 +3618,13 @@
     </row>
     <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
-        <v>627</v>
+        <v>612</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>626</v>
+        <v>611</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3">
@@ -3459,19 +3637,19 @@
         <v>1762</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>623</v>
+        <v>608</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>622</v>
+        <v>607</v>
       </c>
       <c r="O20" s="9" t="s">
         <v>28</v>
@@ -3486,7 +3664,10 @@
         <v>240</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>345</v>
+        <v>331</v>
+      </c>
+      <c r="T20" s="3">
+        <v>1</v>
       </c>
       <c r="U20" s="1">
         <v>27</v>
@@ -3494,45 +3675,49 @@
     </row>
     <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="8" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
       <c r="O21" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
+        <v>624</v>
+      </c>
+      <c r="P21" s="5">
+        <v>320</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>210</v>
+      </c>
       <c r="R21" s="5"/>
       <c r="S21" s="5" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="T21" s="5">
         <v>2</v>
@@ -3540,96 +3725,99 @@
       <c r="W21" s="22"/>
     </row>
     <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="K22" s="5"/>
-      <c r="L22" s="8" t="s">
-        <v>438</v>
-      </c>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="P22" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="T22" s="5">
-        <v>2</v>
+      <c r="A22" s="17" t="s">
+        <v>632</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3">
+        <v>1730</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1805</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1773</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P22" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>400</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T22" s="3">
+        <v>1</v>
+      </c>
+      <c r="U22" s="1">
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>231</v>
+        <v>139</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>232</v>
+        <v>140</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>233</v>
+        <v>141</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5" t="s">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>234</v>
+        <v>123</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>235</v>
+        <v>143</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>236</v>
+        <v>144</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>237</v>
+        <v>145</v>
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="8" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
       <c r="O23" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="P23" s="5" t="s">
-        <v>238</v>
+        <v>146</v>
+      </c>
+      <c r="P23" s="5">
+        <v>14.4</v>
       </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
       <c r="S23" s="5" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="T23" s="5">
         <v>2</v>
@@ -3637,66 +3825,65 @@
     </row>
     <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="K24" s="5"/>
+      <c r="L24" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="P24" s="5">
+        <v>75</v>
+      </c>
+      <c r="Q24" s="5">
+        <v>53</v>
+      </c>
+      <c r="R24" s="5">
         <v>30</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1757</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1822</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L24" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P24" s="3">
-        <v>155</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>168</v>
-      </c>
-      <c r="R24" s="3">
-        <v>101</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="T24" s="3">
-        <v>1</v>
-      </c>
-      <c r="U24" s="1">
-        <v>1</v>
+      <c r="S24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="T24" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
-        <v>421</v>
+      <c r="A25" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F25" s="3">
         <v>1757</v>
@@ -3705,51 +3892,51 @@
         <v>1822</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>369</v>
+        <v>33</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>370</v>
+        <v>329</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>371</v>
+        <v>330</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P25" s="3">
-        <v>540</v>
+        <v>155</v>
       </c>
       <c r="Q25" s="3">
-        <v>480</v>
+        <v>168</v>
       </c>
       <c r="R25" s="3">
-        <v>290</v>
+        <v>101</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="T25" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U25" s="1">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F26" s="3">
         <v>1757</v>
@@ -3758,54 +3945,51 @@
         <v>1822</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>384</v>
+        <v>27</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>385</v>
+        <v>356</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>386</v>
+        <v>357</v>
       </c>
       <c r="O26" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P26" s="3">
-        <v>345</v>
+        <v>540</v>
       </c>
       <c r="Q26" s="3">
-        <v>150</v>
+        <v>480</v>
       </c>
       <c r="R26" s="3">
-        <v>110</v>
+        <v>290</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="T26" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U26" s="1">
-        <v>91</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F27" s="3">
         <v>1757</v>
@@ -3814,51 +3998,54 @@
         <v>1822</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>388</v>
+        <v>369</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>370</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P27" s="3">
-        <v>590</v>
+        <v>345</v>
       </c>
       <c r="Q27" s="3">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="R27" s="3">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="T27" s="3">
         <v>3</v>
       </c>
       <c r="U27" s="1">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F28" s="3">
         <v>1757</v>
@@ -3866,52 +4053,52 @@
       <c r="G28" s="3">
         <v>1822</v>
       </c>
-      <c r="H28" s="3">
-        <v>1790</v>
+      <c r="H28" s="3" t="s">
+        <v>373</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="O28" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P28" s="3">
-        <v>220</v>
+        <v>590</v>
       </c>
       <c r="Q28" s="3">
-        <v>110</v>
+        <v>450</v>
       </c>
       <c r="R28" s="3">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="T28" s="3">
         <v>3</v>
       </c>
       <c r="U28" s="1">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F29" s="3">
         <v>1757</v>
@@ -3920,25 +4107,25 @@
         <v>1822</v>
       </c>
       <c r="H29" s="3">
-        <v>1796</v>
+        <v>1790</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>408</v>
+        <v>118</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>552</v>
+        <v>377</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>409</v>
+        <v>378</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P29" s="3">
-        <v>135</v>
+        <v>220</v>
       </c>
       <c r="Q29" s="3">
         <v>110</v>
@@ -3947,24 +4134,24 @@
         <v>95</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="T29" s="3">
         <v>3</v>
       </c>
       <c r="U29" s="1">
-        <v>130</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="F30" s="3">
         <v>1757</v>
@@ -3972,132 +4159,143 @@
       <c r="G30" s="3">
         <v>1822</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>411</v>
+      <c r="H30" s="3">
+        <v>1796</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>40</v>
+        <v>394</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>412</v>
+        <v>537</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="O30" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P30" s="3">
-        <v>290</v>
+        <v>135</v>
       </c>
       <c r="Q30" s="3">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="R30" s="3">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="T30" s="3">
         <v>3</v>
       </c>
       <c r="U30" s="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>555</v>
+      </c>
+      <c r="F31" s="3">
+        <v>1757</v>
+      </c>
+      <c r="G31" s="3">
+        <v>1822</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P31" s="3">
+        <v>290</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>140</v>
+      </c>
+      <c r="R31" s="3">
+        <v>125</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="T31" s="3">
+        <v>3</v>
+      </c>
+      <c r="U31" s="1">
         <v>131</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="K31" s="5"/>
-      <c r="L31" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="P31" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="T31" s="5">
-        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>283</v>
+        <v>77</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>107</v>
+        <v>176</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>34</v>
+        <v>289</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="K32" s="5"/>
       <c r="L32" s="8" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
       <c r="O32" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
+        <v>112</v>
+      </c>
+      <c r="P32" s="5">
+        <v>322</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>166</v>
+      </c>
+      <c r="R32" s="5">
+        <v>60</v>
+      </c>
       <c r="S32" s="5" t="s">
-        <v>46</v>
+        <v>138</v>
       </c>
       <c r="T32" s="5">
         <v>2</v>
@@ -4105,136 +4303,146 @@
     </row>
     <row r="33" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>305</v>
+        <v>268</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>307</v>
+        <v>270</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>308</v>
+        <v>271</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="K33" s="5"/>
       <c r="L33" s="8" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
       <c r="O33" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="P33" s="5">
+        <v>51.5</v>
+      </c>
+      <c r="Q33" s="5">
+        <v>15</v>
+      </c>
+      <c r="R33" s="5">
+        <v>13</v>
+      </c>
       <c r="S33" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T33" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>20</v>
+        <v>291</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>22</v>
+        <v>293</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5" t="s">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>24</v>
+        <v>294</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="K34" s="5"/>
       <c r="L34" s="8" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
       <c r="O34" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
-      <c r="R34" s="5"/>
+      <c r="P34" s="5">
+        <v>49.5</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>29</v>
+      </c>
+      <c r="R34" s="5">
+        <v>27</v>
+      </c>
       <c r="S34" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="T34" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>40</v>
+        <v>25</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="K35" s="5"/>
       <c r="L35" s="8" t="s">
-        <v>475</v>
+        <v>429</v>
       </c>
       <c r="M35" s="6"/>
-      <c r="N35" s="6" t="s">
-        <v>474</v>
-      </c>
+      <c r="N35" s="6"/>
       <c r="O35" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P35" s="5" t="s">
-        <v>42</v>
+      <c r="P35" s="5">
+        <v>450</v>
       </c>
       <c r="Q35" s="5"/>
       <c r="R35" s="5"/>
@@ -4242,1607 +4450,1670 @@
         <v>29</v>
       </c>
       <c r="T35" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>317</v>
+        <v>36</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>318</v>
+        <v>31</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>319</v>
+        <v>37</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>320</v>
+        <v>39</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>321</v>
+        <v>39</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="8" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="M36" s="6"/>
-      <c r="N36" s="6"/>
+      <c r="N36" s="6" t="s">
+        <v>460</v>
+      </c>
       <c r="O36" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
+      <c r="P36" s="5">
+        <v>195</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>95</v>
+      </c>
       <c r="R36" s="5"/>
       <c r="S36" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="T36" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K37" s="5"/>
+      <c r="L37" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P37" s="5">
+        <v>244</v>
+      </c>
+      <c r="Q37" s="5">
+        <v>270</v>
+      </c>
+      <c r="R37" s="5">
+        <v>220</v>
+      </c>
+      <c r="S37" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="T37" s="5">
         <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
-        <v>491</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="F37" s="3">
-        <v>1677</v>
-      </c>
-      <c r="G37" s="3">
-        <v>1746</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="L37" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P37" s="3">
-        <v>340</v>
-      </c>
-      <c r="Q37" s="3">
-        <v>284</v>
-      </c>
-      <c r="R37" s="3">
-        <v>127</v>
-      </c>
-      <c r="S37" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="T37" s="3">
-        <v>1</v>
-      </c>
-      <c r="U37" s="1">
-        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>200</v>
+        <v>477</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>192</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="I38" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="F38" s="3">
+        <v>1677</v>
+      </c>
+      <c r="G38" s="3">
+        <v>1746</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J38" s="5" t="s">
+      <c r="J38" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="K38" s="5"/>
-      <c r="L38" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="5" t="s">
+      <c r="K38" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="O38" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T38" s="5">
-        <v>2</v>
+      <c r="P38" s="3">
+        <v>340</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>284</v>
+      </c>
+      <c r="R38" s="3">
+        <v>127</v>
+      </c>
+      <c r="S38" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T38" s="3">
+        <v>1</v>
+      </c>
+      <c r="U38" s="1">
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>117</v>
+      <c r="A39" s="14" t="s">
+        <v>194</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>118</v>
+        <v>192</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>119</v>
+        <v>618</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>121</v>
+        <v>195</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="K39" s="5"/>
       <c r="L39" s="8" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
       <c r="O39" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P39" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
+      <c r="P39" s="5">
+        <v>69</v>
+      </c>
+      <c r="Q39" s="5">
+        <v>50</v>
+      </c>
+      <c r="R39" s="5">
+        <v>41</v>
+      </c>
       <c r="S39" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="T39" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="s">
-        <v>631</v>
-      </c>
-      <c r="B40" s="9" t="s">
+      <c r="A40" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="J40" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3">
-        <v>1698</v>
-      </c>
-      <c r="G40" s="3">
-        <v>1768</v>
-      </c>
-      <c r="H40" s="3">
-        <v>1750</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>620</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>630</v>
-      </c>
-      <c r="L40" s="11" t="s">
-        <v>629</v>
-      </c>
-      <c r="N40" s="9" t="s">
-        <v>628</v>
-      </c>
-      <c r="O40" s="9" t="s">
+      <c r="K40" s="5"/>
+      <c r="L40" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P40" s="3">
-        <v>260</v>
-      </c>
-      <c r="Q40" s="3">
-        <v>180</v>
-      </c>
-      <c r="R40" s="3">
-        <v>40</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="U40" s="1">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>169</v>
+      <c r="P40" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="T40" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="17" t="s">
+        <v>616</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>170</v>
+        <v>114</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3">
-        <v>1693</v>
+        <v>1698</v>
       </c>
       <c r="G41" s="3">
-        <v>1741</v>
+        <v>1768</v>
       </c>
       <c r="H41" s="3">
-        <v>1739</v>
+        <v>1750</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>172</v>
+        <v>605</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>615</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>596</v>
+        <v>614</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>595</v>
+        <v>613</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="P41" s="3">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="Q41" s="3">
         <v>180</v>
       </c>
       <c r="R41" s="3">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>594</v>
+        <v>331</v>
+      </c>
+      <c r="T41" s="3">
+        <v>1</v>
       </c>
       <c r="U41" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="K42" s="5"/>
-      <c r="L42" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8"/>
-      <c r="O42" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="5"/>
-      <c r="S42" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="T42" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="17" t="s">
+        <v>663</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3">
+        <v>1696</v>
+      </c>
+      <c r="G42" s="3">
+        <v>1778</v>
+      </c>
+      <c r="H42" s="3">
+        <v>1752</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>658</v>
+      </c>
+      <c r="O42" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P42" s="3">
+        <v>168</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>95</v>
+      </c>
+      <c r="R42" s="3">
+        <v>90</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="T42" s="3">
+        <v>1</v>
+      </c>
+      <c r="U42" s="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>104</v>
+        <v>162</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>587</v>
+        <v>163</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>105</v>
+        <v>164</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3">
-        <v>1716</v>
+        <v>1693</v>
       </c>
       <c r="G43" s="3">
-        <v>1791</v>
+        <v>1741</v>
       </c>
       <c r="H43" s="3">
-        <v>1782</v>
+        <v>1739</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>556</v>
+        <v>165</v>
       </c>
       <c r="L43" s="11" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="P43" s="3">
-        <v>1300</v>
+        <v>240</v>
       </c>
       <c r="Q43" s="3">
-        <v>800</v>
+        <v>180</v>
       </c>
       <c r="R43" s="3">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>349</v>
+        <v>579</v>
+      </c>
+      <c r="T43" s="3">
+        <v>1</v>
       </c>
       <c r="U43" s="1">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="F44" s="3">
-        <v>1696</v>
-      </c>
-      <c r="G44" s="3">
-        <v>1770</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="J44" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="L44" s="11" t="s">
-        <v>472</v>
-      </c>
-      <c r="N44" s="9" t="s">
-        <v>402</v>
-      </c>
-      <c r="O44" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="P44" s="3">
-        <v>85</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>45</v>
-      </c>
-      <c r="R44" s="3">
-        <v>35</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="T44" s="3">
-        <v>3</v>
-      </c>
-      <c r="U44" s="1">
-        <v>111</v>
+      <c r="A44" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="K44" s="5"/>
+      <c r="L44" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="M44" s="8"/>
+      <c r="N44" s="8"/>
+      <c r="O44" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="P44" s="5">
+        <v>250</v>
+      </c>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="T44" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="K45" s="5"/>
-      <c r="L45" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="M45" s="6"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="5"/>
-      <c r="R45" s="5"/>
-      <c r="S45" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="T45" s="5">
-        <v>2</v>
+        <v>100</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3">
+        <v>1716</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1791</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1782</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="N45" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="O45" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="P45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>800</v>
+      </c>
+      <c r="R45" s="3">
+        <v>500</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T45" s="3">
+        <v>1</v>
+      </c>
+      <c r="U45" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
-        <v>593</v>
+        <v>642</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>254</v>
+        <v>572</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>255</v>
+        <v>101</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="3">
-        <v>1755</v>
+        <v>1716</v>
       </c>
       <c r="G46" s="3">
-        <v>1826</v>
+        <v>1791</v>
       </c>
       <c r="H46" s="3">
-        <v>1793</v>
+        <v>1757</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>592</v>
+        <v>35</v>
       </c>
       <c r="L46" s="11" t="s">
-        <v>591</v>
-      </c>
-      <c r="N46" s="9" t="s">
-        <v>590</v>
+        <v>641</v>
       </c>
       <c r="O46" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P46" s="3">
-        <v>195</v>
+        <v>85</v>
       </c>
       <c r="Q46" s="3">
-        <v>210</v>
+        <v>50</v>
       </c>
       <c r="R46" s="3">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>356</v>
+        <v>335</v>
+      </c>
+      <c r="T46" s="3">
+        <v>2</v>
       </c>
       <c r="U46" s="1">
-        <v>16</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="I47" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="J47" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="K47" s="5"/>
-      <c r="L47" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
-      <c r="O47" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="P47" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q47" s="5"/>
-      <c r="R47" s="5"/>
-      <c r="S47" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T47" s="5">
+      <c r="A47" s="17" t="s">
+        <v>644</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3">
+        <v>1716</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1791</v>
+      </c>
+      <c r="H47" s="3">
+        <v>1757</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="O47" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P47" s="3">
+        <v>82</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>35</v>
+      </c>
+      <c r="R47" s="3">
+        <v>32</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T47" s="3">
         <v>2</v>
+      </c>
+      <c r="U47" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="K48" s="5"/>
-      <c r="L48" s="8" t="s">
-        <v>449</v>
-      </c>
-      <c r="M48" s="6"/>
-      <c r="N48" s="6"/>
-      <c r="O48" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="P48" s="5"/>
-      <c r="Q48" s="5"/>
-      <c r="R48" s="5"/>
-      <c r="S48" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T48" s="5">
-        <v>2</v>
+        <v>266</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1696</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1770</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="N48" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="O48" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="P48" s="3">
+        <v>85</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>45</v>
+      </c>
+      <c r="R48" s="3">
+        <v>35</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="T48" s="3">
+        <v>3</v>
+      </c>
+      <c r="U48" s="1">
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>572</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1725</v>
-      </c>
-      <c r="G49" s="3">
-        <v>1775</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="J49" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="L49" s="11" t="s">
-        <v>406</v>
-      </c>
-      <c r="N49" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="O49" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="P49" s="3">
-        <v>182</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>95</v>
-      </c>
-      <c r="R49" s="3">
-        <v>75</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="T49" s="3">
-        <v>3</v>
-      </c>
-      <c r="U49" s="1">
-        <v>112</v>
+        <v>242</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="K49" s="5"/>
+      <c r="L49" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="P49" s="5">
+        <v>46</v>
+      </c>
+      <c r="Q49" s="5">
+        <v>24.13</v>
+      </c>
+      <c r="R49" s="5">
+        <v>24.13</v>
+      </c>
+      <c r="S49" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="T49" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="17" t="s">
-        <v>609</v>
+        <v>578</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>608</v>
+        <v>243</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>572</v>
+        <v>244</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3">
-        <v>1725</v>
+        <v>1755</v>
       </c>
       <c r="G50" s="3">
-        <v>1775</v>
+        <v>1826</v>
       </c>
       <c r="H50" s="3">
-        <v>1763</v>
+        <v>1793</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>607</v>
+        <v>171</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>606</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>358</v>
+        <v>577</v>
       </c>
       <c r="L50" s="11" t="s">
-        <v>605</v>
+        <v>576</v>
       </c>
       <c r="N50" s="9" t="s">
-        <v>604</v>
+        <v>575</v>
       </c>
       <c r="O50" s="9" t="s">
-        <v>359</v>
+        <v>28</v>
       </c>
       <c r="P50" s="3">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="Q50" s="3">
+        <v>210</v>
+      </c>
+      <c r="R50" s="3">
         <v>110</v>
       </c>
-      <c r="R50" s="3">
-        <v>85</v>
-      </c>
       <c r="S50" s="3" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="T50" s="3">
         <v>1</v>
       </c>
       <c r="U50" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="F51" s="3">
-        <v>1741</v>
-      </c>
-      <c r="G51" s="3">
-        <v>1828</v>
-      </c>
-      <c r="H51" s="3">
-        <v>1778</v>
-      </c>
-      <c r="I51" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="K51" s="5"/>
+      <c r="L51" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="M51" s="6"/>
+      <c r="N51" s="6"/>
+      <c r="O51" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="P51" s="5">
+        <v>61.6</v>
+      </c>
+      <c r="Q51" s="5">
+        <v>45.4</v>
+      </c>
+      <c r="R51" s="5">
+        <v>22.8</v>
+      </c>
+      <c r="S51" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="T51" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="17" t="s">
+        <v>640</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3">
+        <v>1739</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1821</v>
+      </c>
+      <c r="H52" s="3">
+        <v>1785</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J51" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="L51" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="O51" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P51" s="3">
-        <v>138</v>
-      </c>
-      <c r="Q51" s="3">
-        <v>90</v>
-      </c>
-      <c r="R51" s="3">
-        <v>100</v>
-      </c>
-      <c r="S51" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="T51" s="3">
-        <v>1</v>
-      </c>
-      <c r="U51" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="14" t="s">
-        <v>499</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1741</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1828</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1788</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>500</v>
-      </c>
       <c r="J52" s="9" t="s">
-        <v>501</v>
+        <v>35</v>
       </c>
       <c r="L52" s="11" t="s">
-        <v>502</v>
+        <v>637</v>
       </c>
       <c r="O52" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P52" s="3">
-        <v>203</v>
+        <v>53.5</v>
       </c>
       <c r="Q52" s="3">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="R52" s="3">
-        <v>90</v>
+        <v>31.5</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="T52" s="3">
+        <v>1</v>
+      </c>
+      <c r="U52" s="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3">
+        <v>1750</v>
+      </c>
+      <c r="G53" s="3">
+        <v>1835</v>
+      </c>
+      <c r="H53" s="3">
+        <v>1781</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>656</v>
+      </c>
+      <c r="O53" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="P53" s="3">
+        <v>240</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R53" s="3">
+        <v>120</v>
+      </c>
+      <c r="S53" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="T53" s="3">
+        <v>1</v>
+      </c>
+      <c r="U53" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="K54" s="5"/>
+      <c r="L54" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="M54" s="6"/>
+      <c r="N54" s="6"/>
+      <c r="O54" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="P54" s="5">
+        <v>600</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>370</v>
+      </c>
+      <c r="R54" s="5">
+        <v>320</v>
+      </c>
+      <c r="S54" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="T54" s="5">
         <v>2</v>
-      </c>
-      <c r="U52" s="1">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
-        <v>503</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="F53" s="3">
-        <v>1741</v>
-      </c>
-      <c r="G53" s="3">
-        <v>1828</v>
-      </c>
-      <c r="H53" s="3">
-        <v>1778</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J53" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L53" s="11" t="s">
-        <v>504</v>
-      </c>
-      <c r="O53" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="P53" s="3">
-        <v>53</v>
-      </c>
-      <c r="Q53" s="3">
-        <v>42</v>
-      </c>
-      <c r="R53" s="3">
-        <v>28</v>
-      </c>
-      <c r="S53" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="T53" s="3">
-        <v>2</v>
-      </c>
-      <c r="U53" s="1">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
-        <v>505</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="F54" s="3">
-        <v>1741</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1828</v>
-      </c>
-      <c r="H54" s="3">
-        <v>1781</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J54" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L54" s="11" t="s">
-        <v>506</v>
-      </c>
-      <c r="O54" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="P54" s="3">
-        <v>51</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>30</v>
-      </c>
-      <c r="R54" s="3">
-        <v>25</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="T54" s="3">
-        <v>2</v>
-      </c>
-      <c r="U54" s="1">
-        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>331</v>
+        <v>196</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>314</v>
+        <v>390</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>574</v>
+        <v>557</v>
       </c>
       <c r="F55" s="3">
-        <v>1731</v>
+        <v>1725</v>
       </c>
       <c r="G55" s="3">
-        <v>1804</v>
-      </c>
-      <c r="H55" s="3">
-        <v>1787</v>
+        <v>1775</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>391</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>373</v>
+        <v>144</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>374</v>
+        <v>145</v>
       </c>
       <c r="L55" s="11" t="s">
-        <v>375</v>
+        <v>392</v>
+      </c>
+      <c r="N55" s="9" t="s">
+        <v>393</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>28</v>
+        <v>345</v>
       </c>
       <c r="P55" s="3">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="Q55" s="3">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="R55" s="3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="T55" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U55" s="1">
-        <v>59</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="17" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>314</v>
+        <v>593</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>574</v>
+        <v>557</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3">
-        <v>1731</v>
+        <v>1725</v>
       </c>
       <c r="G56" s="3">
-        <v>1804</v>
+        <v>1775</v>
       </c>
       <c r="H56" s="3">
-        <v>1785</v>
+        <v>1763</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>34</v>
+        <v>592</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>35</v>
+        <v>591</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>344</v>
       </c>
       <c r="L56" s="11" t="s">
-        <v>588</v>
+        <v>590</v>
+      </c>
+      <c r="N56" s="9" t="s">
+        <v>589</v>
       </c>
       <c r="O56" s="9" t="s">
-        <v>28</v>
+        <v>345</v>
       </c>
       <c r="P56" s="3">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="Q56" s="3">
         <v>110</v>
       </c>
       <c r="R56" s="3">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="T56" s="3">
         <v>1</v>
       </c>
       <c r="U56" s="1">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="17" t="s">
-        <v>610</v>
+      <c r="A57" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>118</v>
+        <v>203</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="E57" s="3"/>
+        <v>558</v>
+      </c>
       <c r="F57" s="3">
-        <v>1678</v>
+        <v>1741</v>
       </c>
       <c r="G57" s="3">
-        <v>1736</v>
+        <v>1828</v>
       </c>
       <c r="H57" s="3">
-        <v>1730</v>
+        <v>1778</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>612</v>
+        <v>34</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>613</v>
+        <v>332</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>614</v>
+        <v>333</v>
       </c>
       <c r="L57" s="11" t="s">
-        <v>615</v>
-      </c>
-      <c r="N57" s="9" t="s">
-        <v>616</v>
+        <v>334</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P57" s="3">
-        <v>220</v>
+        <v>138</v>
       </c>
       <c r="Q57" s="3">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="R57" s="3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="T57" s="3">
         <v>1</v>
       </c>
       <c r="U57" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="14" t="s">
+        <v>485</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1741</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1828</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1788</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="J58" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="O58" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P58" s="3">
+        <v>203</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>105</v>
+      </c>
+      <c r="R58" s="3">
+        <v>90</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T58" s="3">
+        <v>2</v>
+      </c>
+      <c r="U58" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="14" t="s">
+        <v>489</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1741</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1828</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1778</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="O59" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="P59" s="3">
+        <v>53</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>42</v>
+      </c>
+      <c r="R59" s="3">
+        <v>28</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T59" s="3">
+        <v>2</v>
+      </c>
+      <c r="U59" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1741</v>
+      </c>
+      <c r="G60" s="3">
+        <v>1828</v>
+      </c>
+      <c r="H60" s="3">
+        <v>1781</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L60" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="O60" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="P60" s="3">
+        <v>51</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>30</v>
+      </c>
+      <c r="R60" s="3">
         <v>25</v>
       </c>
-    </row>
-    <row r="58" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>575</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1706</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1775</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="J58" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="L58" s="11" t="s">
-        <v>469</v>
-      </c>
-      <c r="N58" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="O58" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="P58" s="3">
-        <v>45</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>38</v>
-      </c>
-      <c r="R58" s="3">
-        <v>38</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="T58" s="3">
-        <v>3</v>
-      </c>
-      <c r="U58" s="1">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="59" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="H59" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="I59" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J59" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="K59" s="5"/>
-      <c r="L59" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="M59" s="6"/>
-      <c r="N59" s="6"/>
-      <c r="O59" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="P59" s="5"/>
-      <c r="Q59" s="5"/>
-      <c r="R59" s="5"/>
-      <c r="S59" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T59" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="K60" s="5"/>
-      <c r="L60" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="M60" s="6"/>
-      <c r="N60" s="6"/>
-      <c r="O60" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P60" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q60" s="5"/>
-      <c r="R60" s="5"/>
-      <c r="S60" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T60" s="5">
-        <v>1</v>
+      <c r="S60" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T60" s="3">
+        <v>2</v>
+      </c>
+      <c r="U60" s="1">
+        <v>88</v>
       </c>
     </row>
     <row r="61" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="I61" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K61" s="5"/>
-      <c r="L61" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="M61" s="6"/>
-      <c r="N61" s="6"/>
-      <c r="O61" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="F61" s="3">
+        <v>1731</v>
+      </c>
+      <c r="G61" s="3">
+        <v>1804</v>
+      </c>
+      <c r="H61" s="3">
+        <v>1787</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="J61" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="L61" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="O61" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P61" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q61" s="5"/>
-      <c r="R61" s="5"/>
-      <c r="S61" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T61" s="5">
+      <c r="P61" s="3">
+        <v>145</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>115</v>
+      </c>
+      <c r="R61" s="3">
+        <v>80</v>
+      </c>
+      <c r="S61" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T61" s="3">
         <v>2</v>
       </c>
+      <c r="U61" s="1">
+        <v>59</v>
+      </c>
     </row>
     <row r="62" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="J62" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="K62" s="5"/>
-      <c r="L62" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="M62" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="N62" s="6"/>
-      <c r="O62" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="P62" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q62" s="5"/>
-      <c r="R62" s="5"/>
-      <c r="S62" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="T62" s="5">
+      <c r="A62" s="17" t="s">
+        <v>574</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3">
+        <v>1731</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1804</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1785</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J62" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L62" s="11" t="s">
+        <v>573</v>
+      </c>
+      <c r="O62" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P62" s="3">
+        <v>175</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>110</v>
+      </c>
+      <c r="R62" s="3">
+        <v>105</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T62" s="3">
         <v>1</v>
       </c>
+      <c r="U62" s="1">
+        <v>14</v>
+      </c>
     </row>
     <row r="63" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="12"/>
+      <c r="A63" s="17" t="s">
+        <v>595</v>
+      </c>
       <c r="B63" s="9" t="s">
-        <v>484</v>
+        <v>114</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>84</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="E63" s="3"/>
       <c r="F63" s="3">
-        <v>1738</v>
+        <v>1678</v>
       </c>
       <c r="G63" s="3">
-        <v>1814</v>
+        <v>1736</v>
       </c>
       <c r="H63" s="3">
-        <v>1782</v>
+        <v>1730</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>34</v>
+        <v>597</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>35</v>
+        <v>598</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>599</v>
       </c>
       <c r="L63" s="11" t="s">
-        <v>354</v>
+        <v>600</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>354</v>
+        <v>601</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="P63" s="3">
-        <v>46</v>
+        <v>220</v>
       </c>
       <c r="Q63" s="3">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="R63" s="3">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="T63" s="3">
         <v>1</v>
       </c>
       <c r="U63" s="1">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H64" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I64" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="J64" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="K64" s="5"/>
-      <c r="L64" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="M64" s="6"/>
-      <c r="N64" s="6"/>
-      <c r="O64" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="P64" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q64" s="5"/>
-      <c r="R64" s="5"/>
-      <c r="S64" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T64" s="5">
-        <v>1</v>
+      <c r="A64" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="F64" s="3">
+        <v>1706</v>
+      </c>
+      <c r="G64" s="3">
+        <v>1775</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J64" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="N64" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="O64" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="P64" s="3">
+        <v>45</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>38</v>
+      </c>
+      <c r="R64" s="3">
+        <v>38</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="T64" s="3">
+        <v>3</v>
+      </c>
+      <c r="U64" s="1">
+        <v>109</v>
       </c>
     </row>
     <row r="65" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="20" t="s">
-        <v>225</v>
+      <c r="A65" s="2" t="s">
+        <v>322</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>226</v>
+        <v>323</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>227</v>
+        <v>324</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5" t="s">
-        <v>201</v>
+        <v>325</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>34</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>230</v>
+        <v>327</v>
       </c>
       <c r="K65" s="5"/>
       <c r="L65" s="8" t="s">
-        <v>550</v>
-      </c>
-      <c r="M65" s="8"/>
-      <c r="N65" s="8"/>
+        <v>436</v>
+      </c>
+      <c r="M65" s="6"/>
+      <c r="N65" s="6"/>
       <c r="O65" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="P65" s="5"/>
-      <c r="Q65" s="5"/>
-      <c r="R65" s="5"/>
+        <v>300</v>
+      </c>
+      <c r="P65" s="5">
+        <v>400</v>
+      </c>
+      <c r="Q65" s="5">
+        <v>485</v>
+      </c>
+      <c r="R65" s="5">
+        <v>25</v>
+      </c>
       <c r="S65" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T65" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="17" t="s">
-        <v>597</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>599</v>
-      </c>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3">
-        <v>1717</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1785</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1753</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="J66" s="9" t="s">
-        <v>600</v>
-      </c>
-      <c r="L66" s="11" t="s">
-        <v>601</v>
-      </c>
-      <c r="N66" s="9" t="s">
-        <v>602</v>
-      </c>
-      <c r="O66" s="9" t="s">
-        <v>603</v>
-      </c>
-      <c r="P66" s="3">
-        <v>280</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>310</v>
-      </c>
-      <c r="R66" s="3">
-        <v>190</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="T66" s="3">
+      <c r="A66" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="K66" s="5"/>
+      <c r="L66" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P66" s="5">
+        <v>78.5</v>
+      </c>
+      <c r="Q66" s="5">
+        <v>58</v>
+      </c>
+      <c r="R66" s="5">
+        <v>36.5</v>
+      </c>
+      <c r="S66" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="T66" s="5">
         <v>1</v>
       </c>
-      <c r="U66" s="1">
-        <v>19</v>
-      </c>
     </row>
     <row r="67" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="10" t="s">
-        <v>185</v>
+      <c r="A67" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="B67" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>174</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>186</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5" t="s">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>187</v>
+        <v>39</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="K67" s="5"/>
       <c r="L67" s="8" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
       <c r="O67" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P67" s="5" t="s">
-        <v>42</v>
+      <c r="P67" s="5">
+        <v>450</v>
       </c>
       <c r="Q67" s="5"/>
       <c r="R67" s="5"/>
@@ -5855,512 +6126,535 @@
     </row>
     <row r="68" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>239</v>
+        <v>154</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>240</v>
+        <v>155</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>241</v>
+        <v>156</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="I68" s="5"/>
+        <v>158</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="J68" s="5" t="s">
-        <v>243</v>
+        <v>160</v>
       </c>
       <c r="K68" s="5"/>
       <c r="L68" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="M68" s="6"/>
+        <v>456</v>
+      </c>
+      <c r="M68" s="8" t="s">
+        <v>457</v>
+      </c>
       <c r="N68" s="6"/>
       <c r="O68" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P68" s="5"/>
-      <c r="Q68" s="5"/>
-      <c r="R68" s="5"/>
+        <v>627</v>
+      </c>
+      <c r="P68" s="5">
+        <v>42</v>
+      </c>
+      <c r="Q68" s="5">
+        <v>21.5</v>
+      </c>
+      <c r="R68" s="5">
+        <v>26</v>
+      </c>
       <c r="S68" s="5" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="T68" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="G69" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="I69" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="J69" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="K69" s="5"/>
-      <c r="L69" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="M69" s="6"/>
-      <c r="N69" s="6"/>
+      <c r="A69" s="12"/>
+      <c r="B69" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F69" s="3">
+        <v>1738</v>
+      </c>
+      <c r="G69" s="3">
+        <v>1814</v>
+      </c>
+      <c r="H69" s="3">
+        <v>1782</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J69" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>340</v>
+      </c>
       <c r="O69" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P69" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q69" s="5"/>
-      <c r="R69" s="5"/>
-      <c r="S69" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="T69" s="5">
+      <c r="P69" s="3">
+        <v>46</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>25</v>
+      </c>
+      <c r="R69" s="3">
+        <v>22</v>
+      </c>
+      <c r="S69" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T69" s="3">
         <v>1</v>
       </c>
+      <c r="U69" s="1">
+        <v>8</v>
+      </c>
     </row>
     <row r="70" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>576</v>
-      </c>
-      <c r="F70" s="3">
-        <v>1730</v>
-      </c>
-      <c r="G70" s="3">
-        <v>1809</v>
-      </c>
-      <c r="H70" s="3">
-        <v>1783</v>
-      </c>
-      <c r="I70" s="3" t="s">
+      <c r="A70" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J70" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="K70" s="5"/>
+      <c r="L70" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="M70" s="6"/>
+      <c r="N70" s="6"/>
+      <c r="O70" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="P70" s="5">
+        <v>58.4</v>
+      </c>
+      <c r="Q70" s="5">
+        <v>27.3</v>
+      </c>
+      <c r="R70" s="5">
+        <v>22.9</v>
+      </c>
+      <c r="S70" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="T70" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="I71" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J70" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L70" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="O70" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P70" s="3">
-        <v>178</v>
-      </c>
-      <c r="Q70" s="3">
-        <v>86</v>
-      </c>
-      <c r="R70" s="3">
-        <v>82</v>
-      </c>
-      <c r="S70" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="T70" s="3">
+      <c r="J71" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="K71" s="5"/>
+      <c r="L71" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="M71" s="8"/>
+      <c r="N71" s="8"/>
+      <c r="O71" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="P71" s="5">
+        <v>34</v>
+      </c>
+      <c r="Q71" s="5">
+        <v>22</v>
+      </c>
+      <c r="R71" s="5">
+        <v>25</v>
+      </c>
+      <c r="S71" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="T71" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="17" t="s">
+        <v>582</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3">
+        <v>1717</v>
+      </c>
+      <c r="G72" s="3">
+        <v>1785</v>
+      </c>
+      <c r="H72" s="3">
+        <v>1753</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J72" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="N72" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="O72" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="P72" s="3">
+        <v>280</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>310</v>
+      </c>
+      <c r="R72" s="3">
+        <v>190</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="T72" s="3">
         <v>1</v>
       </c>
-      <c r="U70" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>576</v>
-      </c>
-      <c r="F71" s="3">
-        <v>1730</v>
-      </c>
-      <c r="G71" s="3">
-        <v>1809</v>
-      </c>
-      <c r="H71" s="3">
-        <v>1773</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="J71" s="9" t="s">
-        <v>429</v>
-      </c>
-      <c r="L71" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="O71" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P71" s="3">
-        <v>60</v>
-      </c>
-      <c r="Q71" s="3">
-        <v>45</v>
-      </c>
-      <c r="R71" s="3">
-        <v>32</v>
-      </c>
-      <c r="S71" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="T71" s="3">
-        <v>2</v>
-      </c>
-      <c r="U71" s="1">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="72" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>576</v>
-      </c>
-      <c r="F72" s="3">
-        <v>1730</v>
-      </c>
-      <c r="G72" s="3">
-        <v>1809</v>
-      </c>
-      <c r="H72" s="3">
-        <v>1775</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J72" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L72" s="11" t="s">
-        <v>394</v>
-      </c>
-      <c r="O72" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P72" s="3">
-        <v>75</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>50</v>
-      </c>
-      <c r="R72" s="3">
-        <v>45</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="T72" s="3">
-        <v>2</v>
-      </c>
       <c r="U72" s="1">
-        <v>99</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>431</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>576</v>
-      </c>
-      <c r="F73" s="3">
-        <v>1730</v>
-      </c>
-      <c r="G73" s="3">
-        <v>1809</v>
-      </c>
-      <c r="H73" s="3">
-        <v>1769</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J73" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L73" s="11" t="s">
-        <v>419</v>
-      </c>
-      <c r="O73" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="J73" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="K73" s="5"/>
+      <c r="L73" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="M73" s="6"/>
+      <c r="N73" s="6"/>
+      <c r="O73" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P73" s="3">
-        <v>76</v>
-      </c>
-      <c r="Q73" s="3">
+      <c r="P73" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="R73" s="3">
-        <v>45</v>
-      </c>
-      <c r="S73" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="T73" s="3">
-        <v>3</v>
-      </c>
-      <c r="U73" s="1">
-        <v>163</v>
+      <c r="Q73" s="5"/>
+      <c r="R73" s="5"/>
+      <c r="S73" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="T73" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="16" t="s">
-        <v>47</v>
+      <c r="A74" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>48</v>
+        <v>229</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>49</v>
+        <v>230</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>51</v>
+        <v>179</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I74" s="5" t="s">
-        <v>53</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="I74" s="5"/>
       <c r="J74" s="5" t="s">
-        <v>54</v>
+        <v>232</v>
       </c>
       <c r="K74" s="5"/>
       <c r="L74" s="8" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
       <c r="O74" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P74" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q74" s="5"/>
+        <v>629</v>
+      </c>
+      <c r="P74" s="5">
+        <v>225</v>
+      </c>
+      <c r="Q74" s="5">
+        <v>118</v>
+      </c>
       <c r="R74" s="5"/>
       <c r="S74" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="T74" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="J75" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="K75" s="5"/>
+      <c r="L75" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="M75" s="6"/>
+      <c r="N75" s="6"/>
+      <c r="O75" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P75" s="5">
+        <v>72.7</v>
+      </c>
+      <c r="Q75" s="5">
+        <v>52</v>
+      </c>
+      <c r="R75" s="5">
+        <v>30</v>
+      </c>
+      <c r="S75" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="T75" s="5">
         <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>577</v>
-      </c>
-      <c r="F75" s="3">
-        <v>1714</v>
-      </c>
-      <c r="G75" s="3">
-        <v>1785</v>
-      </c>
-      <c r="H75" s="3">
-        <v>1744</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J75" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L75" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="O75" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P75" s="3">
-        <v>58</v>
-      </c>
-      <c r="Q75" s="3">
-        <v>35</v>
-      </c>
-      <c r="R75" s="3">
-        <v>38</v>
-      </c>
-      <c r="S75" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="T75" s="3">
-        <v>1</v>
-      </c>
-      <c r="U75" s="1">
-        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>483</v>
+        <v>42</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>214</v>
+        <v>43</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="F76" s="3">
-        <v>1714</v>
+        <v>1730</v>
       </c>
       <c r="G76" s="3">
-        <v>1785</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>376</v>
+        <v>1809</v>
+      </c>
+      <c r="H76" s="3">
+        <v>1783</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>377</v>
+        <v>34</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>378</v>
+        <v>35</v>
       </c>
       <c r="L76" s="11" t="s">
-        <v>379</v>
+        <v>341</v>
       </c>
       <c r="O76" s="9" t="s">
-        <v>364</v>
+        <v>28</v>
       </c>
       <c r="P76" s="3">
-        <v>610</v>
+        <v>178</v>
       </c>
       <c r="Q76" s="3">
-        <v>480</v>
+        <v>86</v>
       </c>
       <c r="R76" s="3">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="S76" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="T76" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U76" s="1">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="13" t="s">
-        <v>479</v>
+      <c r="A77" s="10" t="s">
+        <v>413</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>214</v>
+        <v>43</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="F77" s="3">
-        <v>1714</v>
+        <v>1730</v>
       </c>
       <c r="G77" s="3">
-        <v>1785</v>
+        <v>1809</v>
       </c>
       <c r="H77" s="3">
-        <v>1776</v>
+        <v>1773</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>34</v>
+        <v>414</v>
       </c>
       <c r="J77" s="9" t="s">
-        <v>35</v>
+        <v>415</v>
       </c>
       <c r="L77" s="11" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P77" s="3">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="Q77" s="3">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="R77" s="3">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="S77" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="T77" s="3">
         <v>2</v>
       </c>
       <c r="U77" s="1">
-        <v>73</v>
+        <v>58</v>
       </c>
     </row>
     <row r="78" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>478</v>
+        <v>416</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>214</v>
+        <v>43</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="F78" s="3">
-        <v>1714</v>
+        <v>1730</v>
       </c>
       <c r="G78" s="3">
-        <v>1785</v>
+        <v>1809</v>
       </c>
       <c r="H78" s="3">
-        <v>1759</v>
+        <v>1775</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>34</v>
@@ -6369,984 +6663,979 @@
         <v>35</v>
       </c>
       <c r="L78" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O78" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P78" s="3">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="Q78" s="3">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="R78" s="3">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="S78" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="T78" s="3">
         <v>2</v>
       </c>
       <c r="U78" s="1">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="13" t="s">
-        <v>481</v>
+      <c r="A79" s="10" t="s">
+        <v>417</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>214</v>
+        <v>43</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="F79" s="3">
-        <v>1714</v>
+        <v>1730</v>
       </c>
       <c r="G79" s="3">
-        <v>1785</v>
+        <v>1809</v>
       </c>
       <c r="H79" s="3">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>480</v>
+        <v>34</v>
       </c>
       <c r="J79" s="9" t="s">
-        <v>418</v>
+        <v>35</v>
       </c>
       <c r="L79" s="11" t="s">
-        <v>482</v>
+        <v>405</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="P79" s="3">
-        <v>380</v>
+        <v>76</v>
       </c>
       <c r="Q79" s="3">
-        <v>250</v>
+        <v>54</v>
       </c>
       <c r="R79" s="3">
-        <v>240</v>
+        <v>45</v>
       </c>
       <c r="S79" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="T79" s="3">
         <v>3</v>
       </c>
       <c r="U79" s="1">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="80" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B80" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>578</v>
-      </c>
-      <c r="F80" s="3">
-        <v>1704</v>
-      </c>
-      <c r="G80" s="3">
-        <v>1762</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J80" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L80" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="N80" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="O80" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="P80" s="3">
-        <v>195</v>
-      </c>
-      <c r="Q80" s="3">
-        <v>110</v>
-      </c>
-      <c r="R80" s="3">
-        <v>90</v>
-      </c>
-      <c r="S80" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="T80" s="3">
+      <c r="A80" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K80" s="5"/>
+      <c r="L80" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="M80" s="6"/>
+      <c r="N80" s="6"/>
+      <c r="O80" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P80" s="5">
+        <v>230</v>
+      </c>
+      <c r="Q80" s="5"/>
+      <c r="R80" s="5"/>
+      <c r="S80" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="T80" s="5">
         <v>1</v>
-      </c>
-      <c r="U80" s="1">
-        <v>50</v>
       </c>
     </row>
     <row r="81" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>294</v>
+        <v>210</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>295</v>
+        <v>205</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>579</v>
+        <v>562</v>
       </c>
       <c r="F81" s="3">
-        <v>1702</v>
+        <v>1714</v>
       </c>
       <c r="G81" s="3">
-        <v>1762</v>
+        <v>1785</v>
       </c>
       <c r="H81" s="3">
-        <v>1761</v>
+        <v>1744</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="J81" s="9" t="s">
-        <v>276</v>
+        <v>35</v>
       </c>
       <c r="L81" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="N81" s="9" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P81" s="3">
-        <v>245</v>
+        <v>58</v>
       </c>
       <c r="Q81" s="3">
-        <v>150</v>
+        <v>35</v>
       </c>
       <c r="R81" s="3">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="S81" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="T81" s="3">
         <v>1</v>
       </c>
       <c r="U81" s="1">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D82" s="5"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G82" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="H82" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="I82" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="J82" s="5" t="s">
+      <c r="A82" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="F82" s="3">
+        <v>1714</v>
+      </c>
+      <c r="G82" s="3">
+        <v>1785</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J82" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="L82" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="O82" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="P82" s="3">
+        <v>610</v>
+      </c>
+      <c r="Q82" s="3">
+        <v>480</v>
+      </c>
+      <c r="R82" s="3">
+        <v>280</v>
+      </c>
+      <c r="S82" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T82" s="3">
+        <v>2</v>
+      </c>
+      <c r="U82" s="1">
         <v>72</v>
       </c>
-      <c r="K82" s="5"/>
-      <c r="L82" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="M82" s="6"/>
-      <c r="N82" s="6"/>
-      <c r="O82" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P82" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q82" s="5"/>
-      <c r="R82" s="5"/>
-      <c r="S82" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T82" s="5">
-        <v>2</v>
-      </c>
     </row>
     <row r="83" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="17" t="s">
-        <v>621</v>
+      <c r="A83" s="13" t="s">
+        <v>465</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>66</v>
+        <v>205</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E83" s="3"/>
+        <v>562</v>
+      </c>
       <c r="F83" s="3">
-        <v>1658</v>
+        <v>1714</v>
       </c>
       <c r="G83" s="3">
-        <v>1728</v>
+        <v>1785</v>
       </c>
       <c r="H83" s="3">
-        <v>1718</v>
+        <v>1776</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="J83" s="9" t="s">
-        <v>620</v>
+        <v>35</v>
       </c>
       <c r="L83" s="11" t="s">
-        <v>619</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="N83" s="9" t="s">
-        <v>617</v>
+        <v>366</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P83" s="3">
-        <v>420</v>
+        <v>150</v>
       </c>
       <c r="Q83" s="3">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="R83" s="3">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="S83" s="3" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="T83" s="3">
+        <v>2</v>
+      </c>
+      <c r="U83" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="F84" s="3">
+        <v>1714</v>
+      </c>
+      <c r="G84" s="3">
+        <v>1785</v>
+      </c>
+      <c r="H84" s="3">
+        <v>1759</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L84" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="O84" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P84" s="3">
+        <v>48</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>32</v>
+      </c>
+      <c r="R84" s="3">
+        <v>30</v>
+      </c>
+      <c r="S84" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T84" s="3">
+        <v>2</v>
+      </c>
+      <c r="U84" s="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="F85" s="3">
+        <v>1714</v>
+      </c>
+      <c r="G85" s="3">
+        <v>1785</v>
+      </c>
+      <c r="H85" s="3">
+        <v>1770</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="J85" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="L85" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="O85" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="P85" s="3">
+        <v>380</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>250</v>
+      </c>
+      <c r="R85" s="3">
+        <v>240</v>
+      </c>
+      <c r="S85" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T85" s="3">
+        <v>3</v>
+      </c>
+      <c r="U85" s="1">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="F86" s="3">
+        <v>1704</v>
+      </c>
+      <c r="G86" s="3">
+        <v>1762</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J86" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L86" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="N86" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="O86" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="P86" s="3">
+        <v>195</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>110</v>
+      </c>
+      <c r="R86" s="3">
+        <v>90</v>
+      </c>
+      <c r="S86" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="T86" s="3">
         <v>1</v>
       </c>
-      <c r="U83" s="1">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="84" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="H84" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="I84" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="J84" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="K84" s="5"/>
-      <c r="L84" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="M84" s="6"/>
-      <c r="N84" s="6"/>
-      <c r="O84" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P84" s="5"/>
-      <c r="Q84" s="5"/>
-      <c r="R84" s="5"/>
-      <c r="S84" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="T84" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="G85" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="H85" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="I85" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J85" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K85" s="5"/>
-      <c r="L85" s="8" t="s">
-        <v>460</v>
-      </c>
-      <c r="M85" s="6"/>
-      <c r="N85" s="6"/>
-      <c r="O85" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P85" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q85" s="5"/>
-      <c r="R85" s="5"/>
-      <c r="S85" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="T85" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="G86" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H86" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="I86" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="J86" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="K86" s="5"/>
-      <c r="L86" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="M86" s="6"/>
-      <c r="N86" s="6"/>
-      <c r="O86" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="P86" s="5"/>
-      <c r="Q86" s="5"/>
-      <c r="R86" s="5"/>
-      <c r="S86" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="T86" s="5">
-        <v>2</v>
+      <c r="U86" s="1">
+        <v>50</v>
       </c>
     </row>
     <row r="87" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
-        <v>191</v>
+      <c r="A87" s="17" t="s">
+        <v>676</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>192</v>
+        <v>675</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>580</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="E87" s="3"/>
       <c r="F87" s="3">
-        <v>1720</v>
+        <v>1653</v>
       </c>
       <c r="G87" s="3">
-        <v>1793</v>
+        <v>1686</v>
       </c>
       <c r="H87" s="3">
-        <v>1753</v>
+        <v>1702</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>40</v>
+        <v>171</v>
       </c>
       <c r="J87" s="9" t="s">
-        <v>41</v>
+        <v>673</v>
       </c>
       <c r="L87" s="11" t="s">
-        <v>350</v>
+        <v>672</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>351</v>
+        <v>671</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="P87" s="3">
-        <v>50</v>
+        <v>195</v>
       </c>
       <c r="Q87" s="3">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="R87" s="3">
         <v>80</v>
       </c>
       <c r="S87" s="3" t="s">
-        <v>345</v>
+        <v>664</v>
       </c>
       <c r="T87" s="3">
         <v>1</v>
       </c>
       <c r="U87" s="1">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="88" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="10" t="s">
-        <v>433</v>
+      <c r="A88" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>192</v>
+        <v>282</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="F88" s="3">
-        <v>1720</v>
+        <v>1702</v>
       </c>
       <c r="G88" s="3">
-        <v>1793</v>
+        <v>1762</v>
       </c>
       <c r="H88" s="3">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>40</v>
+        <v>171</v>
       </c>
       <c r="J88" s="9" t="s">
-        <v>415</v>
+        <v>264</v>
       </c>
       <c r="L88" s="11" t="s">
-        <v>416</v>
+        <v>348</v>
       </c>
       <c r="N88" s="9" t="s">
-        <v>417</v>
+        <v>349</v>
       </c>
       <c r="O88" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P88" s="3">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="Q88" s="3">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="R88" s="3">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="S88" s="3" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="T88" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U88" s="1">
-        <v>146</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
-        <v>261</v>
+      <c r="A89" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>262</v>
+        <v>65</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>263</v>
+        <v>66</v>
       </c>
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5" t="s">
-        <v>264</v>
+        <v>67</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>265</v>
+        <v>68</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>266</v>
+        <v>69</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>267</v>
+        <v>70</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>268</v>
+        <v>71</v>
       </c>
       <c r="K89" s="5"/>
       <c r="L89" s="8" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="M89" s="6"/>
       <c r="N89" s="6"/>
       <c r="O89" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P89" s="5" t="s">
-        <v>269</v>
+        <v>87</v>
+      </c>
+      <c r="P89" s="5">
+        <v>84</v>
       </c>
       <c r="Q89" s="5"/>
       <c r="R89" s="5"/>
       <c r="S89" s="5" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="T89" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="17" t="s">
+        <v>606</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3">
+        <v>1658</v>
+      </c>
+      <c r="G90" s="3">
+        <v>1728</v>
+      </c>
+      <c r="H90" s="3">
+        <v>1718</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J90" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="L90" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="M90" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="N90" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="O90" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P90" s="3">
+        <v>420</v>
+      </c>
+      <c r="Q90" s="3">
+        <v>180</v>
+      </c>
+      <c r="R90" s="3">
+        <v>160</v>
+      </c>
+      <c r="S90" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="T90" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="H90" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="I90" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="J90" s="5" t="s">
+      <c r="U90" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="14" t="s">
+        <v>631</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="J91" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="K91" s="5"/>
+      <c r="L91" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="M91" s="6"/>
+      <c r="N91" s="6"/>
+      <c r="O91" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P91" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="Q91" s="5"/>
+      <c r="R91" s="5"/>
+      <c r="S91" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="T91" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J92" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K92" s="5"/>
+      <c r="L92" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="M92" s="6"/>
+      <c r="N92" s="6"/>
+      <c r="O92" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P92" s="5">
+        <v>97</v>
+      </c>
+      <c r="Q92" s="5">
+        <v>46</v>
+      </c>
+      <c r="R92" s="5">
+        <v>34</v>
+      </c>
+      <c r="S92" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="T92" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="K90" s="5"/>
-      <c r="L90" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="M90" s="6"/>
-      <c r="N90" s="6"/>
-      <c r="O90" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="5"/>
-      <c r="R90" s="5"/>
-      <c r="S90" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T90" s="5">
+      <c r="B93" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="H93" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="J93" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="K93" s="5"/>
+      <c r="L93" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="M93" s="6"/>
+      <c r="N93" s="6"/>
+      <c r="O93" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="P93" s="5">
+        <v>246</v>
+      </c>
+      <c r="Q93" s="5">
+        <v>442</v>
+      </c>
+      <c r="R93" s="5">
+        <v>247</v>
+      </c>
+      <c r="S93" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="T93" s="5">
         <v>2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="17" t="s">
-        <v>531</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="C91" s="9" t="s">
-        <v>581</v>
-      </c>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3">
-        <v>1664</v>
-      </c>
-      <c r="G91" s="3">
-        <v>1714</v>
-      </c>
-      <c r="H91" s="3">
-        <v>1703</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="J91" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="L91" s="11" t="s">
-        <v>534</v>
-      </c>
-      <c r="N91" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="O91" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="P91" s="3">
-        <v>290</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>260</v>
-      </c>
-      <c r="R91" s="3">
-        <v>140</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="T91" s="3">
-        <v>1</v>
-      </c>
-      <c r="U91" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="92" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="17" t="s">
-        <v>536</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="C92" s="9" t="s">
-        <v>582</v>
-      </c>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3">
-        <v>1656</v>
-      </c>
-      <c r="G92" s="3">
-        <v>1732</v>
-      </c>
-      <c r="H92" s="3">
-        <v>1702</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="J92" s="9" t="s">
-        <v>539</v>
-      </c>
-      <c r="L92" s="11" t="s">
-        <v>540</v>
-      </c>
-      <c r="N92" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="O92" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="P92" s="3">
-        <v>185</v>
-      </c>
-      <c r="Q92" s="3">
-        <v>72</v>
-      </c>
-      <c r="R92" s="3">
-        <v>50</v>
-      </c>
-      <c r="S92" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="T92" s="3">
-        <v>3</v>
-      </c>
-      <c r="U92" s="1">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="93" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="17" t="s">
-        <v>543</v>
-      </c>
-      <c r="B93" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="C93" s="9" t="s">
-        <v>582</v>
-      </c>
-      <c r="E93" s="3"/>
-      <c r="F93" s="3">
-        <v>1656</v>
-      </c>
-      <c r="G93" s="3">
-        <v>1732</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="J93" s="9" t="s">
-        <v>545</v>
-      </c>
-      <c r="L93" s="11" t="s">
-        <v>546</v>
-      </c>
-      <c r="N93" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="O93" s="9" t="s">
-        <v>548</v>
-      </c>
-      <c r="P93" s="3">
-        <v>180</v>
-      </c>
-      <c r="Q93" s="3">
-        <v>70</v>
-      </c>
-      <c r="R93" s="3">
-        <v>50</v>
-      </c>
-      <c r="S93" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="T93" s="3">
-        <v>1</v>
-      </c>
-      <c r="U93" s="1">
-        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>316</v>
+        <v>183</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>497</v>
+        <v>184</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>583</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>584</v>
+        <v>565</v>
       </c>
       <c r="F94" s="3">
-        <v>1705</v>
+        <v>1720</v>
       </c>
       <c r="G94" s="3">
-        <v>1764</v>
+        <v>1793</v>
       </c>
       <c r="H94" s="3">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="J94" s="9" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="L94" s="11" t="s">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="N94" s="9" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="O94" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P94" s="3">
-        <v>450</v>
+        <v>50</v>
       </c>
       <c r="Q94" s="3">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="R94" s="3">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="S94" s="3" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="T94" s="3">
         <v>1</v>
       </c>
       <c r="U94" s="1">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="17" t="s">
-        <v>636</v>
+      <c r="A95" s="10" t="s">
+        <v>419</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>497</v>
+        <v>184</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>583</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="E95" s="3"/>
+        <v>565</v>
+      </c>
       <c r="F95" s="3">
-        <v>1705</v>
+        <v>1720</v>
       </c>
       <c r="G95" s="3">
-        <v>1764</v>
+        <v>1793</v>
       </c>
       <c r="H95" s="3">
-        <v>1755</v>
+        <v>1760</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J95" s="9" t="s">
-        <v>635</v>
+        <v>401</v>
       </c>
       <c r="L95" s="11" t="s">
-        <v>634</v>
+        <v>402</v>
+      </c>
+      <c r="N95" s="9" t="s">
+        <v>403</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>364</v>
+        <v>28</v>
       </c>
       <c r="P95" s="3">
-        <v>320</v>
+        <v>196</v>
       </c>
       <c r="Q95" s="3">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="R95" s="3">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="S95" s="3" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="T95" s="3">
+        <v>3</v>
+      </c>
+      <c r="U95" s="1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="J96" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="K96" s="5"/>
+      <c r="L96" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="M96" s="6"/>
+      <c r="N96" s="6"/>
+      <c r="O96" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P96" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q96" s="5"/>
+      <c r="R96" s="5"/>
+      <c r="S96" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="T96" s="5">
         <v>1</v>
       </c>
-      <c r="U95" s="1">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="96" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="21" t="s">
-        <v>554</v>
-      </c>
-      <c r="B96" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="C96" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3">
-        <v>1742</v>
-      </c>
-      <c r="G96" s="3">
-        <v>1826</v>
-      </c>
-      <c r="H96" s="5">
-        <v>1789</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J96" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L96" s="11" t="s">
-        <v>555</v>
-      </c>
-      <c r="O96" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P96" s="3">
-        <v>61</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>43</v>
-      </c>
-      <c r="R96" s="3">
-        <v>34</v>
-      </c>
-      <c r="S96" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="T96" s="3">
-        <v>3</v>
-      </c>
-      <c r="U96" s="1">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>222</v>
+        <v>120</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>214</v>
+        <v>121</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>223</v>
+        <v>122</v>
       </c>
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
       <c r="F97" s="5" t="s">
-        <v>203</v>
+        <v>38</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>224</v>
+        <v>123</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>553</v>
+        <v>124</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="J97" s="5" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="K97" s="5"/>
       <c r="L97" s="8" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="M97" s="6"/>
       <c r="N97" s="6"/>
@@ -7354,217 +7643,770 @@
         <v>28</v>
       </c>
       <c r="P97" s="5">
-        <v>30</v>
+        <v>220</v>
       </c>
       <c r="Q97" s="5">
-        <v>102</v>
-      </c>
-      <c r="R97" s="5">
-        <v>46.5</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="R97" s="5"/>
       <c r="S97" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="T97" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="D98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G98" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="H98" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="I98" s="5"/>
-      <c r="J98" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="K98" s="5"/>
-      <c r="L98" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="M98" s="6"/>
-      <c r="N98" s="6"/>
-      <c r="O98" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="P98" s="5"/>
-      <c r="Q98" s="5"/>
-      <c r="R98" s="5"/>
-      <c r="S98" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="T98" s="5">
+    <row r="98" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="17" t="s">
+        <v>516</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3">
+        <v>1664</v>
+      </c>
+      <c r="G98" s="3">
+        <v>1714</v>
+      </c>
+      <c r="H98" s="3">
+        <v>1703</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J98" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="L98" s="11" t="s">
+        <v>519</v>
+      </c>
+      <c r="N98" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="O98" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="P98" s="3">
+        <v>290</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>260</v>
+      </c>
+      <c r="R98" s="3">
+        <v>140</v>
+      </c>
+      <c r="S98" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="T98" s="3">
+        <v>1</v>
+      </c>
+      <c r="U98" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3">
+        <v>1656</v>
+      </c>
+      <c r="G99" s="3">
+        <v>1732</v>
+      </c>
+      <c r="H99" s="3">
+        <v>1702</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="J99" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="L99" s="11" t="s">
+        <v>525</v>
+      </c>
+      <c r="N99" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="O99" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="P99" s="3">
+        <v>185</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>72</v>
+      </c>
+      <c r="R99" s="3">
+        <v>50</v>
+      </c>
+      <c r="S99" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="T99" s="3">
+        <v>3</v>
+      </c>
+      <c r="U99" s="1">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3">
+        <v>1656</v>
+      </c>
+      <c r="G100" s="3">
+        <v>1732</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="J100" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="L100" s="11" t="s">
+        <v>531</v>
+      </c>
+      <c r="N100" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="O100" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="P100" s="3">
+        <v>180</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>70</v>
+      </c>
+      <c r="R100" s="3">
+        <v>50</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="T100" s="3">
+        <v>1</v>
+      </c>
+      <c r="U100" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="F101" s="3">
+        <v>1705</v>
+      </c>
+      <c r="G101" s="3">
+        <v>1764</v>
+      </c>
+      <c r="H101" s="3">
+        <v>1750</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J101" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L101" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="N101" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="O101" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P101" s="3">
+        <v>450</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>190</v>
+      </c>
+      <c r="R101" s="3">
+        <v>170</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T101" s="3">
+        <v>1</v>
+      </c>
+      <c r="U101" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="17" t="s">
+        <v>621</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3">
+        <v>1705</v>
+      </c>
+      <c r="G102" s="3">
+        <v>1764</v>
+      </c>
+      <c r="H102" s="3">
+        <v>1755</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J102" s="9" t="s">
+        <v>620</v>
+      </c>
+      <c r="L102" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="O102" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="P102" s="3">
+        <v>320</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>210</v>
+      </c>
+      <c r="R102" s="3">
+        <v>140</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T102" s="3">
+        <v>1</v>
+      </c>
+      <c r="U102" s="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="21" t="s">
+        <v>539</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3">
+        <v>1742</v>
+      </c>
+      <c r="G103" s="3">
+        <v>1826</v>
+      </c>
+      <c r="H103" s="5">
+        <v>1789</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J103" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L103" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="O103" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P103" s="3">
+        <v>61</v>
+      </c>
+      <c r="Q103" s="3">
+        <v>43</v>
+      </c>
+      <c r="R103" s="3">
+        <v>34</v>
+      </c>
+      <c r="S103" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T103" s="3">
+        <v>3</v>
+      </c>
+      <c r="U103" s="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="H104" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="I104" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J104" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K104" s="5"/>
+      <c r="L104" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="M104" s="6"/>
+      <c r="N104" s="6"/>
+      <c r="O104" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P104" s="5">
+        <v>30</v>
+      </c>
+      <c r="Q104" s="5">
+        <v>102</v>
+      </c>
+      <c r="R104" s="5">
+        <v>46.5</v>
+      </c>
+      <c r="S104" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="T104" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="2" t="s">
+    <row r="105" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I105" s="5"/>
+      <c r="J105" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="K105" s="5"/>
+      <c r="L105" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="M105" s="6"/>
+      <c r="N105" s="6"/>
+      <c r="O105" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="P105" s="5">
+        <v>1200</v>
+      </c>
+      <c r="Q105" s="5"/>
+      <c r="R105" s="5"/>
+      <c r="S105" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="T105" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="17" t="s">
+        <v>649</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3">
+        <v>1745</v>
+      </c>
+      <c r="G106" s="3">
+        <v>1809</v>
+      </c>
+      <c r="H106" s="3">
+        <v>1790</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J106" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="L106" s="11" t="s">
+        <v>646</v>
+      </c>
+      <c r="N106" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="O106" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="P106" s="3">
+        <v>52</v>
+      </c>
+      <c r="Q106" s="3">
+        <v>65</v>
+      </c>
+      <c r="R106" s="3">
+        <v>45</v>
+      </c>
+      <c r="S106" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="T106" s="3">
+        <v>2</v>
+      </c>
+      <c r="U106" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3">
+        <v>1727</v>
+      </c>
+      <c r="G107" s="3">
+        <v>1788</v>
+      </c>
+      <c r="H107" s="3">
+        <v>1774</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J107" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="L107" s="11" t="s">
+        <v>666</v>
+      </c>
+      <c r="N107" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="O107" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P107" s="3">
+        <v>54</v>
+      </c>
+      <c r="Q107" s="3">
+        <v>38</v>
+      </c>
+      <c r="R107" s="3">
+        <v>30</v>
+      </c>
+      <c r="S107" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="T107" s="3">
+        <v>1</v>
+      </c>
+      <c r="U107" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D108" s="5"/>
+      <c r="E108" s="5"/>
+      <c r="F108" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G108" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="H108" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C99" s="5" t="s">
+      <c r="I108" s="5"/>
+      <c r="J108" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G99" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="H99" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I99" s="5"/>
-      <c r="J99" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="K99" s="5"/>
-      <c r="L99" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="M99" s="6"/>
-      <c r="N99" s="6"/>
-      <c r="O99" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="P99" s="5"/>
-      <c r="Q99" s="5"/>
-      <c r="R99" s="5"/>
-      <c r="S99" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="T99" s="5">
+      <c r="K108" s="5"/>
+      <c r="L108" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="M108" s="6"/>
+      <c r="N108" s="6"/>
+      <c r="O108" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="P108" s="5">
+        <v>170</v>
+      </c>
+      <c r="Q108" s="5"/>
+      <c r="R108" s="5"/>
+      <c r="S108" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="T108" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="G100" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="H100" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="I100" s="5" t="s">
+    <row r="109" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D109" s="5"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="G109" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="J100" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="K100" s="5"/>
-      <c r="L100" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="M100" s="6"/>
-      <c r="N100" s="6"/>
-      <c r="O100" s="5" t="s">
+      <c r="H109" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="I109" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="J109" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="K109" s="5"/>
+      <c r="L109" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="M109" s="6"/>
+      <c r="N109" s="6"/>
+      <c r="O109" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P100" s="5">
+      <c r="P109" s="5">
         <v>105</v>
       </c>
-      <c r="Q100" s="5">
+      <c r="Q109" s="5">
         <v>75</v>
       </c>
-      <c r="R100" s="5">
+      <c r="R109" s="5">
         <v>41</v>
       </c>
-      <c r="S100" s="5" t="s">
+      <c r="S109" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="T100" s="5">
+      <c r="T109" s="5">
         <v>2</v>
       </c>
     </row>
+    <row r="110" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="17" t="s">
+        <v>677</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="C110" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3">
+        <v>1667</v>
+      </c>
+      <c r="G110" s="3">
+        <v>1737</v>
+      </c>
+      <c r="H110" s="3">
+        <v>1713</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="J110" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="L110" s="11" t="s">
+        <v>681</v>
+      </c>
+      <c r="N110" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="O110" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="P110" s="3">
+        <v>450</v>
+      </c>
+      <c r="Q110" s="3">
+        <v>320</v>
+      </c>
+      <c r="R110" s="3">
+        <v>280</v>
+      </c>
+      <c r="S110" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="T110" s="3">
+        <v>1</v>
+      </c>
+      <c r="U110" s="1">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U100">
-    <sortCondition ref="C2:C100"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U109">
+    <sortCondition ref="C2:C109"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A25" r:id="rId1" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/61/St._Peter%27s_Basilica%2C_Monument_to_Pope_Clement_XIII%2C_by_Antonio_Canova%2C_1792_%2848466617492%29.jpg/960px-St._Peter%27s_Basilica%2C_Monument_to_Pope_Clement_XIII%2C_by_Antonio_Canova%2C_1792_%2848466617492%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{97D8A985-25A8-42F5-AB91-4D34B8D2CF33}"/>
-    <hyperlink ref="A26" r:id="rId2" xr:uid="{0085B750-7165-450F-88C7-C7D74EDB91D2}"/>
-    <hyperlink ref="A27" r:id="rId3" xr:uid="{33115DFF-D6FB-432C-AC20-F8188FC4E845}"/>
-    <hyperlink ref="A28" r:id="rId4" xr:uid="{564A8E9E-A430-4CBD-A867-E8D70CC037F1}"/>
-    <hyperlink ref="A29" r:id="rId5" xr:uid="{47B832C3-5F1F-4664-A39C-56986DEA70FD}"/>
-    <hyperlink ref="A30" r:id="rId6" xr:uid="{6FD1AA65-A962-43F5-9AF8-2782EDB38C99}"/>
+    <hyperlink ref="A26" r:id="rId1" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/61/St._Peter%27s_Basilica%2C_Monument_to_Pope_Clement_XIII%2C_by_Antonio_Canova%2C_1792_%2848466617492%29.jpg/960px-St._Peter%27s_Basilica%2C_Monument_to_Pope_Clement_XIII%2C_by_Antonio_Canova%2C_1792_%2848466617492%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{97D8A985-25A8-42F5-AB91-4D34B8D2CF33}"/>
+    <hyperlink ref="A27" r:id="rId2" xr:uid="{0085B750-7165-450F-88C7-C7D74EDB91D2}"/>
+    <hyperlink ref="A28" r:id="rId3" xr:uid="{33115DFF-D6FB-432C-AC20-F8188FC4E845}"/>
+    <hyperlink ref="A29" r:id="rId4" xr:uid="{564A8E9E-A430-4CBD-A867-E8D70CC037F1}"/>
+    <hyperlink ref="A30" r:id="rId5" xr:uid="{47B832C3-5F1F-4664-A39C-56986DEA70FD}"/>
+    <hyperlink ref="A31" r:id="rId6" xr:uid="{6FD1AA65-A962-43F5-9AF8-2782EDB38C99}"/>
     <hyperlink ref="A12" r:id="rId7" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/ba/Berruer_-_Louis_XV_r%C3%A9compense_la_Peinture_et_la_Sculpture_02.jpg/960px-Berruer_-_Louis_XV_r%C3%A9compense_la_Peinture_et_la_Sculpture_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AC674F25-B516-4210-95DB-2B9BE4FA03D2}"/>
-    <hyperlink ref="A70" r:id="rId8" xr:uid="{07F915D4-1271-41D4-946B-F8A031FBE0FC}"/>
-    <hyperlink ref="A71" r:id="rId9" xr:uid="{6FBBC01C-B5AB-47B6-AFFB-C034C73ABAF2}"/>
-    <hyperlink ref="A72" r:id="rId10" xr:uid="{B8014724-DB41-4117-B03C-CBCF522A04E9}"/>
-    <hyperlink ref="A73" r:id="rId11" xr:uid="{687283BF-7CF3-4ECD-8A40-2FC25BA8E62F}"/>
-    <hyperlink ref="A67" r:id="rId12" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a2/Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg/960px-Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B882B89E-D692-4561-81F4-F9B10455D101}"/>
-    <hyperlink ref="A88" r:id="rId13" xr:uid="{87C77131-7AF2-443C-BE39-DA2381CEF0F2}"/>
-    <hyperlink ref="A78" r:id="rId14" xr:uid="{3981DDB0-AD13-4258-B3E4-558F12031D35}"/>
-    <hyperlink ref="A77" r:id="rId15" xr:uid="{9DF373F2-F34B-4B78-8BB5-19096B52117F}"/>
-    <hyperlink ref="A79" r:id="rId16" xr:uid="{2C298685-B822-4549-8B8B-1A988CC9C92E}"/>
-    <hyperlink ref="A76" r:id="rId17" xr:uid="{F0E9C6C5-DC60-4097-B4E8-6A9CB090D986}"/>
-    <hyperlink ref="A64" r:id="rId18" xr:uid="{3152661E-E9C2-4110-A6F4-B0000F786A7C}"/>
+    <hyperlink ref="A76" r:id="rId8" xr:uid="{07F915D4-1271-41D4-946B-F8A031FBE0FC}"/>
+    <hyperlink ref="A77" r:id="rId9" xr:uid="{6FBBC01C-B5AB-47B6-AFFB-C034C73ABAF2}"/>
+    <hyperlink ref="A78" r:id="rId10" xr:uid="{B8014724-DB41-4117-B03C-CBCF522A04E9}"/>
+    <hyperlink ref="A79" r:id="rId11" xr:uid="{687283BF-7CF3-4ECD-8A40-2FC25BA8E62F}"/>
+    <hyperlink ref="A73" r:id="rId12" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a2/Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg/960px-Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B882B89E-D692-4561-81F4-F9B10455D101}"/>
+    <hyperlink ref="A95" r:id="rId13" xr:uid="{87C77131-7AF2-443C-BE39-DA2381CEF0F2}"/>
+    <hyperlink ref="A84" r:id="rId14" xr:uid="{3981DDB0-AD13-4258-B3E4-558F12031D35}"/>
+    <hyperlink ref="A83" r:id="rId15" xr:uid="{9DF373F2-F34B-4B78-8BB5-19096B52117F}"/>
+    <hyperlink ref="A85" r:id="rId16" xr:uid="{2C298685-B822-4549-8B8B-1A988CC9C92E}"/>
+    <hyperlink ref="A82" r:id="rId17" xr:uid="{F0E9C6C5-DC60-4097-B4E8-6A9CB090D986}"/>
+    <hyperlink ref="A70" r:id="rId18" xr:uid="{3152661E-E9C2-4110-A6F4-B0000F786A7C}"/>
     <hyperlink ref="A15" r:id="rId19" xr:uid="{4B5C2BA1-F0E7-45E3-85F5-52FACA51AEEC}"/>
     <hyperlink ref="A16" r:id="rId20" xr:uid="{E36BBF0A-FDD1-4E1F-B6AF-52B26008603D}"/>
-    <hyperlink ref="A37" r:id="rId21" xr:uid="{12BC5328-FD5C-46EE-BBFA-CC32724C1FF9}"/>
-    <hyperlink ref="A38" r:id="rId22" xr:uid="{59DAD066-FC37-40D1-AE3B-24B67C5BA5DB}"/>
-    <hyperlink ref="A80" r:id="rId23" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Francesco_Queirolo_-_Il_Disinganno_%281753-54%29_-_Detail.jpg/1280px-Francesco_Queirolo_-_Il_Disinganno_%281753-54%29_-_Detail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{E164A41D-A597-4071-A821-F2A3C24D3F2C}"/>
-    <hyperlink ref="A52" r:id="rId24" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/40/Virginia_State_Capitol_complex_-_Houdon%27s_Washington%2C_seen_from_the_front.jpg/960px-Virginia_State_Capitol_complex_-_Houdon%27s_Washington%2C_seen_from_the_front.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7D07FDBD-D83E-44FD-9843-724946F8CF2E}"/>
-    <hyperlink ref="A53" r:id="rId25" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a9/Benjamin_Franklin_by_Jean-Antoine_Houdon_Louvre_RF349_%28001%29.jpg/960px-Benjamin_Franklin_by_Jean-Antoine_Houdon_Louvre_RF349_%28001%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{02EF6FBA-1D59-44C1-81B9-9E02FBFCA15E}"/>
-    <hyperlink ref="A54" r:id="rId26" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Jean_Jacques_Rousseau_-_Jean-Antoine_Houdon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_1729_-_photo_2.jpg/960px-Jean_Jacques_Rousseau_-_Jean-Antoine_Houdon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_1729_-_photo_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{891A227E-7E17-4543-A86F-E151DEDE309A}"/>
-    <hyperlink ref="A74" r:id="rId27" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/WA1216_99_Lower_Belvedere_Apotheosis_of_Prince_Eugene_of_Savoy_3D.jpg/1280px-WA1216_99_Lower_Belvedere_Apotheosis_of_Prince_Eugene_of_Savoy_3D.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{64E12365-8F6F-4867-9D1F-F6D484E30252}"/>
+    <hyperlink ref="A38" r:id="rId21" xr:uid="{12BC5328-FD5C-46EE-BBFA-CC32724C1FF9}"/>
+    <hyperlink ref="A39" r:id="rId22" xr:uid="{59DAD066-FC37-40D1-AE3B-24B67C5BA5DB}"/>
+    <hyperlink ref="A86" r:id="rId23" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Francesco_Queirolo_-_Il_Disinganno_%281753-54%29_-_Detail.jpg/1280px-Francesco_Queirolo_-_Il_Disinganno_%281753-54%29_-_Detail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{E164A41D-A597-4071-A821-F2A3C24D3F2C}"/>
+    <hyperlink ref="A58" r:id="rId24" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/40/Virginia_State_Capitol_complex_-_Houdon%27s_Washington%2C_seen_from_the_front.jpg/960px-Virginia_State_Capitol_complex_-_Houdon%27s_Washington%2C_seen_from_the_front.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7D07FDBD-D83E-44FD-9843-724946F8CF2E}"/>
+    <hyperlink ref="A59" r:id="rId25" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a9/Benjamin_Franklin_by_Jean-Antoine_Houdon_Louvre_RF349_%28001%29.jpg/960px-Benjamin_Franklin_by_Jean-Antoine_Houdon_Louvre_RF349_%28001%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{02EF6FBA-1D59-44C1-81B9-9E02FBFCA15E}"/>
+    <hyperlink ref="A60" r:id="rId26" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Jean_Jacques_Rousseau_-_Jean-Antoine_Houdon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_1729_-_photo_2.jpg/960px-Jean_Jacques_Rousseau_-_Jean-Antoine_Houdon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_1729_-_photo_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{891A227E-7E17-4543-A86F-E151DEDE309A}"/>
+    <hyperlink ref="A80" r:id="rId27" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/WA1216_99_Lower_Belvedere_Apotheosis_of_Prince_Eugene_of_Savoy_3D.jpg/1280px-WA1216_99_Lower_Belvedere_Apotheosis_of_Prince_Eugene_of_Savoy_3D.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{64E12365-8F6F-4867-9D1F-F6D484E30252}"/>
     <hyperlink ref="A4" r:id="rId28" xr:uid="{D7C82055-C52E-45AE-9DBA-19B870EA7238}"/>
     <hyperlink ref="A13" r:id="rId29" xr:uid="{92F5F847-C929-46B0-B7D5-EABFBD5C1062}"/>
-    <hyperlink ref="A11" r:id="rId30" xr:uid="{B840ECC2-059E-4FB4-9C95-020AF3A34BFC}"/>
-    <hyperlink ref="A8" r:id="rId31" xr:uid="{BD82F391-08E2-4580-9316-5F6036E48C50}"/>
-    <hyperlink ref="A10" r:id="rId32" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/24/Monument_to_William_Pitt%2C_Earl_of_Chatham%2C_Westminster_Abbey_02.jpg/1280px-Monument_to_William_Pitt%2C_Earl_of_Chatham%2C_Westminster_Abbey_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{090DEA6E-279F-4E35-9453-E91299BE8DB1}"/>
-    <hyperlink ref="A9" r:id="rId33" xr:uid="{D556DA19-547A-422C-8D59-F79689BBC3AD}"/>
-    <hyperlink ref="A91" r:id="rId34" xr:uid="{DF772C01-846B-46CB-BBB5-54B3A39DFA21}"/>
-    <hyperlink ref="A92" r:id="rId35" xr:uid="{86F08EE4-9192-45E7-B96F-AA2CFF20DED3}"/>
-    <hyperlink ref="A93" r:id="rId36" xr:uid="{DF13CE7F-4EE7-4AC2-911A-28AC8D58DC65}"/>
-    <hyperlink ref="A69" r:id="rId37" xr:uid="{735A23FA-995E-46FA-B865-5B5875BF663B}"/>
-    <hyperlink ref="A96" r:id="rId38" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Louvre_lens_l%27affliction_jean-baptiste_stouf_v_1789_-1.jpg/960px-Louvre_lens_l%27affliction_jean-baptiste_stouf_v_1789_-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4CAA7886-2A7B-4B31-80C6-C94546C79E78}"/>
-    <hyperlink ref="A18" r:id="rId39" xr:uid="{E510A62E-C5C1-4187-BB94-122445CA89D9}"/>
-    <hyperlink ref="A19" r:id="rId40" xr:uid="{B20F13C1-D167-415A-B47F-AF926F0C3CAD}"/>
-    <hyperlink ref="W21" r:id="rId41" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/EdmeBouchardon-FrancoisHubertDrouais.JPG/960px-EdmeBouchardon-FrancoisHubertDrouais.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{695A1C2D-051F-4A6D-9187-F83F25B5D93C}"/>
-    <hyperlink ref="A56" r:id="rId42" xr:uid="{73A207B4-13BA-44CB-8D20-61BB82BA279C}"/>
-    <hyperlink ref="W46" r:id="rId43" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/EdmeBouchardon-FrancoisHubertDrouais.JPG/960px-EdmeBouchardon-FrancoisHubertDrouais.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{177A6C13-47F3-441E-8A4D-77ACBE2C7EE1}"/>
-    <hyperlink ref="A46" r:id="rId44" xr:uid="{EB94FBA9-28BA-4C8B-A988-F9496F21CACF}"/>
-    <hyperlink ref="A66" r:id="rId45" location="/media/File:Austria-00838_-_Empress_Maria_Theresa_(21042592266).jpg" xr:uid="{8D15B4F7-D8DE-41FF-AFC1-6942F522286A}"/>
-    <hyperlink ref="A50" r:id="rId46" xr:uid="{A0D6DDDB-4568-4AE8-9DB6-7F8F191373F7}"/>
-    <hyperlink ref="A57" r:id="rId47" xr:uid="{4A148A4D-BAD5-46E3-B00E-6801D3D7EE62}"/>
-    <hyperlink ref="A83" r:id="rId48" xr:uid="{80CF61D8-9703-4219-BCE7-043C33659633}"/>
-    <hyperlink ref="A20" r:id="rId49" xr:uid="{EDC78297-9DF1-47A1-A85D-5CD7A18A019D}"/>
-    <hyperlink ref="A40" r:id="rId50" xr:uid="{6D89E607-E8D6-4112-8858-1C158E67C1BD}"/>
-    <hyperlink ref="A95" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/%C3%89glise_Saint-Sulpice_de_Paris_Monument_Jean-Baptiste_Languet_de_Gergy.jpg/1280px-%C3%89glise_Saint-Sulpice_de_Paris_Monument_Jean-Baptiste_Languet_de_Gergy.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{25C8C2C4-4F33-4299-90F9-5FC260F89F59}"/>
+    <hyperlink ref="A8" r:id="rId30" xr:uid="{BD82F391-08E2-4580-9316-5F6036E48C50}"/>
+    <hyperlink ref="A10" r:id="rId31" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/24/Monument_to_William_Pitt%2C_Earl_of_Chatham%2C_Westminster_Abbey_02.jpg/1280px-Monument_to_William_Pitt%2C_Earl_of_Chatham%2C_Westminster_Abbey_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{090DEA6E-279F-4E35-9453-E91299BE8DB1}"/>
+    <hyperlink ref="A9" r:id="rId32" xr:uid="{D556DA19-547A-422C-8D59-F79689BBC3AD}"/>
+    <hyperlink ref="A98" r:id="rId33" xr:uid="{DF772C01-846B-46CB-BBB5-54B3A39DFA21}"/>
+    <hyperlink ref="A99" r:id="rId34" xr:uid="{86F08EE4-9192-45E7-B96F-AA2CFF20DED3}"/>
+    <hyperlink ref="A100" r:id="rId35" xr:uid="{DF13CE7F-4EE7-4AC2-911A-28AC8D58DC65}"/>
+    <hyperlink ref="A75" r:id="rId36" xr:uid="{735A23FA-995E-46FA-B865-5B5875BF663B}"/>
+    <hyperlink ref="A103" r:id="rId37" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Louvre_lens_l%27affliction_jean-baptiste_stouf_v_1789_-1.jpg/960px-Louvre_lens_l%27affliction_jean-baptiste_stouf_v_1789_-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4CAA7886-2A7B-4B31-80C6-C94546C79E78}"/>
+    <hyperlink ref="A18" r:id="rId38" xr:uid="{E510A62E-C5C1-4187-BB94-122445CA89D9}"/>
+    <hyperlink ref="A19" r:id="rId39" xr:uid="{B20F13C1-D167-415A-B47F-AF926F0C3CAD}"/>
+    <hyperlink ref="W21" r:id="rId40" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/EdmeBouchardon-FrancoisHubertDrouais.JPG/960px-EdmeBouchardon-FrancoisHubertDrouais.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{695A1C2D-051F-4A6D-9187-F83F25B5D93C}"/>
+    <hyperlink ref="A62" r:id="rId41" xr:uid="{73A207B4-13BA-44CB-8D20-61BB82BA279C}"/>
+    <hyperlink ref="W50" r:id="rId42" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/EdmeBouchardon-FrancoisHubertDrouais.JPG/960px-EdmeBouchardon-FrancoisHubertDrouais.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{177A6C13-47F3-441E-8A4D-77ACBE2C7EE1}"/>
+    <hyperlink ref="A50" r:id="rId43" xr:uid="{EB94FBA9-28BA-4C8B-A988-F9496F21CACF}"/>
+    <hyperlink ref="A72" r:id="rId44" location="/media/File:Austria-00838_-_Empress_Maria_Theresa_(21042592266).jpg" xr:uid="{8D15B4F7-D8DE-41FF-AFC1-6942F522286A}"/>
+    <hyperlink ref="A56" r:id="rId45" xr:uid="{A0D6DDDB-4568-4AE8-9DB6-7F8F191373F7}"/>
+    <hyperlink ref="A63" r:id="rId46" xr:uid="{4A148A4D-BAD5-46E3-B00E-6801D3D7EE62}"/>
+    <hyperlink ref="A90" r:id="rId47" xr:uid="{80CF61D8-9703-4219-BCE7-043C33659633}"/>
+    <hyperlink ref="A20" r:id="rId48" xr:uid="{EDC78297-9DF1-47A1-A85D-5CD7A18A019D}"/>
+    <hyperlink ref="A41" r:id="rId49" xr:uid="{6D89E607-E8D6-4112-8858-1C158E67C1BD}"/>
+    <hyperlink ref="A102" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/%C3%89glise_Saint-Sulpice_de_Paris_Monument_Jean-Baptiste_Languet_de_Gergy.jpg/1280px-%C3%89glise_Saint-Sulpice_de_Paris_Monument_Jean-Baptiste_Languet_de_Gergy.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{25C8C2C4-4F33-4299-90F9-5FC260F89F59}"/>
+    <hyperlink ref="A11" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/21/Thetis_dipping_Achilles_into_the_River_Styx_%2849219058951%29.jpg/1280px-Thetis_dipping_Achilles_into_the_River_Styx_%2849219058951%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6B56F7E3-B4F2-4BCA-90F7-CB2B33A8065F}"/>
+    <hyperlink ref="A5" r:id="rId52" xr:uid="{76D35042-825A-4CF8-BC76-DA445E85ABE2}"/>
+    <hyperlink ref="A14" r:id="rId53" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/Marie-Antoinette%2C_reine_de_France_-_Louis_Boizot_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_4515.jpg/1280px-Marie-Antoinette%2C_reine_de_France_-_Louis_Boizot_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_4515.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EFF1BD6F-96BD-440D-B128-4D0F5A419C91}"/>
+    <hyperlink ref="A89" r:id="rId54" xr:uid="{F76FAC8C-01CA-4532-B5F5-6F6F84CEE2B0}"/>
+    <hyperlink ref="A91" r:id="rId55" xr:uid="{35AF36E4-3878-4F7F-A947-FB78406D2575}"/>
+    <hyperlink ref="A22" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Chartres_-_Cath%C3%A9drale_Notre-Dame_-_L%27Assomption_%28Charles-Antoine_Bridan%29.jpg/960px-Chartres_-_Cath%C3%A9drale_Notre-Dame_-_L%27Assomption_%28Charles-Antoine_Bridan%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{36D8FDD5-F2AB-4FAD-A8A1-FB5C4788CEAB}"/>
+    <hyperlink ref="A52" r:id="rId57" xr:uid="{109BC90B-9DF3-42E9-B979-2BE112F23FB7}"/>
+    <hyperlink ref="A46" r:id="rId58" xr:uid="{4B6430AA-9055-4BD2-88A3-DE5F9053E399}"/>
+    <hyperlink ref="A47" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_177.JPG/960px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_177.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6C4A4583-92AC-41E0-80C7-F8C00255063E}"/>
+    <hyperlink ref="A106" r:id="rId60" xr:uid="{34369B02-D34B-4131-A338-511D7ACF06B8}"/>
+    <hyperlink ref="A53" r:id="rId61" xr:uid="{61309A5B-5C60-4B12-BD40-33E580A62672}"/>
+    <hyperlink ref="A42" r:id="rId62" xr:uid="{5B77419D-BD87-4E18-8412-975EA001E41F}"/>
+    <hyperlink ref="A107" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Bust_of_Moses_Mendelssohn_by_Jean-Pierre-Antoine_Tassaert.jpg/500px-Bust_of_Moses_Mendelssohn_by_Jean-Pierre-Antoine_Tassaert.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7BA96FFB-24B1-483D-AA2F-83C31FC109F7}"/>
+    <hyperlink ref="A87" r:id="rId64" xr:uid="{164E8FBD-B3C1-43AD-B5D6-7B72A57C8B80}"/>
+    <hyperlink ref="A110" r:id="rId65" xr:uid="{3596A210-86AA-42CC-A99A-7E64E20F3043}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers simplifiés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B293C7C5-5F0B-4DA1-9A10-A18DD10F4C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F5AD3F-E7A8-4221-98BA-C133317C19B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="682">
   <si>
     <t>Image</t>
   </si>
@@ -1055,9 +1055,6 @@
     <t>Mercure attachant sa talonnière</t>
   </si>
   <si>
-    <t>La Bacchante courant</t>
-  </si>
-  <si>
     <t>Psyché abandonnée</t>
   </si>
   <si>
@@ -1445,9 +1442,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Int%C3%A9rieur_%C3%89glise_St_Thomas_Strasbourg_114.jpg/1920px-Int%C3%A9rieur_%C3%89glise_St_Thomas_Strasbourg_114.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t xml:space="preserve">Claude </t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d2/Louvre_biscuit.jpg/960px-Louvre_biscuit.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -1781,9 +1775,6 @@
     <t xml:space="preserve">La Providence </t>
   </si>
   <si>
-    <t>https://commons.wikimedia.org/wiki/Category:Tomb_of_Maria_Theresia_of_Austria_and_Francis_I,_Holy_Roman_Emperor#/media/File:Austria-00838_-_Empress_Maria_Theresa_(21042592266).jpg</t>
-  </si>
-  <si>
     <t>Balthasar Ferdinand</t>
   </si>
   <si>
@@ -2085,6 +2076,9 @@
   </si>
   <si>
     <t>Bois de chêne</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/46/Austria-00838_-_Empress_Maria_Theresa_%2821042592266%29.jpg/1280px-Austria-00838_-_Empress_Maria_Theresa_%2821042592266%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -2215,7 +2209,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2246,7 +2240,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
@@ -2584,7 +2577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W110"/>
+  <dimension ref="A1:W109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" style="2" customWidth="1"/>
@@ -2607,7 +2600,7 @@
     <col min="19" max="19" width="12.7109375" style="3" customWidth="1"/>
     <col min="20" max="20" width="6.85546875" style="3" customWidth="1"/>
     <col min="21" max="21" width="12" style="3" customWidth="1"/>
-    <col min="23" max="23" width="9.140625" style="19"/>
+    <col min="23" max="23" width="9.140625" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2672,7 +2665,7 @@
         <v>19</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2702,7 +2695,7 @@
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -2754,7 +2747,7 @@
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
@@ -2778,8 +2771,8 @@
       </c>
     </row>
     <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>481</v>
+      <c r="A4" s="13" t="s">
+        <v>479</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>278</v>
@@ -2800,10 +2793,10 @@
         <v>209</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="O4" s="9" t="s">
         <v>328</v>
@@ -2828,7 +2821,7 @@
       </c>
     </row>
     <row r="5" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>308</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -2856,7 +2849,7 @@
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -2908,7 +2901,7 @@
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
@@ -2959,10 +2952,10 @@
         <v>98</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
@@ -2970,7 +2963,7 @@
         <v>99</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
@@ -2982,14 +2975,14 @@
       </c>
     </row>
     <row r="8" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>504</v>
+      <c r="A8" s="16" t="s">
+        <v>502</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>243</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3">
@@ -3005,16 +2998,16 @@
         <v>171</v>
       </c>
       <c r="J8" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="L8" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="N8" s="9" t="s">
         <v>506</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>507</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>508</v>
       </c>
       <c r="O8" s="9" t="s">
         <v>104</v>
@@ -3029,7 +3022,7 @@
         <v>210</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="T8" s="3">
         <v>2</v>
@@ -3039,14 +3032,14 @@
       </c>
     </row>
     <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
-        <v>512</v>
+      <c r="A9" s="16" t="s">
+        <v>510</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>243</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3">
@@ -3062,13 +3055,13 @@
         <v>171</v>
       </c>
       <c r="J9" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>512</v>
+      </c>
+      <c r="N9" s="9" t="s">
         <v>513</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>514</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>515</v>
       </c>
       <c r="O9" s="9" t="s">
         <v>28</v>
@@ -3083,7 +3076,7 @@
         <v>85</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="T9" s="3">
         <v>3</v>
@@ -3093,14 +3086,14 @@
       </c>
     </row>
     <row r="10" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>509</v>
+      <c r="A10" s="16" t="s">
+        <v>507</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>243</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3">
@@ -3119,10 +3112,10 @@
         <v>264</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="O10" s="9" t="s">
         <v>28</v>
@@ -3137,7 +3130,7 @@
         <v>280</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="T10" s="3">
         <v>3</v>
@@ -3147,14 +3140,14 @@
       </c>
     </row>
     <row r="11" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>622</v>
+      <c r="A11" s="16" t="s">
+        <v>619</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F11" s="3">
         <v>1735</v>
@@ -3168,14 +3161,14 @@
       <c r="I11" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="J11" s="23" t="s">
+      <c r="J11" s="22" t="s">
         <v>172</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>502</v>
-      </c>
-      <c r="N11" s="25" t="s">
-        <v>503</v>
+        <v>500</v>
+      </c>
+      <c r="N11" s="24" t="s">
+        <v>501</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>28</v>
@@ -3190,12 +3183,12 @@
         <v>56</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="T11" s="3">
         <v>2</v>
       </c>
-      <c r="U11" s="18"/>
+      <c r="U11" s="17"/>
     </row>
     <row r="12" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
@@ -3221,15 +3214,15 @@
       <c r="I12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="23" t="s">
         <v>35</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M12" s="6"/>
-      <c r="N12" s="26"/>
+      <c r="N12" s="25"/>
       <c r="O12" s="5" t="s">
         <v>28</v>
       </c>
@@ -3250,8 +3243,8 @@
       </c>
     </row>
     <row r="13" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>495</v>
+      <c r="A13" s="13" t="s">
+        <v>493</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>319</v>
@@ -3269,19 +3262,19 @@
         <v>1773</v>
       </c>
       <c r="I13" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="L13" s="11" t="s">
         <v>497</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="O13" s="9" t="s">
         <v>498</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>499</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>500</v>
       </c>
       <c r="P13" s="3">
         <v>230</v>
@@ -3303,7 +3296,7 @@
       </c>
     </row>
     <row r="14" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="13" t="s">
         <v>283</v>
       </c>
       <c r="B14" s="5" t="s">
@@ -3331,7 +3324,7 @@
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="8" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
@@ -3355,8 +3348,8 @@
       </c>
     </row>
     <row r="15" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>471</v>
+      <c r="A15" s="13" t="s">
+        <v>469</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>284</v>
@@ -3380,10 +3373,10 @@
         <v>35</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="P15" s="3">
         <v>48</v>
@@ -3405,8 +3398,8 @@
       </c>
     </row>
     <row r="16" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>474</v>
+      <c r="A16" s="13" t="s">
+        <v>472</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>284</v>
@@ -3427,10 +3420,10 @@
         <v>209</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="O16" s="9" t="s">
         <v>28</v>
@@ -3455,11 +3448,11 @@
       </c>
     </row>
     <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="19" t="s">
         <v>88</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>89</v>
@@ -3484,7 +3477,7 @@
         <v>338</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>28</v>
@@ -3509,11 +3502,11 @@
       </c>
     </row>
     <row r="18" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
-        <v>544</v>
+      <c r="A18" s="16" t="s">
+        <v>542</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>89</v>
@@ -3535,10 +3528,10 @@
         <v>35</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="N18" s="9" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="O18" s="9" t="s">
         <v>28</v>
@@ -3563,11 +3556,11 @@
       </c>
     </row>
     <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
-        <v>547</v>
+      <c r="A19" s="16" t="s">
+        <v>545</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>89</v>
@@ -3580,22 +3573,22 @@
         <v>1762</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>34</v>
       </c>
       <c r="J19" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="N19" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="O19" s="9" t="s">
         <v>550</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>552</v>
       </c>
       <c r="P19" s="3">
         <v>1200</v>
@@ -3617,14 +3610,14 @@
       </c>
     </row>
     <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
-        <v>612</v>
+      <c r="A20" s="16" t="s">
+        <v>609</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3">
@@ -3643,13 +3636,13 @@
         <v>119</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="N20" s="9" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="O20" s="9" t="s">
         <v>28</v>
@@ -3695,19 +3688,19 @@
         <v>75</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>299</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
       <c r="O21" s="5" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="P21" s="5">
         <v>320</v>
@@ -3722,17 +3715,17 @@
       <c r="T21" s="5">
         <v>2</v>
       </c>
-      <c r="W21" s="22"/>
+      <c r="W21" s="21"/>
     </row>
     <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
-        <v>632</v>
+      <c r="A22" s="16" t="s">
+        <v>629</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3">
@@ -3745,16 +3738,16 @@
         <v>1773</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O22" s="9" t="s">
         <v>28</v>
@@ -3804,7 +3797,7 @@
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
@@ -3852,7 +3845,7 @@
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
@@ -3883,7 +3876,7 @@
         <v>31</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F25" s="3">
         <v>1757</v>
@@ -3930,13 +3923,13 @@
     </row>
     <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F26" s="3">
         <v>1757</v>
@@ -3945,7 +3938,7 @@
         <v>1822</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>118</v>
@@ -3954,10 +3947,10 @@
         <v>27</v>
       </c>
       <c r="L26" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="N26" s="9" t="s">
         <v>356</v>
-      </c>
-      <c r="N26" s="9" t="s">
-        <v>357</v>
       </c>
       <c r="O26" s="9" t="s">
         <v>28</v>
@@ -3983,13 +3976,13 @@
     </row>
     <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F27" s="3">
         <v>1757</v>
@@ -3998,22 +3991,22 @@
         <v>1822</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>171</v>
       </c>
       <c r="J27" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="L27" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="N27" s="9" t="s">
         <v>371</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>372</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>28</v>
@@ -4039,13 +4032,13 @@
     </row>
     <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F28" s="3">
         <v>1757</v>
@@ -4054,19 +4047,19 @@
         <v>1822</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>52</v>
       </c>
       <c r="J28" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="L28" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="L28" s="11" t="s">
+      <c r="N28" s="9" t="s">
         <v>375</v>
-      </c>
-      <c r="N28" s="9" t="s">
-        <v>376</v>
       </c>
       <c r="O28" s="9" t="s">
         <v>28</v>
@@ -4092,13 +4085,13 @@
     </row>
     <row r="29" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F29" s="3">
         <v>1757</v>
@@ -4113,13 +4106,13 @@
         <v>118</v>
       </c>
       <c r="J29" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="L29" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="L29" s="11" t="s">
+      <c r="N29" s="9" t="s">
         <v>378</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>379</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>28</v>
@@ -4145,13 +4138,13 @@
     </row>
     <row r="30" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F30" s="3">
         <v>1757</v>
@@ -4163,16 +4156,16 @@
         <v>1796</v>
       </c>
       <c r="I30" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="L30" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="J30" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="L30" s="11" t="s">
+      <c r="N30" s="9" t="s">
         <v>395</v>
-      </c>
-      <c r="N30" s="9" t="s">
-        <v>396</v>
       </c>
       <c r="O30" s="9" t="s">
         <v>28</v>
@@ -4198,13 +4191,13 @@
     </row>
     <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>31</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F31" s="3">
         <v>1757</v>
@@ -4213,19 +4206,19 @@
         <v>1822</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J31" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="L31" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="L31" s="11" t="s">
+      <c r="N31" s="9" t="s">
         <v>399</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>400</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>28</v>
@@ -4278,7 +4271,7 @@
       </c>
       <c r="K32" s="5"/>
       <c r="L32" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
@@ -4330,7 +4323,7 @@
       </c>
       <c r="K33" s="5"/>
       <c r="L33" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
@@ -4382,7 +4375,7 @@
       </c>
       <c r="K34" s="5"/>
       <c r="L34" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
@@ -4434,7 +4427,7 @@
       </c>
       <c r="K35" s="5"/>
       <c r="L35" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
@@ -4482,11 +4475,11 @@
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M36" s="6"/>
       <c r="N36" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="O36" s="5" t="s">
         <v>28</v>
@@ -4534,7 +4527,7 @@
       </c>
       <c r="K37" s="5"/>
       <c r="L37" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
@@ -4558,14 +4551,14 @@
       </c>
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>477</v>
+      <c r="A38" s="13" t="s">
+        <v>475</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>192</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="F38" s="3">
         <v>1677</v>
@@ -4574,7 +4567,7 @@
         <v>1746</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>34</v>
@@ -4583,10 +4576,10 @@
         <v>35</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="O38" s="9" t="s">
         <v>28</v>
@@ -4611,14 +4604,14 @@
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="13" t="s">
         <v>194</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>192</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -4639,7 +4632,7 @@
       </c>
       <c r="K39" s="5"/>
       <c r="L39" s="8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
@@ -4691,7 +4684,7 @@
       </c>
       <c r="K40" s="5"/>
       <c r="L40" s="8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
@@ -4699,7 +4692,7 @@
         <v>28</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="Q40" s="5"/>
       <c r="R40" s="5"/>
@@ -4711,8 +4704,8 @@
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
-        <v>616</v>
+      <c r="A41" s="16" t="s">
+        <v>613</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>114</v>
@@ -4734,16 +4727,16 @@
         <v>118</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>28</v>
@@ -4768,14 +4761,14 @@
       </c>
     </row>
     <row r="42" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
-        <v>663</v>
+      <c r="A42" s="16" t="s">
+        <v>660</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3">
@@ -4788,16 +4781,16 @@
         <v>1752</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="L42" s="11" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="O42" s="9" t="s">
         <v>28</v>
@@ -4812,7 +4805,7 @@
         <v>90</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="T42" s="3">
         <v>1</v>
@@ -4848,10 +4841,10 @@
         <v>165</v>
       </c>
       <c r="L43" s="11" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>63</v>
@@ -4866,7 +4859,7 @@
         <v>150</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="T43" s="3">
         <v>1</v>
@@ -4876,7 +4869,7 @@
       </c>
     </row>
     <row r="44" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="20" t="s">
+      <c r="A44" s="19" t="s">
         <v>310</v>
       </c>
       <c r="B44" s="5" t="s">
@@ -4904,12 +4897,12 @@
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="M44" s="8"/>
       <c r="N44" s="8"/>
       <c r="O44" s="5" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="P44" s="5">
         <v>250</v>
@@ -4928,7 +4921,7 @@
         <v>100</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>101</v>
@@ -4947,13 +4940,13 @@
         <v>70</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="L45" s="11" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>104</v>
@@ -4978,11 +4971,11 @@
       </c>
     </row>
     <row r="46" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="17" t="s">
-        <v>642</v>
+      <c r="A46" s="16" t="s">
+        <v>639</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>101</v>
@@ -5004,7 +4997,7 @@
         <v>35</v>
       </c>
       <c r="L46" s="11" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="O46" s="9" t="s">
         <v>28</v>
@@ -5029,11 +5022,11 @@
       </c>
     </row>
     <row r="47" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="17" t="s">
-        <v>644</v>
+      <c r="A47" s="16" t="s">
+        <v>641</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>101</v>
@@ -5055,7 +5048,7 @@
         <v>35</v>
       </c>
       <c r="L47" s="11" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>28</v>
@@ -5087,7 +5080,7 @@
         <v>267</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F48" s="3">
         <v>1696</v>
@@ -5096,25 +5089,25 @@
         <v>1770</v>
       </c>
       <c r="H48" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="I48" s="3" t="s">
+      <c r="J48" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="J48" s="9" t="s">
+      <c r="K48" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="K48" s="3" t="s">
+      <c r="L48" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="N48" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="L48" s="11" t="s">
-        <v>458</v>
-      </c>
-      <c r="N48" s="9" t="s">
+      <c r="O48" s="9" t="s">
         <v>388</v>
-      </c>
-      <c r="O48" s="9" t="s">
-        <v>389</v>
       </c>
       <c r="P48" s="3">
         <v>85</v>
@@ -5126,7 +5119,7 @@
         <v>35</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="T48" s="3">
         <v>3</v>
@@ -5164,7 +5157,7 @@
       </c>
       <c r="K49" s="5"/>
       <c r="L49" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
@@ -5188,8 +5181,8 @@
       </c>
     </row>
     <row r="50" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="17" t="s">
-        <v>578</v>
+      <c r="A50" s="16" t="s">
+        <v>576</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>243</v>
@@ -5211,13 +5204,13 @@
         <v>171</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="L50" s="11" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="N50" s="9" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="O50" s="9" t="s">
         <v>28</v>
@@ -5232,7 +5225,7 @@
         <v>110</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="T50" s="3">
         <v>1</v>
@@ -5270,7 +5263,7 @@
       </c>
       <c r="K51" s="5"/>
       <c r="L51" s="8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
@@ -5294,14 +5287,14 @@
       </c>
     </row>
     <row r="52" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="17" t="s">
-        <v>640</v>
+      <c r="A52" s="16" t="s">
+        <v>637</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3">
@@ -5320,7 +5313,7 @@
         <v>35</v>
       </c>
       <c r="L52" s="11" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="O52" s="9" t="s">
         <v>28</v>
@@ -5345,14 +5338,14 @@
       </c>
     </row>
     <row r="53" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="17" t="s">
-        <v>650</v>
+      <c r="A53" s="16" t="s">
+        <v>647</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3">
@@ -5365,16 +5358,16 @@
         <v>1781</v>
       </c>
       <c r="I53" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="L53" s="11" t="s">
         <v>653</v>
-      </c>
-      <c r="J53" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="L53" s="11" t="s">
-        <v>656</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>300</v>
@@ -5389,7 +5382,7 @@
         <v>120</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="T53" s="3">
         <v>1</v>
@@ -5427,7 +5420,7 @@
       </c>
       <c r="K54" s="5"/>
       <c r="L54" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
@@ -5455,10 +5448,10 @@
         <v>196</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F55" s="3">
         <v>1725</v>
@@ -5467,7 +5460,7 @@
         <v>1775</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>144</v>
@@ -5476,13 +5469,13 @@
         <v>145</v>
       </c>
       <c r="L55" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="N55" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="N55" s="9" t="s">
-        <v>393</v>
-      </c>
       <c r="O55" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P55" s="3">
         <v>182</v>
@@ -5494,7 +5487,7 @@
         <v>75</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="T55" s="3">
         <v>3</v>
@@ -5504,14 +5497,14 @@
       </c>
     </row>
     <row r="56" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="17" t="s">
-        <v>594</v>
+      <c r="A56" s="16" t="s">
+        <v>591</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3">
@@ -5524,22 +5517,22 @@
         <v>1763</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="K56" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="N56" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="O56" s="9" t="s">
         <v>344</v>
-      </c>
-      <c r="L56" s="11" t="s">
-        <v>590</v>
-      </c>
-      <c r="N56" s="9" t="s">
-        <v>589</v>
-      </c>
-      <c r="O56" s="9" t="s">
-        <v>345</v>
       </c>
       <c r="P56" s="3">
         <v>165</v>
@@ -5551,7 +5544,7 @@
         <v>85</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="T56" s="3">
         <v>1</v>
@@ -5568,7 +5561,7 @@
         <v>203</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F57" s="3">
         <v>1741</v>
@@ -5614,14 +5607,14 @@
       </c>
     </row>
     <row r="58" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="14" t="s">
-        <v>485</v>
+      <c r="A58" s="13" t="s">
+        <v>483</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>203</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F58" s="3">
         <v>1741</v>
@@ -5633,13 +5626,13 @@
         <v>1788</v>
       </c>
       <c r="I58" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="J58" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="L58" s="11" t="s">
         <v>486</v>
-      </c>
-      <c r="J58" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="L58" s="11" t="s">
-        <v>488</v>
       </c>
       <c r="O58" s="9" t="s">
         <v>28</v>
@@ -5664,14 +5657,14 @@
       </c>
     </row>
     <row r="59" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
-        <v>489</v>
+      <c r="A59" s="13" t="s">
+        <v>487</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>203</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F59" s="3">
         <v>1741</v>
@@ -5689,7 +5682,7 @@
         <v>35</v>
       </c>
       <c r="L59" s="11" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>87</v>
@@ -5714,14 +5707,14 @@
       </c>
     </row>
     <row r="60" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
-        <v>491</v>
+      <c r="A60" s="13" t="s">
+        <v>489</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>203</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F60" s="3">
         <v>1741</v>
@@ -5739,10 +5732,10 @@
         <v>35</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="O60" s="9" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="P60" s="3">
         <v>51</v>
@@ -5771,7 +5764,7 @@
         <v>300</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F61" s="3">
         <v>1731</v>
@@ -5783,13 +5776,13 @@
         <v>1787</v>
       </c>
       <c r="I61" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J61" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="J61" s="9" t="s">
+      <c r="L61" s="11" t="s">
         <v>360</v>
-      </c>
-      <c r="L61" s="11" t="s">
-        <v>361</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>28</v>
@@ -5814,14 +5807,14 @@
       </c>
     </row>
     <row r="62" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="17" t="s">
-        <v>574</v>
+      <c r="A62" s="16" t="s">
+        <v>572</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>300</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3">
@@ -5840,7 +5833,7 @@
         <v>35</v>
       </c>
       <c r="L62" s="11" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="O62" s="9" t="s">
         <v>28</v>
@@ -5865,14 +5858,14 @@
       </c>
     </row>
     <row r="63" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="17" t="s">
-        <v>595</v>
+      <c r="A63" s="16" t="s">
+        <v>592</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>114</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3">
@@ -5885,19 +5878,19 @@
         <v>1730</v>
       </c>
       <c r="I63" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="L63" s="11" t="s">
         <v>597</v>
       </c>
-      <c r="J63" s="9" t="s">
+      <c r="N63" s="9" t="s">
         <v>598</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="L63" s="11" t="s">
-        <v>600</v>
-      </c>
-      <c r="N63" s="9" t="s">
-        <v>601</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>28</v>
@@ -5929,7 +5922,7 @@
         <v>241</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F64" s="3">
         <v>1706</v>
@@ -5938,7 +5931,7 @@
         <v>1775</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>315</v>
@@ -5947,13 +5940,13 @@
         <v>316</v>
       </c>
       <c r="L64" s="11" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N64" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="O64" s="9" t="s">
         <v>382</v>
-      </c>
-      <c r="O64" s="9" t="s">
-        <v>383</v>
       </c>
       <c r="P64" s="3">
         <v>45</v>
@@ -5965,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="T64" s="3">
         <v>3</v>
@@ -6003,7 +5996,7 @@
       </c>
       <c r="K65" s="5"/>
       <c r="L65" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
@@ -6053,7 +6046,7 @@
       </c>
       <c r="K66" s="5"/>
       <c r="L66" s="8" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
@@ -6105,7 +6098,7 @@
       </c>
       <c r="K67" s="5"/>
       <c r="L67" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
@@ -6153,14 +6146,14 @@
       </c>
       <c r="K68" s="5"/>
       <c r="L68" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="M68" s="8" t="s">
         <v>456</v>
-      </c>
-      <c r="M68" s="8" t="s">
-        <v>457</v>
       </c>
       <c r="N68" s="6"/>
       <c r="O68" s="5" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="P68" s="5">
         <v>42</v>
@@ -6179,242 +6172,237 @@
       </c>
     </row>
     <row r="69" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="12"/>
-      <c r="B69" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="C69" s="9" t="s">
+      <c r="A69" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>81</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F69" s="3">
-        <v>1738</v>
-      </c>
-      <c r="G69" s="3">
-        <v>1814</v>
-      </c>
-      <c r="H69" s="3">
-        <v>1782</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J69" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L69" s="11" t="s">
-        <v>340</v>
-      </c>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="K69" s="5"/>
+      <c r="L69" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="M69" s="6"/>
+      <c r="N69" s="6"/>
       <c r="O69" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P69" s="3">
-        <v>46</v>
-      </c>
-      <c r="Q69" s="3">
-        <v>25</v>
-      </c>
-      <c r="R69" s="3">
-        <v>22</v>
-      </c>
-      <c r="S69" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="T69" s="3">
+        <v>87</v>
+      </c>
+      <c r="P69" s="5">
+        <v>58.4</v>
+      </c>
+      <c r="Q69" s="5">
+        <v>27.3</v>
+      </c>
+      <c r="R69" s="5">
+        <v>22.9</v>
+      </c>
+      <c r="S69" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="T69" s="5">
         <v>1</v>
       </c>
-      <c r="U69" s="1">
-        <v>8</v>
-      </c>
     </row>
     <row r="70" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="13" t="s">
-        <v>79</v>
+      <c r="A70" s="19" t="s">
+        <v>215</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>82</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="D70" s="5"/>
       <c r="E70" s="5"/>
       <c r="F70" s="5" t="s">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>84</v>
+        <v>218</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>85</v>
+        <v>219</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="J70" s="5" t="s">
-        <v>628</v>
+        <v>220</v>
       </c>
       <c r="K70" s="5"/>
       <c r="L70" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="M70" s="6"/>
-      <c r="N70" s="6"/>
+        <v>533</v>
+      </c>
+      <c r="M70" s="8"/>
+      <c r="N70" s="8"/>
       <c r="O70" s="5" t="s">
         <v>87</v>
       </c>
       <c r="P70" s="5">
-        <v>58.4</v>
+        <v>34</v>
       </c>
       <c r="Q70" s="5">
-        <v>27.3</v>
+        <v>22</v>
       </c>
       <c r="R70" s="5">
-        <v>22.9</v>
+        <v>25</v>
       </c>
       <c r="S70" s="5" t="s">
         <v>45</v>
       </c>
       <c r="T70" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="16" t="s">
+        <v>681</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3">
+        <v>1717</v>
+      </c>
+      <c r="G71" s="3">
+        <v>1785</v>
+      </c>
+      <c r="H71" s="3">
+        <v>1753</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J71" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>583</v>
+      </c>
+      <c r="N71" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="O71" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="P71" s="3">
+        <v>280</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>310</v>
+      </c>
+      <c r="R71" s="3">
+        <v>190</v>
+      </c>
+      <c r="S71" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="T71" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="I71" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J71" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="K71" s="5"/>
-      <c r="L71" s="8" t="s">
-        <v>535</v>
-      </c>
-      <c r="M71" s="8"/>
-      <c r="N71" s="8"/>
-      <c r="O71" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="P71" s="5">
-        <v>34</v>
-      </c>
-      <c r="Q71" s="5">
-        <v>22</v>
-      </c>
-      <c r="R71" s="5">
-        <v>25</v>
-      </c>
-      <c r="S71" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="T71" s="5">
+      <c r="U71" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="J72" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="K72" s="5"/>
+      <c r="L72" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="M72" s="6"/>
+      <c r="N72" s="6"/>
+      <c r="O72" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P72" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q72" s="5"/>
+      <c r="R72" s="5"/>
+      <c r="S72" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="T72" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="17" t="s">
-        <v>582</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>583</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>584</v>
-      </c>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3">
-        <v>1717</v>
-      </c>
-      <c r="G72" s="3">
-        <v>1785</v>
-      </c>
-      <c r="H72" s="3">
-        <v>1753</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J72" s="9" t="s">
-        <v>585</v>
-      </c>
-      <c r="L72" s="11" t="s">
-        <v>586</v>
-      </c>
-      <c r="N72" s="9" t="s">
-        <v>587</v>
-      </c>
-      <c r="O72" s="9" t="s">
-        <v>588</v>
-      </c>
-      <c r="P72" s="3">
-        <v>280</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>310</v>
-      </c>
-      <c r="R72" s="3">
-        <v>190</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="T72" s="3">
-        <v>1</v>
-      </c>
-      <c r="U72" s="1">
-        <v>19</v>
-      </c>
-    </row>
     <row r="73" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="10" t="s">
-        <v>177</v>
+      <c r="A73" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>167</v>
+        <v>229</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>178</v>
+        <v>230</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
       <c r="F73" s="5" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>179</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="I73" s="5" t="s">
-        <v>181</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="I73" s="5"/>
       <c r="J73" s="5" t="s">
-        <v>182</v>
+        <v>232</v>
       </c>
       <c r="K73" s="5"/>
       <c r="L73" s="8" t="s">
@@ -6423,44 +6411,48 @@
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
       <c r="O73" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P73" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q73" s="5"/>
+        <v>626</v>
+      </c>
+      <c r="P73" s="5">
+        <v>225</v>
+      </c>
+      <c r="Q73" s="5">
+        <v>118</v>
+      </c>
       <c r="R73" s="5"/>
       <c r="S73" s="5" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="T73" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>228</v>
+      <c r="A74" s="13" t="s">
+        <v>272</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>229</v>
+        <v>269</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>230</v>
+        <v>273</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5" t="s">
-        <v>75</v>
+        <v>274</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>179</v>
+        <v>275</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="I74" s="5"/>
+        <v>103</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>171</v>
+      </c>
       <c r="J74" s="5" t="s">
-        <v>232</v>
+        <v>276</v>
       </c>
       <c r="K74" s="5"/>
       <c r="L74" s="8" t="s">
@@ -6469,83 +6461,83 @@
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
       <c r="O74" s="5" t="s">
-        <v>629</v>
+        <v>28</v>
       </c>
       <c r="P74" s="5">
-        <v>225</v>
+        <v>72.7</v>
       </c>
       <c r="Q74" s="5">
-        <v>118</v>
-      </c>
-      <c r="R74" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="R74" s="5">
+        <v>30</v>
+      </c>
       <c r="S74" s="5" t="s">
-        <v>55</v>
+        <v>249</v>
       </c>
       <c r="T74" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="G75" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="H75" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="I75" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="J75" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="K75" s="5"/>
-      <c r="L75" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="M75" s="6"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="5" t="s">
+      <c r="A75" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="F75" s="3">
+        <v>1730</v>
+      </c>
+      <c r="G75" s="3">
+        <v>1809</v>
+      </c>
+      <c r="H75" s="3">
+        <v>1783</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J75" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="O75" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P75" s="5">
-        <v>72.7</v>
-      </c>
-      <c r="Q75" s="5">
-        <v>52</v>
-      </c>
-      <c r="R75" s="5">
-        <v>30</v>
-      </c>
-      <c r="S75" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="T75" s="5">
+      <c r="P75" s="3">
+        <v>178</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>86</v>
+      </c>
+      <c r="R75" s="3">
+        <v>82</v>
+      </c>
+      <c r="S75" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T75" s="3">
         <v>1</v>
+      </c>
+      <c r="U75" s="1">
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>42</v>
+        <v>412</v>
       </c>
       <c r="B76" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F76" s="3">
         <v>1730</v>
@@ -6554,48 +6546,48 @@
         <v>1809</v>
       </c>
       <c r="H76" s="3">
-        <v>1783</v>
+        <v>1773</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>34</v>
+        <v>413</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>35</v>
+        <v>414</v>
       </c>
       <c r="L76" s="11" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="O76" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P76" s="3">
-        <v>178</v>
+        <v>60</v>
       </c>
       <c r="Q76" s="3">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="R76" s="3">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>335</v>
       </c>
       <c r="T76" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U76" s="1">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="77" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>43</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F77" s="3">
         <v>1730</v>
@@ -6604,28 +6596,28 @@
         <v>1809</v>
       </c>
       <c r="H77" s="3">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>414</v>
+        <v>34</v>
       </c>
       <c r="J77" s="9" t="s">
-        <v>415</v>
+        <v>35</v>
       </c>
       <c r="L77" s="11" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P77" s="3">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Q77" s="3">
+        <v>50</v>
+      </c>
+      <c r="R77" s="3">
         <v>45</v>
-      </c>
-      <c r="R77" s="3">
-        <v>32</v>
       </c>
       <c r="S77" s="3" t="s">
         <v>335</v>
@@ -6634,7 +6626,7 @@
         <v>2</v>
       </c>
       <c r="U77" s="1">
-        <v>58</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6645,7 +6637,7 @@
         <v>43</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F78" s="3">
         <v>1730</v>
@@ -6654,7 +6646,7 @@
         <v>1809</v>
       </c>
       <c r="H78" s="3">
-        <v>1775</v>
+        <v>1769</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>34</v>
@@ -6663,16 +6655,16 @@
         <v>35</v>
       </c>
       <c r="L78" s="11" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="O78" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P78" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q78" s="3">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="R78" s="3">
         <v>45</v>
@@ -6681,119 +6673,119 @@
         <v>335</v>
       </c>
       <c r="T78" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U78" s="1">
-        <v>99</v>
+        <v>163</v>
       </c>
     </row>
     <row r="79" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C79" s="9" t="s">
-        <v>561</v>
-      </c>
-      <c r="F79" s="3">
-        <v>1730</v>
-      </c>
-      <c r="G79" s="3">
-        <v>1809</v>
-      </c>
-      <c r="H79" s="3">
-        <v>1769</v>
-      </c>
-      <c r="I79" s="3" t="s">
+      <c r="A79" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K79" s="5"/>
+      <c r="L79" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="M79" s="6"/>
+      <c r="N79" s="6"/>
+      <c r="O79" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P79" s="5">
+        <v>230</v>
+      </c>
+      <c r="Q79" s="5"/>
+      <c r="R79" s="5"/>
+      <c r="S79" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="T79" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="F80" s="3">
+        <v>1714</v>
+      </c>
+      <c r="G80" s="3">
+        <v>1785</v>
+      </c>
+      <c r="H80" s="3">
+        <v>1744</v>
+      </c>
+      <c r="I80" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J79" s="9" t="s">
+      <c r="J80" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="L79" s="11" t="s">
-        <v>405</v>
-      </c>
-      <c r="O79" s="9" t="s">
+      <c r="L80" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="O80" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P79" s="3">
-        <v>76</v>
-      </c>
-      <c r="Q79" s="3">
-        <v>54</v>
-      </c>
-      <c r="R79" s="3">
-        <v>45</v>
-      </c>
-      <c r="S79" s="3" t="s">
+      <c r="P80" s="3">
+        <v>58</v>
+      </c>
+      <c r="Q80" s="3">
+        <v>35</v>
+      </c>
+      <c r="R80" s="3">
+        <v>38</v>
+      </c>
+      <c r="S80" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="T79" s="3">
-        <v>3</v>
-      </c>
-      <c r="U79" s="1">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G80" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H80" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I80" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J80" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="K80" s="5"/>
-      <c r="L80" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="M80" s="6"/>
-      <c r="N80" s="6"/>
-      <c r="O80" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P80" s="5">
-        <v>230</v>
-      </c>
-      <c r="Q80" s="5"/>
-      <c r="R80" s="5"/>
-      <c r="S80" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="T80" s="5">
+      <c r="T80" s="3">
         <v>1</v>
       </c>
+      <c r="U80" s="1">
+        <v>7</v>
+      </c>
     </row>
     <row r="81" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="2" t="s">
-        <v>210</v>
+      <c r="A81" s="10" t="s">
+        <v>468</v>
       </c>
       <c r="B81" s="9" t="s">
         <v>205</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F81" s="3">
         <v>1714</v>
@@ -6801,49 +6793,49 @@
       <c r="G81" s="3">
         <v>1785</v>
       </c>
-      <c r="H81" s="3">
-        <v>1744</v>
+      <c r="H81" s="3" t="s">
+        <v>361</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>34</v>
+        <v>362</v>
       </c>
       <c r="J81" s="9" t="s">
-        <v>35</v>
+        <v>363</v>
       </c>
       <c r="L81" s="11" t="s">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>28</v>
+        <v>349</v>
       </c>
       <c r="P81" s="3">
-        <v>58</v>
+        <v>610</v>
       </c>
       <c r="Q81" s="3">
-        <v>35</v>
+        <v>480</v>
       </c>
       <c r="R81" s="3">
-        <v>38</v>
+        <v>280</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>335</v>
       </c>
       <c r="T81" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U81" s="1">
-        <v>7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="82" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="10" t="s">
-        <v>469</v>
+      <c r="A82" s="12" t="s">
+        <v>464</v>
       </c>
       <c r="B82" s="9" t="s">
         <v>205</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F82" s="3">
         <v>1714</v>
@@ -6851,29 +6843,29 @@
       <c r="G82" s="3">
         <v>1785</v>
       </c>
-      <c r="H82" s="3" t="s">
-        <v>362</v>
+      <c r="H82" s="3">
+        <v>1776</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>363</v>
+        <v>34</v>
       </c>
       <c r="J82" s="9" t="s">
-        <v>364</v>
+        <v>35</v>
       </c>
       <c r="L82" s="11" t="s">
         <v>365</v>
       </c>
       <c r="O82" s="9" t="s">
-        <v>350</v>
+        <v>28</v>
       </c>
       <c r="P82" s="3">
-        <v>610</v>
+        <v>150</v>
       </c>
       <c r="Q82" s="3">
-        <v>480</v>
+        <v>85</v>
       </c>
       <c r="R82" s="3">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="S82" s="3" t="s">
         <v>335</v>
@@ -6882,18 +6874,18 @@
         <v>2</v>
       </c>
       <c r="U82" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="83" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="13" t="s">
-        <v>465</v>
+      <c r="A83" s="10" t="s">
+        <v>463</v>
       </c>
       <c r="B83" s="9" t="s">
         <v>205</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F83" s="3">
         <v>1714</v>
@@ -6902,7 +6894,7 @@
         <v>1785</v>
       </c>
       <c r="H83" s="3">
-        <v>1776</v>
+        <v>1759</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>34</v>
@@ -6917,13 +6909,13 @@
         <v>28</v>
       </c>
       <c r="P83" s="3">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="Q83" s="3">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="R83" s="3">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>335</v>
@@ -6932,18 +6924,18 @@
         <v>2</v>
       </c>
       <c r="U83" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="10" t="s">
-        <v>464</v>
+      <c r="A84" s="12" t="s">
+        <v>466</v>
       </c>
       <c r="B84" s="9" t="s">
         <v>205</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F84" s="3">
         <v>1714</v>
@@ -6952,380 +6944,378 @@
         <v>1785</v>
       </c>
       <c r="H84" s="3">
-        <v>1759</v>
+        <v>1770</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>34</v>
+        <v>465</v>
       </c>
       <c r="J84" s="9" t="s">
-        <v>35</v>
+        <v>403</v>
       </c>
       <c r="L84" s="11" t="s">
-        <v>367</v>
+        <v>467</v>
       </c>
       <c r="O84" s="9" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="P84" s="3">
-        <v>48</v>
+        <v>380</v>
       </c>
       <c r="Q84" s="3">
-        <v>32</v>
+        <v>250</v>
       </c>
       <c r="R84" s="3">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="S84" s="3" t="s">
         <v>335</v>
       </c>
       <c r="T84" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U84" s="1">
-        <v>74</v>
+        <v>158</v>
       </c>
     </row>
     <row r="85" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="13" t="s">
-        <v>467</v>
+      <c r="A85" s="14" t="s">
+        <v>127</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>205</v>
+        <v>128</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F85" s="3">
-        <v>1714</v>
+        <v>1704</v>
       </c>
       <c r="G85" s="3">
-        <v>1785</v>
-      </c>
-      <c r="H85" s="3">
-        <v>1770</v>
+        <v>1762</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>351</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>466</v>
+        <v>40</v>
       </c>
       <c r="J85" s="9" t="s">
-        <v>404</v>
+        <v>41</v>
       </c>
       <c r="L85" s="11" t="s">
-        <v>468</v>
+        <v>417</v>
+      </c>
+      <c r="N85" s="9" t="s">
+        <v>352</v>
       </c>
       <c r="O85" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="P85" s="3">
+        <v>195</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>110</v>
+      </c>
+      <c r="R85" s="3">
+        <v>90</v>
+      </c>
+      <c r="S85" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="T85" s="3">
+        <v>1</v>
+      </c>
+      <c r="U85" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="16" t="s">
+        <v>673</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3">
+        <v>1653</v>
+      </c>
+      <c r="G86" s="3">
+        <v>1686</v>
+      </c>
+      <c r="H86" s="3">
+        <v>1702</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="J86" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="L86" s="11" t="s">
+        <v>669</v>
+      </c>
+      <c r="N86" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="O86" s="9" t="s">
         <v>104</v>
-      </c>
-      <c r="P85" s="3">
-        <v>380</v>
-      </c>
-      <c r="Q85" s="3">
-        <v>250</v>
-      </c>
-      <c r="R85" s="3">
-        <v>240</v>
-      </c>
-      <c r="S85" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="T85" s="3">
-        <v>3</v>
-      </c>
-      <c r="U85" s="1">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="86" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="B86" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C86" s="9" t="s">
-        <v>563</v>
-      </c>
-      <c r="F86" s="3">
-        <v>1704</v>
-      </c>
-      <c r="G86" s="3">
-        <v>1762</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J86" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L86" s="11" t="s">
-        <v>418</v>
-      </c>
-      <c r="N86" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="O86" s="9" t="s">
-        <v>354</v>
       </c>
       <c r="P86" s="3">
         <v>195</v>
       </c>
       <c r="Q86" s="3">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="R86" s="3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="S86" s="3" t="s">
-        <v>331</v>
+        <v>661</v>
       </c>
       <c r="T86" s="3">
         <v>1</v>
       </c>
       <c r="U86" s="1">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="87" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="17" t="s">
-        <v>676</v>
+      <c r="A87" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>675</v>
+        <v>282</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="E87" s="3"/>
+        <v>562</v>
+      </c>
       <c r="F87" s="3">
-        <v>1653</v>
+        <v>1702</v>
       </c>
       <c r="G87" s="3">
-        <v>1686</v>
+        <v>1762</v>
       </c>
       <c r="H87" s="3">
-        <v>1702</v>
+        <v>1761</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>171</v>
       </c>
       <c r="J87" s="9" t="s">
-        <v>673</v>
+        <v>264</v>
       </c>
       <c r="L87" s="11" t="s">
-        <v>672</v>
+        <v>347</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>671</v>
+        <v>348</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="P87" s="3">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="Q87" s="3">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="R87" s="3">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="S87" s="3" t="s">
-        <v>664</v>
+        <v>335</v>
       </c>
       <c r="T87" s="3">
         <v>1</v>
       </c>
       <c r="U87" s="1">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B88" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="C88" s="9" t="s">
-        <v>564</v>
-      </c>
-      <c r="F88" s="3">
-        <v>1702</v>
-      </c>
-      <c r="G88" s="3">
-        <v>1762</v>
-      </c>
-      <c r="H88" s="3">
-        <v>1761</v>
-      </c>
-      <c r="I88" s="3" t="s">
+      <c r="A88" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J88" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="K88" s="5"/>
+      <c r="L88" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="M88" s="6"/>
+      <c r="N88" s="6"/>
+      <c r="O88" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="P88" s="5">
+        <v>84</v>
+      </c>
+      <c r="Q88" s="5"/>
+      <c r="R88" s="5"/>
+      <c r="S88" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="T88" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="16" t="s">
+        <v>603</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3">
+        <v>1658</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1728</v>
+      </c>
+      <c r="H89" s="3">
+        <v>1718</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="L89" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="N89" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="O89" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P89" s="3">
+        <v>420</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>180</v>
+      </c>
+      <c r="R89" s="3">
+        <v>160</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="T89" s="3">
+        <v>1</v>
+      </c>
+      <c r="U89" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="13" t="s">
+        <v>628</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="I90" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="J88" s="9" t="s">
+      <c r="J90" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="L88" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="N88" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="O88" s="9" t="s">
+      <c r="K90" s="5"/>
+      <c r="L90" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="M90" s="6"/>
+      <c r="N90" s="6"/>
+      <c r="O90" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P88" s="3">
-        <v>245</v>
-      </c>
-      <c r="Q88" s="3">
-        <v>150</v>
-      </c>
-      <c r="R88" s="3">
-        <v>95</v>
-      </c>
-      <c r="S88" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="T88" s="3">
+      <c r="P90" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="Q90" s="5"/>
+      <c r="R90" s="5"/>
+      <c r="S90" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="T90" s="5">
         <v>1</v>
       </c>
-      <c r="U88" s="1">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="89" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="H89" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I89" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="J89" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K89" s="5"/>
-      <c r="L89" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="M89" s="6"/>
-      <c r="N89" s="6"/>
-      <c r="O89" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="P89" s="5">
-        <v>84</v>
-      </c>
-      <c r="Q89" s="5"/>
-      <c r="R89" s="5"/>
-      <c r="S89" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T89" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="17" t="s">
-        <v>606</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C90" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3">
-        <v>1658</v>
-      </c>
-      <c r="G90" s="3">
-        <v>1728</v>
-      </c>
-      <c r="H90" s="3">
-        <v>1718</v>
-      </c>
-      <c r="I90" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J90" s="9" t="s">
-        <v>605</v>
-      </c>
-      <c r="L90" s="11" t="s">
-        <v>604</v>
-      </c>
-      <c r="M90" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="N90" s="9" t="s">
-        <v>602</v>
-      </c>
-      <c r="O90" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P90" s="3">
-        <v>420</v>
-      </c>
-      <c r="Q90" s="3">
-        <v>180</v>
-      </c>
-      <c r="R90" s="3">
-        <v>160</v>
-      </c>
-      <c r="S90" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="T90" s="3">
-        <v>1</v>
-      </c>
-      <c r="U90" s="1">
-        <v>26</v>
-      </c>
     </row>
     <row r="91" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="14" t="s">
-        <v>631</v>
+      <c r="A91" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>259</v>
+        <v>198</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>260</v>
+        <v>199</v>
       </c>
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
       <c r="F91" s="5" t="s">
-        <v>261</v>
+        <v>200</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>263</v>
+        <v>185</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>171</v>
+        <v>34</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>264</v>
+        <v>35</v>
       </c>
       <c r="K91" s="5"/>
       <c r="L91" s="8" t="s">
@@ -7336,44 +7326,48 @@
       <c r="O91" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P91" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="Q91" s="5"/>
-      <c r="R91" s="5"/>
+      <c r="P91" s="5">
+        <v>97</v>
+      </c>
+      <c r="Q91" s="5">
+        <v>46</v>
+      </c>
+      <c r="R91" s="5">
+        <v>34</v>
+      </c>
       <c r="S91" s="5" t="s">
-        <v>265</v>
+        <v>45</v>
       </c>
       <c r="T91" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>197</v>
+        <v>130</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>199</v>
+        <v>132</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5" t="s">
-        <v>200</v>
+        <v>133</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>35</v>
+        <v>137</v>
       </c>
       <c r="K92" s="5"/>
       <c r="L92" s="8" t="s">
@@ -7382,19 +7376,19 @@
       <c r="M92" s="6"/>
       <c r="N92" s="6"/>
       <c r="O92" s="5" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="P92" s="5">
-        <v>97</v>
+        <v>246</v>
       </c>
       <c r="Q92" s="5">
-        <v>46</v>
+        <v>442</v>
       </c>
       <c r="R92" s="5">
-        <v>34</v>
+        <v>247</v>
       </c>
       <c r="S92" s="5" t="s">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="T92" s="5">
         <v>2</v>
@@ -7402,65 +7396,66 @@
     </row>
     <row r="93" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G93" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H93" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I93" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="J93" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="K93" s="5"/>
-      <c r="L93" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="M93" s="6"/>
-      <c r="N93" s="6"/>
-      <c r="O93" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="P93" s="5">
-        <v>246</v>
-      </c>
-      <c r="Q93" s="5">
-        <v>442</v>
-      </c>
-      <c r="R93" s="5">
-        <v>247</v>
-      </c>
-      <c r="S93" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="T93" s="5">
-        <v>2</v>
+        <v>183</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="F93" s="3">
+        <v>1720</v>
+      </c>
+      <c r="G93" s="3">
+        <v>1793</v>
+      </c>
+      <c r="H93" s="3">
+        <v>1753</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J93" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L93" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="N93" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="O93" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="P93" s="3">
+        <v>50</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>180</v>
+      </c>
+      <c r="R93" s="3">
+        <v>80</v>
+      </c>
+      <c r="S93" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="T93" s="3">
+        <v>1</v>
+      </c>
+      <c r="U93" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>183</v>
+      <c r="A94" s="10" t="s">
+        <v>418</v>
       </c>
       <c r="B94" s="9" t="s">
         <v>184</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F94" s="3">
         <v>1720</v>
@@ -7469,121 +7464,116 @@
         <v>1793</v>
       </c>
       <c r="H94" s="3">
-        <v>1753</v>
+        <v>1760</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>40</v>
       </c>
       <c r="J94" s="9" t="s">
-        <v>41</v>
+        <v>400</v>
       </c>
       <c r="L94" s="11" t="s">
-        <v>336</v>
+        <v>401</v>
       </c>
       <c r="N94" s="9" t="s">
-        <v>337</v>
+        <v>402</v>
       </c>
       <c r="O94" s="9" t="s">
         <v>28</v>
       </c>
       <c r="P94" s="3">
-        <v>50</v>
+        <v>196</v>
       </c>
       <c r="Q94" s="3">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="R94" s="3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>331</v>
       </c>
       <c r="T94" s="3">
+        <v>3</v>
+      </c>
+      <c r="U94" s="1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="J95" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="K95" s="5"/>
+      <c r="L95" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="M95" s="6"/>
+      <c r="N95" s="6"/>
+      <c r="O95" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P95" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q95" s="5"/>
+      <c r="R95" s="5"/>
+      <c r="S95" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="T95" s="5">
         <v>1</v>
-      </c>
-      <c r="U94" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="B95" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="C95" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="F95" s="3">
-        <v>1720</v>
-      </c>
-      <c r="G95" s="3">
-        <v>1793</v>
-      </c>
-      <c r="H95" s="3">
-        <v>1760</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J95" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="L95" s="11" t="s">
-        <v>402</v>
-      </c>
-      <c r="N95" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="O95" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P95" s="3">
-        <v>196</v>
-      </c>
-      <c r="Q95" s="3">
-        <v>110</v>
-      </c>
-      <c r="R95" s="3">
-        <v>85</v>
-      </c>
-      <c r="S95" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="T95" s="3">
-        <v>3</v>
-      </c>
-      <c r="U95" s="1">
-        <v>146</v>
       </c>
     </row>
     <row r="96" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>251</v>
+        <v>121</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>252</v>
+        <v>122</v>
       </c>
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
       <c r="F96" s="5" t="s">
-        <v>253</v>
+        <v>38</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>254</v>
+        <v>123</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>255</v>
+        <v>124</v>
       </c>
       <c r="I96" s="5" t="s">
-        <v>256</v>
+        <v>125</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>257</v>
+        <v>126</v>
       </c>
       <c r="K96" s="5"/>
       <c r="L96" s="8" t="s">
@@ -7594,131 +7584,137 @@
       <c r="O96" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P96" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q96" s="5"/>
+      <c r="P96" s="5">
+        <v>220</v>
+      </c>
+      <c r="Q96" s="5">
+        <v>100</v>
+      </c>
       <c r="R96" s="5"/>
       <c r="S96" s="5" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="T96" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3">
+        <v>1664</v>
+      </c>
+      <c r="G97" s="3">
+        <v>1714</v>
+      </c>
+      <c r="H97" s="3">
+        <v>1703</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J97" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="L97" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="N97" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="O97" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="P97" s="3">
+        <v>290</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>260</v>
+      </c>
+      <c r="R97" s="3">
+        <v>140</v>
+      </c>
+      <c r="S97" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="T97" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D97" s="5"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="H97" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="I97" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="J97" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="K97" s="5"/>
-      <c r="L97" s="8" t="s">
-        <v>449</v>
-      </c>
-      <c r="M97" s="6"/>
-      <c r="N97" s="6"/>
-      <c r="O97" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P97" s="5">
-        <v>220</v>
-      </c>
-      <c r="Q97" s="5">
-        <v>100</v>
-      </c>
-      <c r="R97" s="5"/>
-      <c r="S97" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T97" s="5">
-        <v>2</v>
+      <c r="U97" s="1">
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="17" t="s">
-        <v>516</v>
+      <c r="A98" s="16" t="s">
+        <v>519</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="3">
-        <v>1664</v>
+        <v>1656</v>
       </c>
       <c r="G98" s="3">
-        <v>1714</v>
+        <v>1732</v>
       </c>
       <c r="H98" s="3">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>256</v>
+        <v>521</v>
       </c>
       <c r="J98" s="9" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="L98" s="11" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N98" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="O98" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="P98" s="3">
+        <v>185</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>72</v>
+      </c>
+      <c r="R98" s="3">
+        <v>50</v>
+      </c>
+      <c r="S98" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="T98" s="3">
+        <v>3</v>
+      </c>
+      <c r="U98" s="1">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="16" t="s">
+        <v>526</v>
+      </c>
+      <c r="B99" s="9" t="s">
         <v>520</v>
       </c>
-      <c r="O98" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="P98" s="3">
-        <v>290</v>
-      </c>
-      <c r="Q98" s="3">
-        <v>260</v>
-      </c>
-      <c r="R98" s="3">
-        <v>140</v>
-      </c>
-      <c r="S98" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="T98" s="3">
-        <v>1</v>
-      </c>
-      <c r="U98" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="99" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="17" t="s">
-        <v>521</v>
-      </c>
-      <c r="B99" s="9" t="s">
-        <v>522</v>
-      </c>
       <c r="C99" s="9" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3">
@@ -7727,29 +7723,29 @@
       <c r="G99" s="3">
         <v>1732</v>
       </c>
-      <c r="H99" s="3">
-        <v>1702</v>
+      <c r="H99" s="3" t="s">
+        <v>527</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="J99" s="9" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="L99" s="11" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="P99" s="3">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="Q99" s="3">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R99" s="3">
         <v>50</v>
@@ -7758,79 +7754,82 @@
         <v>331</v>
       </c>
       <c r="T99" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U99" s="1">
-        <v>203</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="17" t="s">
-        <v>528</v>
+      <c r="A100" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>522</v>
+        <v>481</v>
       </c>
       <c r="C100" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="D100" s="9" t="s">
         <v>567</v>
       </c>
-      <c r="E100" s="3"/>
       <c r="F100" s="3">
-        <v>1656</v>
+        <v>1705</v>
       </c>
       <c r="G100" s="3">
-        <v>1732</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>529</v>
+        <v>1764</v>
+      </c>
+      <c r="H100" s="3">
+        <v>1750</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>523</v>
+        <v>118</v>
       </c>
       <c r="J100" s="9" t="s">
-        <v>530</v>
+        <v>27</v>
       </c>
       <c r="L100" s="11" t="s">
-        <v>531</v>
+        <v>345</v>
       </c>
       <c r="N100" s="9" t="s">
-        <v>532</v>
+        <v>346</v>
       </c>
       <c r="O100" s="9" t="s">
-        <v>533</v>
+        <v>28</v>
       </c>
       <c r="P100" s="3">
-        <v>180</v>
+        <v>450</v>
       </c>
       <c r="Q100" s="3">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="R100" s="3">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="S100" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="T100" s="3">
         <v>1</v>
       </c>
       <c r="U100" s="1">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="2" t="s">
-        <v>302</v>
+      <c r="A101" s="16" t="s">
+        <v>618</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>569</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="E101" s="3"/>
       <c r="F101" s="3">
         <v>1705</v>
       </c>
@@ -7838,31 +7837,28 @@
         <v>1764</v>
       </c>
       <c r="H101" s="3">
-        <v>1750</v>
+        <v>1755</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="J101" s="9" t="s">
-        <v>27</v>
+        <v>617</v>
       </c>
       <c r="L101" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="N101" s="9" t="s">
-        <v>347</v>
+        <v>616</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>28</v>
+        <v>349</v>
       </c>
       <c r="P101" s="3">
-        <v>450</v>
+        <v>320</v>
       </c>
       <c r="Q101" s="3">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="R101" s="3">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>335</v>
@@ -7871,140 +7867,136 @@
         <v>1</v>
       </c>
       <c r="U101" s="1">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="102" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="17" t="s">
-        <v>621</v>
+      <c r="A102" s="20" t="s">
+        <v>537</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>483</v>
+        <v>205</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="D102" s="9" t="s">
-        <v>484</v>
+        <v>213</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3">
-        <v>1705</v>
+        <v>1742</v>
       </c>
       <c r="G102" s="3">
-        <v>1764</v>
-      </c>
-      <c r="H102" s="3">
-        <v>1755</v>
+        <v>1826</v>
+      </c>
+      <c r="H102" s="5">
+        <v>1789</v>
       </c>
       <c r="I102" s="3" t="s">
         <v>34</v>
       </c>
       <c r="J102" s="9" t="s">
-        <v>620</v>
+        <v>35</v>
       </c>
       <c r="L102" s="11" t="s">
-        <v>619</v>
+        <v>538</v>
       </c>
       <c r="O102" s="9" t="s">
-        <v>350</v>
+        <v>28</v>
       </c>
       <c r="P102" s="3">
-        <v>320</v>
+        <v>61</v>
       </c>
       <c r="Q102" s="3">
-        <v>210</v>
+        <v>43</v>
       </c>
       <c r="R102" s="3">
-        <v>140</v>
+        <v>34</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>335</v>
       </c>
       <c r="T102" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U102" s="1">
-        <v>33</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="21" t="s">
-        <v>539</v>
-      </c>
-      <c r="B103" s="9" t="s">
+      <c r="A103" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C103" s="9" t="s">
+      <c r="C103" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3">
-        <v>1742</v>
-      </c>
-      <c r="G103" s="3">
-        <v>1826</v>
-      </c>
-      <c r="H103" s="5">
-        <v>1789</v>
-      </c>
-      <c r="I103" s="3" t="s">
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="H103" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="I103" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J103" s="9" t="s">
+      <c r="J103" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="L103" s="11" t="s">
-        <v>540</v>
-      </c>
-      <c r="O103" s="9" t="s">
+      <c r="K103" s="5"/>
+      <c r="L103" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="M103" s="6"/>
+      <c r="N103" s="6"/>
+      <c r="O103" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="P103" s="3">
-        <v>61</v>
-      </c>
-      <c r="Q103" s="3">
-        <v>43</v>
-      </c>
-      <c r="R103" s="3">
-        <v>34</v>
-      </c>
-      <c r="S103" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="T103" s="3">
-        <v>3</v>
-      </c>
-      <c r="U103" s="1">
-        <v>103</v>
+      <c r="P103" s="5">
+        <v>30</v>
+      </c>
+      <c r="Q103" s="5">
+        <v>102</v>
+      </c>
+      <c r="R103" s="5">
+        <v>46.5</v>
+      </c>
+      <c r="S103" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="T103" s="5">
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D104" s="5"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5" t="s">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="I104" s="5" t="s">
-        <v>34</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="I104" s="5"/>
       <c r="J104" s="5" t="s">
-        <v>35</v>
+        <v>238</v>
       </c>
       <c r="K104" s="5"/>
       <c r="L104" s="8" t="s">
@@ -8013,202 +8005,200 @@
       <c r="M104" s="6"/>
       <c r="N104" s="6"/>
       <c r="O104" s="5" t="s">
-        <v>28</v>
+        <v>239</v>
       </c>
       <c r="P104" s="5">
-        <v>30</v>
-      </c>
-      <c r="Q104" s="5">
-        <v>102</v>
-      </c>
-      <c r="R104" s="5">
-        <v>46.5</v>
-      </c>
+        <v>1200</v>
+      </c>
+      <c r="Q104" s="5"/>
+      <c r="R104" s="5"/>
       <c r="S104" s="5" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T104" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D105" s="5"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="G105" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="H105" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="I105" s="5"/>
-      <c r="J105" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="K105" s="5"/>
-      <c r="L105" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="M105" s="6"/>
-      <c r="N105" s="6"/>
-      <c r="O105" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="P105" s="5">
-        <v>1200</v>
-      </c>
-      <c r="Q105" s="5"/>
-      <c r="R105" s="5"/>
-      <c r="S105" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="T105" s="5">
+      <c r="A105" s="16" t="s">
+        <v>646</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3">
+        <v>1745</v>
+      </c>
+      <c r="G105" s="3">
+        <v>1809</v>
+      </c>
+      <c r="H105" s="3">
+        <v>1790</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J105" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="L105" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="N105" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="O105" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="P105" s="3">
+        <v>52</v>
+      </c>
+      <c r="Q105" s="3">
+        <v>65</v>
+      </c>
+      <c r="R105" s="3">
+        <v>45</v>
+      </c>
+      <c r="S105" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="T105" s="3">
         <v>2</v>
       </c>
+      <c r="U105" s="1">
+        <v>75</v>
+      </c>
     </row>
     <row r="106" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="17" t="s">
-        <v>649</v>
+      <c r="A106" s="16" t="s">
+        <v>667</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>114</v>
+        <v>666</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>648</v>
+        <v>665</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="3">
-        <v>1745</v>
+        <v>1727</v>
       </c>
       <c r="G106" s="3">
-        <v>1809</v>
+        <v>1788</v>
       </c>
       <c r="H106" s="3">
-        <v>1790</v>
+        <v>1774</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>40</v>
+        <v>256</v>
       </c>
       <c r="J106" s="9" t="s">
-        <v>647</v>
+        <v>664</v>
       </c>
       <c r="L106" s="11" t="s">
-        <v>646</v>
+        <v>663</v>
       </c>
       <c r="N106" s="9" t="s">
-        <v>645</v>
+        <v>662</v>
       </c>
       <c r="O106" s="9" t="s">
-        <v>473</v>
+        <v>28</v>
       </c>
       <c r="P106" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q106" s="3">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="R106" s="3">
+        <v>30</v>
+      </c>
+      <c r="S106" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="T106" s="3">
+        <v>1</v>
+      </c>
+      <c r="U106" s="1">
         <v>45</v>
       </c>
-      <c r="S106" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="T106" s="3">
+    </row>
+    <row r="107" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D107" s="5"/>
+      <c r="E107" s="5"/>
+      <c r="F107" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="H107" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="I107" s="5"/>
+      <c r="J107" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="K107" s="5"/>
+      <c r="L107" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="M107" s="6"/>
+      <c r="N107" s="6"/>
+      <c r="O107" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="P107" s="5">
+        <v>170</v>
+      </c>
+      <c r="Q107" s="5"/>
+      <c r="R107" s="5"/>
+      <c r="S107" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="T107" s="5">
         <v>2</v>
-      </c>
-      <c r="U106" s="1">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="107" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="17" t="s">
-        <v>670</v>
-      </c>
-      <c r="B107" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="C107" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="E107" s="3"/>
-      <c r="F107" s="3">
-        <v>1727</v>
-      </c>
-      <c r="G107" s="3">
-        <v>1788</v>
-      </c>
-      <c r="H107" s="3">
-        <v>1774</v>
-      </c>
-      <c r="I107" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="J107" s="9" t="s">
-        <v>667</v>
-      </c>
-      <c r="L107" s="11" t="s">
-        <v>666</v>
-      </c>
-      <c r="N107" s="9" t="s">
-        <v>665</v>
-      </c>
-      <c r="O107" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="P107" s="3">
-        <v>54</v>
-      </c>
-      <c r="Q107" s="3">
-        <v>38</v>
-      </c>
-      <c r="R107" s="3">
-        <v>30</v>
-      </c>
-      <c r="S107" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="T107" s="3">
-        <v>1</v>
-      </c>
-      <c r="U107" s="1">
-        <v>45</v>
       </c>
     </row>
     <row r="108" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>107</v>
+        <v>187</v>
       </c>
       <c r="D108" s="5"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5" t="s">
-        <v>108</v>
+        <v>188</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>109</v>
+        <v>189</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="I108" s="5"/>
+        <v>190</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>181</v>
+      </c>
       <c r="J108" s="5" t="s">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="K108" s="5"/>
       <c r="L108" s="8" t="s">
@@ -8217,129 +8207,81 @@
       <c r="M108" s="6"/>
       <c r="N108" s="6"/>
       <c r="O108" s="5" t="s">
-        <v>534</v>
+        <v>28</v>
       </c>
       <c r="P108" s="5">
-        <v>170</v>
-      </c>
-      <c r="Q108" s="5"/>
-      <c r="R108" s="5"/>
+        <v>105</v>
+      </c>
+      <c r="Q108" s="5">
+        <v>75</v>
+      </c>
+      <c r="R108" s="5">
+        <v>41</v>
+      </c>
       <c r="S108" s="5" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="T108" s="5">
         <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D109" s="5"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="G109" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="H109" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="I109" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="J109" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="K109" s="5"/>
-      <c r="L109" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="M109" s="6"/>
-      <c r="N109" s="6"/>
-      <c r="O109" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P109" s="5">
-        <v>105</v>
-      </c>
-      <c r="Q109" s="5">
-        <v>75</v>
-      </c>
-      <c r="R109" s="5">
-        <v>41</v>
-      </c>
-      <c r="S109" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T109" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="17" t="s">
+      <c r="A109" s="16" t="s">
+        <v>674</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3">
+        <v>1667</v>
+      </c>
+      <c r="G109" s="3">
+        <v>1737</v>
+      </c>
+      <c r="H109" s="3">
+        <v>1713</v>
+      </c>
+      <c r="I109" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="B110" s="9" t="s">
+      <c r="J109" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="L109" s="11" t="s">
         <v>678</v>
       </c>
-      <c r="C110" s="9" t="s">
+      <c r="N109" s="9" t="s">
         <v>679</v>
       </c>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3">
-        <v>1667</v>
-      </c>
-      <c r="G110" s="3">
-        <v>1737</v>
-      </c>
-      <c r="H110" s="3">
-        <v>1713</v>
-      </c>
-      <c r="I110" s="3" t="s">
+      <c r="O109" s="9" t="s">
         <v>680</v>
       </c>
-      <c r="J110" s="9" t="s">
-        <v>636</v>
-      </c>
-      <c r="L110" s="11" t="s">
-        <v>681</v>
-      </c>
-      <c r="N110" s="9" t="s">
-        <v>682</v>
-      </c>
-      <c r="O110" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="P110" s="3">
+      <c r="P109" s="3">
         <v>450</v>
       </c>
-      <c r="Q110" s="3">
+      <c r="Q109" s="3">
         <v>320</v>
       </c>
-      <c r="R110" s="3">
+      <c r="R109" s="3">
         <v>280</v>
       </c>
-      <c r="S110" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="T110" s="3">
+      <c r="S109" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="T109" s="3">
         <v>1</v>
       </c>
-      <c r="U110" s="1">
+      <c r="U109" s="1">
         <v>47</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U109">
-    <sortCondition ref="C2:C109"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U108">
+    <sortCondition ref="C2:C108"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="A26" r:id="rId1" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/61/St._Peter%27s_Basilica%2C_Monument_to_Pope_Clement_XIII%2C_by_Antonio_Canova%2C_1792_%2848466617492%29.jpg/960px-St._Peter%27s_Basilica%2C_Monument_to_Pope_Clement_XIII%2C_by_Antonio_Canova%2C_1792_%2848466617492%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{97D8A985-25A8-42F5-AB91-4D34B8D2CF33}"/>
@@ -8349,64 +8291,64 @@
     <hyperlink ref="A30" r:id="rId5" xr:uid="{47B832C3-5F1F-4664-A39C-56986DEA70FD}"/>
     <hyperlink ref="A31" r:id="rId6" xr:uid="{6FD1AA65-A962-43F5-9AF8-2782EDB38C99}"/>
     <hyperlink ref="A12" r:id="rId7" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/ba/Berruer_-_Louis_XV_r%C3%A9compense_la_Peinture_et_la_Sculpture_02.jpg/960px-Berruer_-_Louis_XV_r%C3%A9compense_la_Peinture_et_la_Sculpture_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AC674F25-B516-4210-95DB-2B9BE4FA03D2}"/>
-    <hyperlink ref="A76" r:id="rId8" xr:uid="{07F915D4-1271-41D4-946B-F8A031FBE0FC}"/>
-    <hyperlink ref="A77" r:id="rId9" xr:uid="{6FBBC01C-B5AB-47B6-AFFB-C034C73ABAF2}"/>
-    <hyperlink ref="A78" r:id="rId10" xr:uid="{B8014724-DB41-4117-B03C-CBCF522A04E9}"/>
-    <hyperlink ref="A79" r:id="rId11" xr:uid="{687283BF-7CF3-4ECD-8A40-2FC25BA8E62F}"/>
-    <hyperlink ref="A73" r:id="rId12" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a2/Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg/960px-Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B882B89E-D692-4561-81F4-F9B10455D101}"/>
-    <hyperlink ref="A95" r:id="rId13" xr:uid="{87C77131-7AF2-443C-BE39-DA2381CEF0F2}"/>
-    <hyperlink ref="A84" r:id="rId14" xr:uid="{3981DDB0-AD13-4258-B3E4-558F12031D35}"/>
-    <hyperlink ref="A83" r:id="rId15" xr:uid="{9DF373F2-F34B-4B78-8BB5-19096B52117F}"/>
-    <hyperlink ref="A85" r:id="rId16" xr:uid="{2C298685-B822-4549-8B8B-1A988CC9C92E}"/>
-    <hyperlink ref="A82" r:id="rId17" xr:uid="{F0E9C6C5-DC60-4097-B4E8-6A9CB090D986}"/>
-    <hyperlink ref="A70" r:id="rId18" xr:uid="{3152661E-E9C2-4110-A6F4-B0000F786A7C}"/>
+    <hyperlink ref="A75" r:id="rId8" xr:uid="{07F915D4-1271-41D4-946B-F8A031FBE0FC}"/>
+    <hyperlink ref="A76" r:id="rId9" xr:uid="{6FBBC01C-B5AB-47B6-AFFB-C034C73ABAF2}"/>
+    <hyperlink ref="A77" r:id="rId10" xr:uid="{B8014724-DB41-4117-B03C-CBCF522A04E9}"/>
+    <hyperlink ref="A78" r:id="rId11" xr:uid="{687283BF-7CF3-4ECD-8A40-2FC25BA8E62F}"/>
+    <hyperlink ref="A72" r:id="rId12" display="https://upload.wikimedia.org/wikipedia/commons/thumb/a/a2/Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg/960px-Interior_of_Chiesa_dei_Gesuiti_%28Venice%29_-_right_nave_-_St._Barbara_by_Giovanni_Maria_Morlaiter.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B882B89E-D692-4561-81F4-F9B10455D101}"/>
+    <hyperlink ref="A94" r:id="rId13" xr:uid="{87C77131-7AF2-443C-BE39-DA2381CEF0F2}"/>
+    <hyperlink ref="A83" r:id="rId14" xr:uid="{3981DDB0-AD13-4258-B3E4-558F12031D35}"/>
+    <hyperlink ref="A82" r:id="rId15" xr:uid="{9DF373F2-F34B-4B78-8BB5-19096B52117F}"/>
+    <hyperlink ref="A84" r:id="rId16" xr:uid="{2C298685-B822-4549-8B8B-1A988CC9C92E}"/>
+    <hyperlink ref="A81" r:id="rId17" xr:uid="{F0E9C6C5-DC60-4097-B4E8-6A9CB090D986}"/>
+    <hyperlink ref="A69" r:id="rId18" xr:uid="{3152661E-E9C2-4110-A6F4-B0000F786A7C}"/>
     <hyperlink ref="A15" r:id="rId19" xr:uid="{4B5C2BA1-F0E7-45E3-85F5-52FACA51AEEC}"/>
     <hyperlink ref="A16" r:id="rId20" xr:uid="{E36BBF0A-FDD1-4E1F-B6AF-52B26008603D}"/>
     <hyperlink ref="A38" r:id="rId21" xr:uid="{12BC5328-FD5C-46EE-BBFA-CC32724C1FF9}"/>
     <hyperlink ref="A39" r:id="rId22" xr:uid="{59DAD066-FC37-40D1-AE3B-24B67C5BA5DB}"/>
-    <hyperlink ref="A86" r:id="rId23" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Francesco_Queirolo_-_Il_Disinganno_%281753-54%29_-_Detail.jpg/1280px-Francesco_Queirolo_-_Il_Disinganno_%281753-54%29_-_Detail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{E164A41D-A597-4071-A821-F2A3C24D3F2C}"/>
+    <hyperlink ref="A85" r:id="rId23" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Francesco_Queirolo_-_Il_Disinganno_%281753-54%29_-_Detail.jpg/1280px-Francesco_Queirolo_-_Il_Disinganno_%281753-54%29_-_Detail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{E164A41D-A597-4071-A821-F2A3C24D3F2C}"/>
     <hyperlink ref="A58" r:id="rId24" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/40/Virginia_State_Capitol_complex_-_Houdon%27s_Washington%2C_seen_from_the_front.jpg/960px-Virginia_State_Capitol_complex_-_Houdon%27s_Washington%2C_seen_from_the_front.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7D07FDBD-D83E-44FD-9843-724946F8CF2E}"/>
     <hyperlink ref="A59" r:id="rId25" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a9/Benjamin_Franklin_by_Jean-Antoine_Houdon_Louvre_RF349_%28001%29.jpg/960px-Benjamin_Franklin_by_Jean-Antoine_Houdon_Louvre_RF349_%28001%29.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{02EF6FBA-1D59-44C1-81B9-9E02FBFCA15E}"/>
     <hyperlink ref="A60" r:id="rId26" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Jean_Jacques_Rousseau_-_Jean-Antoine_Houdon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_1729_-_photo_2.jpg/960px-Jean_Jacques_Rousseau_-_Jean-Antoine_Houdon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_1729_-_photo_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{891A227E-7E17-4543-A86F-E151DEDE309A}"/>
-    <hyperlink ref="A80" r:id="rId27" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/WA1216_99_Lower_Belvedere_Apotheosis_of_Prince_Eugene_of_Savoy_3D.jpg/1280px-WA1216_99_Lower_Belvedere_Apotheosis_of_Prince_Eugene_of_Savoy_3D.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{64E12365-8F6F-4867-9D1F-F6D484E30252}"/>
+    <hyperlink ref="A79" r:id="rId27" display="https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/WA1216_99_Lower_Belvedere_Apotheosis_of_Prince_Eugene_of_Savoy_3D.jpg/1280px-WA1216_99_Lower_Belvedere_Apotheosis_of_Prince_Eugene_of_Savoy_3D.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original" xr:uid="{64E12365-8F6F-4867-9D1F-F6D484E30252}"/>
     <hyperlink ref="A4" r:id="rId28" xr:uid="{D7C82055-C52E-45AE-9DBA-19B870EA7238}"/>
     <hyperlink ref="A13" r:id="rId29" xr:uid="{92F5F847-C929-46B0-B7D5-EABFBD5C1062}"/>
     <hyperlink ref="A8" r:id="rId30" xr:uid="{BD82F391-08E2-4580-9316-5F6036E48C50}"/>
     <hyperlink ref="A10" r:id="rId31" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/24/Monument_to_William_Pitt%2C_Earl_of_Chatham%2C_Westminster_Abbey_02.jpg/1280px-Monument_to_William_Pitt%2C_Earl_of_Chatham%2C_Westminster_Abbey_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{090DEA6E-279F-4E35-9453-E91299BE8DB1}"/>
     <hyperlink ref="A9" r:id="rId32" xr:uid="{D556DA19-547A-422C-8D59-F79689BBC3AD}"/>
-    <hyperlink ref="A98" r:id="rId33" xr:uid="{DF772C01-846B-46CB-BBB5-54B3A39DFA21}"/>
-    <hyperlink ref="A99" r:id="rId34" xr:uid="{86F08EE4-9192-45E7-B96F-AA2CFF20DED3}"/>
-    <hyperlink ref="A100" r:id="rId35" xr:uid="{DF13CE7F-4EE7-4AC2-911A-28AC8D58DC65}"/>
-    <hyperlink ref="A75" r:id="rId36" xr:uid="{735A23FA-995E-46FA-B865-5B5875BF663B}"/>
-    <hyperlink ref="A103" r:id="rId37" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Louvre_lens_l%27affliction_jean-baptiste_stouf_v_1789_-1.jpg/960px-Louvre_lens_l%27affliction_jean-baptiste_stouf_v_1789_-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4CAA7886-2A7B-4B31-80C6-C94546C79E78}"/>
+    <hyperlink ref="A97" r:id="rId33" xr:uid="{DF772C01-846B-46CB-BBB5-54B3A39DFA21}"/>
+    <hyperlink ref="A98" r:id="rId34" xr:uid="{86F08EE4-9192-45E7-B96F-AA2CFF20DED3}"/>
+    <hyperlink ref="A99" r:id="rId35" xr:uid="{DF13CE7F-4EE7-4AC2-911A-28AC8D58DC65}"/>
+    <hyperlink ref="A74" r:id="rId36" xr:uid="{735A23FA-995E-46FA-B865-5B5875BF663B}"/>
+    <hyperlink ref="A102" r:id="rId37" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Louvre_lens_l%27affliction_jean-baptiste_stouf_v_1789_-1.jpg/960px-Louvre_lens_l%27affliction_jean-baptiste_stouf_v_1789_-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4CAA7886-2A7B-4B31-80C6-C94546C79E78}"/>
     <hyperlink ref="A18" r:id="rId38" xr:uid="{E510A62E-C5C1-4187-BB94-122445CA89D9}"/>
     <hyperlink ref="A19" r:id="rId39" xr:uid="{B20F13C1-D167-415A-B47F-AF926F0C3CAD}"/>
     <hyperlink ref="W21" r:id="rId40" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/EdmeBouchardon-FrancoisHubertDrouais.JPG/960px-EdmeBouchardon-FrancoisHubertDrouais.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{695A1C2D-051F-4A6D-9187-F83F25B5D93C}"/>
     <hyperlink ref="A62" r:id="rId41" xr:uid="{73A207B4-13BA-44CB-8D20-61BB82BA279C}"/>
     <hyperlink ref="W50" r:id="rId42" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/EdmeBouchardon-FrancoisHubertDrouais.JPG/960px-EdmeBouchardon-FrancoisHubertDrouais.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{177A6C13-47F3-441E-8A4D-77ACBE2C7EE1}"/>
     <hyperlink ref="A50" r:id="rId43" xr:uid="{EB94FBA9-28BA-4C8B-A988-F9496F21CACF}"/>
-    <hyperlink ref="A72" r:id="rId44" location="/media/File:Austria-00838_-_Empress_Maria_Theresa_(21042592266).jpg" xr:uid="{8D15B4F7-D8DE-41FF-AFC1-6942F522286A}"/>
-    <hyperlink ref="A56" r:id="rId45" xr:uid="{A0D6DDDB-4568-4AE8-9DB6-7F8F191373F7}"/>
-    <hyperlink ref="A63" r:id="rId46" xr:uid="{4A148A4D-BAD5-46E3-B00E-6801D3D7EE62}"/>
-    <hyperlink ref="A90" r:id="rId47" xr:uid="{80CF61D8-9703-4219-BCE7-043C33659633}"/>
-    <hyperlink ref="A20" r:id="rId48" xr:uid="{EDC78297-9DF1-47A1-A85D-5CD7A18A019D}"/>
-    <hyperlink ref="A41" r:id="rId49" xr:uid="{6D89E607-E8D6-4112-8858-1C158E67C1BD}"/>
-    <hyperlink ref="A102" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/%C3%89glise_Saint-Sulpice_de_Paris_Monument_Jean-Baptiste_Languet_de_Gergy.jpg/1280px-%C3%89glise_Saint-Sulpice_de_Paris_Monument_Jean-Baptiste_Languet_de_Gergy.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{25C8C2C4-4F33-4299-90F9-5FC260F89F59}"/>
-    <hyperlink ref="A11" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/21/Thetis_dipping_Achilles_into_the_River_Styx_%2849219058951%29.jpg/1280px-Thetis_dipping_Achilles_into_the_River_Styx_%2849219058951%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6B56F7E3-B4F2-4BCA-90F7-CB2B33A8065F}"/>
-    <hyperlink ref="A5" r:id="rId52" xr:uid="{76D35042-825A-4CF8-BC76-DA445E85ABE2}"/>
-    <hyperlink ref="A14" r:id="rId53" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/Marie-Antoinette%2C_reine_de_France_-_Louis_Boizot_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_4515.jpg/1280px-Marie-Antoinette%2C_reine_de_France_-_Louis_Boizot_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_4515.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EFF1BD6F-96BD-440D-B128-4D0F5A419C91}"/>
-    <hyperlink ref="A89" r:id="rId54" xr:uid="{F76FAC8C-01CA-4532-B5F5-6F6F84CEE2B0}"/>
-    <hyperlink ref="A91" r:id="rId55" xr:uid="{35AF36E4-3878-4F7F-A947-FB78406D2575}"/>
-    <hyperlink ref="A22" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Chartres_-_Cath%C3%A9drale_Notre-Dame_-_L%27Assomption_%28Charles-Antoine_Bridan%29.jpg/960px-Chartres_-_Cath%C3%A9drale_Notre-Dame_-_L%27Assomption_%28Charles-Antoine_Bridan%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{36D8FDD5-F2AB-4FAD-A8A1-FB5C4788CEAB}"/>
-    <hyperlink ref="A52" r:id="rId57" xr:uid="{109BC90B-9DF3-42E9-B979-2BE112F23FB7}"/>
-    <hyperlink ref="A46" r:id="rId58" xr:uid="{4B6430AA-9055-4BD2-88A3-DE5F9053E399}"/>
-    <hyperlink ref="A47" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_177.JPG/960px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_177.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6C4A4583-92AC-41E0-80C7-F8C00255063E}"/>
-    <hyperlink ref="A106" r:id="rId60" xr:uid="{34369B02-D34B-4131-A338-511D7ACF06B8}"/>
-    <hyperlink ref="A53" r:id="rId61" xr:uid="{61309A5B-5C60-4B12-BD40-33E580A62672}"/>
-    <hyperlink ref="A42" r:id="rId62" xr:uid="{5B77419D-BD87-4E18-8412-975EA001E41F}"/>
-    <hyperlink ref="A107" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Bust_of_Moses_Mendelssohn_by_Jean-Pierre-Antoine_Tassaert.jpg/500px-Bust_of_Moses_Mendelssohn_by_Jean-Pierre-Antoine_Tassaert.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7BA96FFB-24B1-483D-AA2F-83C31FC109F7}"/>
-    <hyperlink ref="A87" r:id="rId64" xr:uid="{164E8FBD-B3C1-43AD-B5D6-7B72A57C8B80}"/>
-    <hyperlink ref="A110" r:id="rId65" xr:uid="{3596A210-86AA-42CC-A99A-7E64E20F3043}"/>
+    <hyperlink ref="A56" r:id="rId44" xr:uid="{A0D6DDDB-4568-4AE8-9DB6-7F8F191373F7}"/>
+    <hyperlink ref="A63" r:id="rId45" xr:uid="{4A148A4D-BAD5-46E3-B00E-6801D3D7EE62}"/>
+    <hyperlink ref="A89" r:id="rId46" xr:uid="{80CF61D8-9703-4219-BCE7-043C33659633}"/>
+    <hyperlink ref="A20" r:id="rId47" xr:uid="{EDC78297-9DF1-47A1-A85D-5CD7A18A019D}"/>
+    <hyperlink ref="A41" r:id="rId48" xr:uid="{6D89E607-E8D6-4112-8858-1C158E67C1BD}"/>
+    <hyperlink ref="A101" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/%C3%89glise_Saint-Sulpice_de_Paris_Monument_Jean-Baptiste_Languet_de_Gergy.jpg/1280px-%C3%89glise_Saint-Sulpice_de_Paris_Monument_Jean-Baptiste_Languet_de_Gergy.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{25C8C2C4-4F33-4299-90F9-5FC260F89F59}"/>
+    <hyperlink ref="A11" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/21/Thetis_dipping_Achilles_into_the_River_Styx_%2849219058951%29.jpg/1280px-Thetis_dipping_Achilles_into_the_River_Styx_%2849219058951%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6B56F7E3-B4F2-4BCA-90F7-CB2B33A8065F}"/>
+    <hyperlink ref="A5" r:id="rId51" xr:uid="{76D35042-825A-4CF8-BC76-DA445E85ABE2}"/>
+    <hyperlink ref="A14" r:id="rId52" display="https://upload.wikimedia.org/wikipedia/commons/thumb/0/01/Marie-Antoinette%2C_reine_de_France_-_Louis_Boizot_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_4515.jpg/1280px-Marie-Antoinette%2C_reine_de_France_-_Louis_Boizot_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_4515.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EFF1BD6F-96BD-440D-B128-4D0F5A419C91}"/>
+    <hyperlink ref="A88" r:id="rId53" xr:uid="{F76FAC8C-01CA-4532-B5F5-6F6F84CEE2B0}"/>
+    <hyperlink ref="A90" r:id="rId54" xr:uid="{35AF36E4-3878-4F7F-A947-FB78406D2575}"/>
+    <hyperlink ref="A22" r:id="rId55" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Chartres_-_Cath%C3%A9drale_Notre-Dame_-_L%27Assomption_%28Charles-Antoine_Bridan%29.jpg/960px-Chartres_-_Cath%C3%A9drale_Notre-Dame_-_L%27Assomption_%28Charles-Antoine_Bridan%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{36D8FDD5-F2AB-4FAD-A8A1-FB5C4788CEAB}"/>
+    <hyperlink ref="A52" r:id="rId56" xr:uid="{109BC90B-9DF3-42E9-B979-2BE112F23FB7}"/>
+    <hyperlink ref="A46" r:id="rId57" xr:uid="{4B6430AA-9055-4BD2-88A3-DE5F9053E399}"/>
+    <hyperlink ref="A47" r:id="rId58" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_177.JPG/960px-Lens_-_Inauguration_du_Louvre-Lens_le_4_d%C3%A9cembre_2012%2C_la_Galerie_du_Temps%2C_n%C2%B0_177.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6C4A4583-92AC-41E0-80C7-F8C00255063E}"/>
+    <hyperlink ref="A105" r:id="rId59" xr:uid="{34369B02-D34B-4131-A338-511D7ACF06B8}"/>
+    <hyperlink ref="A53" r:id="rId60" xr:uid="{61309A5B-5C60-4B12-BD40-33E580A62672}"/>
+    <hyperlink ref="A42" r:id="rId61" xr:uid="{5B77419D-BD87-4E18-8412-975EA001E41F}"/>
+    <hyperlink ref="A106" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Bust_of_Moses_Mendelssohn_by_Jean-Pierre-Antoine_Tassaert.jpg/500px-Bust_of_Moses_Mendelssohn_by_Jean-Pierre-Antoine_Tassaert.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7BA96FFB-24B1-483D-AA2F-83C31FC109F7}"/>
+    <hyperlink ref="A86" r:id="rId63" xr:uid="{164E8FBD-B3C1-43AD-B5D6-7B72A57C8B80}"/>
+    <hyperlink ref="A109" r:id="rId64" xr:uid="{3596A210-86AA-42CC-A99A-7E64E20F3043}"/>
+    <hyperlink ref="A71" r:id="rId65" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/46/Austria-00838_-_Empress_Maria_Theresa_%2821042592266%29.jpg/1280px-Austria-00838_-_Empress_Maria_Theresa_%2821042592266%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C61BDDE1-B736-4B08-834A-20A71172028B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -7622,7 +7622,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>c.1760</t>
+          <t>environ 1760</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">

--- a/quizzes/sculpture-18e.xlsx
+++ b/quizzes/sculpture-18e.xlsx
@@ -7658,7 +7658,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>environ 1760</t>
+          <t>1760 environ</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
